--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -313,69 +313,69 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
+    <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
   </si>
   <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
@@ -388,13 +388,22 @@
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Germany Bundesliga</t>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>France Ligue 1</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
@@ -403,15 +412,6 @@
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -427,27 +427,27 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -493,205 +493,232 @@
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Toronto II</t>
+    <t>Kabel Novi Sad</t>
   </si>
   <si>
     <t>Fakel</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Karlovac 1919</t>
+  </si>
+  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
     <t>Brann W</t>
   </si>
   <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Karlovac 1919</t>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
   </si>
   <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Örebro</t>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
     <t>Rijeka</t>
   </si>
   <si>
+    <t>PSV W</t>
+  </si>
+  <si>
     <t>Utrecht W</t>
   </si>
   <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Pescara</t>
   </si>
   <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Monza</t>
   </si>
   <si>
     <t>Avellino</t>
   </si>
   <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
     <t>Cesena</t>
   </si>
   <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Pescara</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
   </si>
   <si>
     <t>Dundalk</t>
@@ -700,57 +727,30 @@
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
     <t>Galway United</t>
   </si>
   <si>
+    <t>Levante UD</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>ÍA</t>
   </si>
   <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -766,111 +766,111 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
     <t>Spartak Subotica</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
     <t>Radnik Bijeljina</t>
   </si>
   <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -913,205 +913,232 @@
     <t>Arda</t>
   </si>
   <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>New York RB II</t>
+    <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Liepāja</t>
   </si>
   <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Rudeš</t>
+  </si>
+  <si>
     <t>Haugesund W</t>
   </si>
   <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Rudeš</t>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
   </si>
   <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Brage</t>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
     <t>Heerenveen W</t>
   </si>
   <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Spezia</t>
   </si>
   <si>
     <t>Mantova</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Empoli</t>
   </si>
   <si>
     <t>Modena</t>
   </si>
   <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
     <t>Calcio Padova</t>
   </si>
   <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Spezia</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
   </si>
   <si>
     <t>Bohemians</t>
@@ -1120,57 +1147,30 @@
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
     <t>Keflavík</t>
   </si>
   <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>FH</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1186,109 +1186,109 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
     <t>Napredak</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Almagro</t>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Celje</t>
   </si>
   <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
     <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Confiança</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4265,7 +4265,7 @@
         <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>159</v>
@@ -4450,7 +4450,7 @@
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
         <v>160</v>
@@ -5187,10 +5187,10 @@
         <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
         <v>164</v>
@@ -5372,10 +5372,10 @@
         <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
         <v>165</v>
@@ -5557,10 +5557,10 @@
         <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
         <v>166</v>
@@ -5742,7 +5742,7 @@
         <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5927,7 +5927,7 @@
         <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -6112,10 +6112,10 @@
         <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>169</v>
@@ -6297,10 +6297,10 @@
         <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
         <v>170</v>
@@ -6482,10 +6482,10 @@
         <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E27" t="s">
         <v>171</v>
@@ -6852,10 +6852,10 @@
         <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>173</v>
@@ -7222,7 +7222,7 @@
         <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -7410,7 +7410,7 @@
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>176</v>
@@ -7592,10 +7592,10 @@
         <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>177</v>
@@ -7777,10 +7777,10 @@
         <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>178</v>
@@ -7962,7 +7962,7 @@
         <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
         <v>144</v>
@@ -8147,10 +8147,10 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
         <v>180</v>
@@ -8332,10 +8332,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>181</v>
@@ -8887,10 +8887,10 @@
         <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E40" t="s">
         <v>184</v>
@@ -9072,10 +9072,10 @@
         <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
         <v>185</v>
@@ -9442,7 +9442,7 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
         <v>144</v>
@@ -9627,7 +9627,7 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -9812,7 +9812,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
         <v>144</v>
@@ -9997,7 +9997,7 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D46" t="s">
         <v>144</v>
@@ -10182,7 +10182,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10367,7 +10367,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10552,7 +10552,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
         <v>145</v>
@@ -10740,7 +10740,7 @@
         <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E50" t="s">
         <v>194</v>
@@ -10773,7 +10773,7 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -11295,7 +11295,7 @@
         <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
         <v>197</v>
@@ -11328,7 +11328,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11477,7 +11477,7 @@
         <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D54" t="s">
         <v>144</v>
@@ -11662,7 +11662,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
         <v>144</v>
@@ -11847,7 +11847,7 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
         <v>144</v>
@@ -12032,7 +12032,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D57" t="s">
         <v>144</v>
@@ -13142,7 +13142,7 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>144</v>
@@ -14252,7 +14252,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
         <v>144</v>
@@ -14437,7 +14437,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D70" t="s">
         <v>144</v>
@@ -14476,13 +14476,13 @@
         <v>426</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14527,10 +14527,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14807,7 +14807,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>144</v>
@@ -14992,7 +14992,7 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
         <v>144</v>
@@ -15216,13 +15216,13 @@
         <v>426</v>
       </c>
       <c r="P74">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15267,10 +15267,10 @@
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH74">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>144</v>
@@ -15547,7 +15547,7 @@
         <v>79</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>144</v>
@@ -15732,7 +15732,7 @@
         <v>79</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>144</v>
@@ -15917,7 +15917,7 @@
         <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>144</v>
@@ -16102,7 +16102,7 @@
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>144</v>
@@ -16287,7 +16287,7 @@
         <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>144</v>
@@ -16472,7 +16472,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>144</v>
@@ -17212,10 +17212,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D85" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
         <v>229</v>
@@ -17397,10 +17397,10 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>230</v>
@@ -17436,13 +17436,13 @@
         <v>426</v>
       </c>
       <c r="P86">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17582,7 +17582,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D87" t="s">
         <v>145</v>
@@ -17767,10 +17767,10 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E88" t="s">
         <v>232</v>
@@ -17806,13 +17806,13 @@
         <v>426</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17952,7 +17952,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
         <v>145</v>
@@ -18140,7 +18140,7 @@
         <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E90" t="s">
         <v>234</v>
@@ -18322,7 +18322,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
         <v>145</v>
@@ -18507,7 +18507,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D92" t="s">
         <v>145</v>
@@ -18692,7 +18692,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
         <v>145</v>
@@ -18877,10 +18877,10 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E94" t="s">
         <v>238</v>
@@ -19062,10 +19062,10 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E95" t="s">
         <v>239</v>
@@ -19432,7 +19432,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19617,7 +19617,7 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D98" t="s">
         <v>145</v>
@@ -19802,7 +19802,7 @@
         <v>82</v>
       </c>
       <c r="C99" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
         <v>145</v>
@@ -19987,7 +19987,7 @@
         <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
         <v>145</v>
@@ -20727,7 +20727,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D104" t="s">
         <v>145</v>
@@ -21100,7 +21100,7 @@
         <v>137</v>
       </c>
       <c r="D106" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E106" t="s">
         <v>250</v>
@@ -21467,7 +21467,7 @@
         <v>87</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D108" t="s">
         <v>145</v>
@@ -21652,7 +21652,7 @@
         <v>87</v>
       </c>
       <c r="C109" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
         <v>144</v>
@@ -21837,10 +21837,10 @@
         <v>87</v>
       </c>
       <c r="C110" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D110" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
         <v>254</v>
@@ -22207,7 +22207,7 @@
         <v>87</v>
       </c>
       <c r="C112" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D112" t="s">
         <v>144</v>
@@ -22392,7 +22392,7 @@
         <v>87</v>
       </c>
       <c r="C113" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D113" t="s">
         <v>145</v>
@@ -22577,10 +22577,10 @@
         <v>87</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D114" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
         <v>258</v>
@@ -22613,7 +22613,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22762,7 +22762,7 @@
         <v>87</v>
       </c>
       <c r="C115" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D115" t="s">
         <v>144</v>
@@ -22950,7 +22950,7 @@
         <v>137</v>
       </c>
       <c r="D116" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E116" t="s">
         <v>260</v>
@@ -23135,7 +23135,7 @@
         <v>137</v>
       </c>
       <c r="D117" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>261</v>
@@ -23317,10 +23317,10 @@
         <v>87</v>
       </c>
       <c r="C118" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E118" t="s">
         <v>262</v>
@@ -23502,7 +23502,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D119" t="s">
         <v>145</v>
@@ -23687,7 +23687,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D120" t="s">
         <v>145</v>
@@ -23872,10 +23872,10 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D121" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E121" t="s">
         <v>265</v>
@@ -24057,10 +24057,10 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D122" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>266</v>
@@ -24242,7 +24242,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
         <v>144</v>
@@ -24427,7 +24427,7 @@
         <v>87</v>
       </c>
       <c r="C124" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
         <v>144</v>
@@ -24612,10 +24612,10 @@
         <v>87</v>
       </c>
       <c r="C125" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D125" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>269</v>
@@ -24797,7 +24797,7 @@
         <v>87</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
         <v>144</v>
@@ -24982,10 +24982,10 @@
         <v>87</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E127" t="s">
         <v>271</v>
@@ -25167,10 +25167,10 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E128" t="s">
         <v>272</v>
@@ -25352,10 +25352,10 @@
         <v>87</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E129" t="s">
         <v>273</v>
@@ -25537,7 +25537,7 @@
         <v>87</v>
       </c>
       <c r="C130" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -25722,10 +25722,10 @@
         <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="D131" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
         <v>275</v>
@@ -25907,10 +25907,10 @@
         <v>87</v>
       </c>
       <c r="C132" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E132" t="s">
         <v>276</v>
@@ -26092,7 +26092,7 @@
         <v>87</v>
       </c>
       <c r="C133" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
         <v>144</v>
@@ -26277,10 +26277,10 @@
         <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E134" t="s">
         <v>278</v>
@@ -26462,7 +26462,7 @@
         <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26647,10 +26647,10 @@
         <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D136" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E136" t="s">
         <v>280</v>
@@ -27017,7 +27017,7 @@
         <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D138" t="s">
         <v>144</v>
@@ -27202,10 +27202,10 @@
         <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D139" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E139" t="s">
         <v>283</v>
@@ -27238,7 +27238,7 @@
         <v>-1</v>
       </c>
       <c r="O139" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P139">
         <v>0</v>
@@ -27387,10 +27387,10 @@
         <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D140" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E140" t="s">
         <v>284</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="429">
   <si>
     <t>Date</t>
   </si>
@@ -235,6 +235,9 @@
     <t>12:30</t>
   </si>
   <si>
+    <t>12:45</t>
+  </si>
+  <si>
     <t>13:00</t>
   </si>
   <si>
@@ -325,99 +328,102 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Croatia Druga HNL</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Croatia Druga HNL</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
+    <t>South Africa Premier Soccer League</t>
   </si>
   <si>
     <t>France National</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
+    <t>Netherlands Eredivisie Women</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Netherlands Eredivisie Women</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -430,21 +436,18 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -472,12 +475,12 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
@@ -508,226 +511,232 @@
     <t>Sabah</t>
   </si>
   <si>
+    <t>Karlovac 1919</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Anorthosis</t>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Brann W</t>
   </si>
   <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>Molde W</t>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
   </si>
   <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Karlovac 1919</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
   </si>
   <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>Ranheim</t>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
+    <t>Coca-Cola</t>
   </si>
   <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>HamKam</t>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Villefranche</t>
   </si>
   <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
     <t>Wil</t>
   </si>
   <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Aarau</t>
   </si>
   <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Torino</t>
   </si>
   <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Galway United</t>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>Levante UD</t>
@@ -736,18 +745,15 @@
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>ÍA</t>
   </si>
   <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -757,120 +763,117 @@
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
     <t>San Telmo</t>
   </si>
   <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
     <t>Maranhão</t>
   </si>
   <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Brusque</t>
   </si>
   <si>
     <t>Orense SC</t>
   </si>
   <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Partizan</t>
   </si>
   <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
+    <t>Rudar Prijedor</t>
   </si>
   <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -892,12 +895,12 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -928,226 +931,232 @@
     <t>Kapaz</t>
   </si>
   <si>
+    <t>Rudeš</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Digenis Ypsonas</t>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
   </si>
   <si>
     <t>Admira</t>
   </si>
   <si>
-    <t>Røa Women</t>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
   </si>
   <si>
     <t>Lyn W</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Rudeš</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Brage</t>
   </si>
   <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Kongsvinger</t>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Brage</t>
+    <t>Al Ittihad</t>
   </si>
   <si>
     <t>Pharco</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Ajaccio</t>
   </si>
   <si>
+    <t>Thór</t>
+  </si>
+  <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
     <t>Vaduz</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
     <t>Sassuolo</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>CA Osasuna</t>
@@ -1156,18 +1165,15 @@
     <t>Waterford</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
   </si>
   <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
@@ -1177,118 +1183,115 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Leones del Norte</t>
   </si>
   <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
   </si>
   <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
+    <t>Sarajevo</t>
   </si>
   <si>
     <t>Confiança</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -1857,16 +1860,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1893,7 +1896,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2042,16 +2045,16 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2078,7 +2081,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2227,16 +2230,16 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2263,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2412,16 +2415,16 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2448,7 +2451,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2597,16 +2600,16 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2633,7 +2636,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2782,16 +2785,16 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2818,7 +2821,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2967,16 +2970,16 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3003,7 +3006,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3152,16 +3155,16 @@
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3188,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3337,16 +3340,16 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3373,7 +3376,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3522,16 +3525,16 @@
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3558,7 +3561,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3707,16 +3710,16 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3743,7 +3746,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3892,16 +3895,16 @@
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3928,7 +3931,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4077,16 +4080,16 @@
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4113,7 +4116,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4262,16 +4265,16 @@
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -4298,7 +4301,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4447,16 +4450,16 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4483,7 +4486,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4632,16 +4635,16 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4668,7 +4671,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4817,16 +4820,16 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4853,7 +4856,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5002,16 +5005,16 @@
         <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -5038,7 +5041,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5187,16 +5190,16 @@
         <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -5223,7 +5226,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5361,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3">
-        <v>46150.54166666666</v>
+        <v>46150.53125</v>
       </c>
     </row>
     <row r="21" spans="1:61">
@@ -5369,19 +5372,19 @@
         <v>46150</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -5408,7 +5411,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5554,19 +5557,19 @@
         <v>46150</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F22" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5593,7 +5596,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5739,19 +5742,19 @@
         <v>46150</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
         <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5778,7 +5781,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5924,19 +5927,19 @@
         <v>46150</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
       </c>
       <c r="E24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5963,7 +5966,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -6109,19 +6112,19 @@
         <v>46150</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -6148,7 +6151,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -6294,19 +6297,19 @@
         <v>46150</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
         <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6333,7 +6336,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -6479,19 +6482,19 @@
         <v>46150</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6518,7 +6521,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6664,19 +6667,19 @@
         <v>46150</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
         <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F28" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6703,7 +6706,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6849,19 +6852,19 @@
         <v>46150</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6888,7 +6891,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -7034,19 +7037,19 @@
         <v>46150</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7073,7 +7076,7 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -7219,19 +7222,19 @@
         <v>46150</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F31" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7258,7 +7261,7 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -7404,19 +7407,19 @@
         <v>46150</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F32" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7443,7 +7446,7 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -7589,19 +7592,19 @@
         <v>46150</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
         <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F33" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7628,7 +7631,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7774,19 +7777,19 @@
         <v>46150</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7813,7 +7816,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7959,19 +7962,19 @@
         <v>46150</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7998,7 +8001,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -8144,19 +8147,19 @@
         <v>46150</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -8183,7 +8186,7 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -8329,19 +8332,19 @@
         <v>46150</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -8368,7 +8371,7 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -8517,16 +8520,16 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -8553,7 +8556,7 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -8691,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3">
-        <v>46150.5625</v>
+        <v>46150.54166666666</v>
       </c>
     </row>
     <row r="39" spans="1:61">
@@ -8699,19 +8702,19 @@
         <v>46150</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8738,7 +8741,7 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -8887,16 +8890,16 @@
         <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8923,7 +8926,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -9061,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3">
-        <v>46150.58333333334</v>
+        <v>46150.5625</v>
       </c>
     </row>
     <row r="41" spans="1:61">
@@ -9069,19 +9072,19 @@
         <v>46150</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F41" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -9108,7 +9111,7 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -9254,19 +9257,19 @@
         <v>46150</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -9293,7 +9296,7 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -9439,19 +9442,19 @@
         <v>46150</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -9478,7 +9481,7 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -9624,19 +9627,19 @@
         <v>46150</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
       </c>
       <c r="E44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -9663,7 +9666,7 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -9809,19 +9812,19 @@
         <v>46150</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9848,7 +9851,7 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -9994,19 +9997,19 @@
         <v>46150</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F46" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -10033,7 +10036,7 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -10179,19 +10182,19 @@
         <v>46150</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -10218,7 +10221,7 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -10364,19 +10367,19 @@
         <v>46150</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
       </c>
       <c r="E48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F48" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -10403,7 +10406,7 @@
         <v>-1</v>
       </c>
       <c r="O48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -10549,19 +10552,19 @@
         <v>46150</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
         <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F49" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -10588,7 +10591,7 @@
         <v>-1</v>
       </c>
       <c r="O49" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -10737,16 +10740,16 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -10911,7 +10914,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3">
-        <v>46150.60416666666</v>
+        <v>46150.58333333334</v>
       </c>
     </row>
     <row r="51" spans="1:61">
@@ -10919,19 +10922,19 @@
         <v>46150</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F51" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -10958,7 +10961,7 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -11104,19 +11107,19 @@
         <v>46150</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F52" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -11143,7 +11146,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11289,7 +11292,7 @@
         <v>46150</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
         <v>119</v>
@@ -11298,10 +11301,10 @@
         <v>145</v>
       </c>
       <c r="E53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -11328,7 +11331,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11474,19 +11477,19 @@
         <v>46150</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -11513,7 +11516,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11662,16 +11665,16 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F55" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -11698,7 +11701,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11836,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3">
-        <v>46150.625</v>
+        <v>46150.60416666666</v>
       </c>
     </row>
     <row r="56" spans="1:61">
@@ -11844,19 +11847,19 @@
         <v>46150</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -11883,7 +11886,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12029,19 +12032,19 @@
         <v>46150</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -12068,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -12214,19 +12217,19 @@
         <v>46150</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F58" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -12253,7 +12256,7 @@
         <v>-1</v>
       </c>
       <c r="O58" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -12399,19 +12402,19 @@
         <v>46150</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12438,7 +12441,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12584,19 +12587,19 @@
         <v>46150</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F60" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12623,7 +12626,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12769,19 +12772,19 @@
         <v>46150</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F61" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12808,7 +12811,7 @@
         <v>-1</v>
       </c>
       <c r="O61" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -12954,19 +12957,19 @@
         <v>46150</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12993,7 +12996,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -13139,19 +13142,19 @@
         <v>46150</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
         <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -13178,7 +13181,7 @@
         <v>-1</v>
       </c>
       <c r="O63" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -13327,16 +13330,16 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F64" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -13363,7 +13366,7 @@
         <v>-1</v>
       </c>
       <c r="O64" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -13501,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3">
-        <v>46150.63541666666</v>
+        <v>46150.625</v>
       </c>
     </row>
     <row r="65" spans="1:61">
@@ -13509,19 +13512,19 @@
         <v>46150</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13548,7 +13551,7 @@
         <v>-1</v>
       </c>
       <c r="O65" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -13694,19 +13697,19 @@
         <v>46150</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13733,7 +13736,7 @@
         <v>-1</v>
       </c>
       <c r="O66" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -13879,19 +13882,19 @@
         <v>46150</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F67" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13918,7 +13921,7 @@
         <v>-1</v>
       </c>
       <c r="O67" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -14064,19 +14067,19 @@
         <v>46150</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F68" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -14103,7 +14106,7 @@
         <v>-1</v>
       </c>
       <c r="O68" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -14252,16 +14255,16 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F69" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14288,7 +14291,7 @@
         <v>-1</v>
       </c>
       <c r="O69" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -14426,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3">
-        <v>46150.64583333334</v>
+        <v>46150.63541666666</v>
       </c>
     </row>
     <row r="70" spans="1:61">
@@ -14434,19 +14437,19 @@
         <v>46150</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D70" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F70" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14473,7 +14476,7 @@
         <v>-1</v>
       </c>
       <c r="O70" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P70">
         <v>1.57</v>
@@ -14619,19 +14622,19 @@
         <v>46150</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F71" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -14658,7 +14661,7 @@
         <v>-1</v>
       </c>
       <c r="O71" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -14804,19 +14807,19 @@
         <v>46150</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D72" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -14843,7 +14846,7 @@
         <v>-1</v>
       </c>
       <c r="O72" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -14989,19 +14992,19 @@
         <v>46150</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F73" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -15028,7 +15031,7 @@
         <v>-1</v>
       </c>
       <c r="O73" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P73">
         <v>0</v>
@@ -15174,19 +15177,19 @@
         <v>46150</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F74" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -15213,7 +15216,7 @@
         <v>-1</v>
       </c>
       <c r="O74" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P74">
         <v>0</v>
@@ -15359,19 +15362,19 @@
         <v>46150</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F75" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -15398,7 +15401,7 @@
         <v>-1</v>
       </c>
       <c r="O75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P75">
         <v>0</v>
@@ -15544,19 +15547,19 @@
         <v>46150</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F76" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -15583,7 +15586,7 @@
         <v>-1</v>
       </c>
       <c r="O76" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P76">
         <v>0</v>
@@ -15729,19 +15732,19 @@
         <v>46150</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F77" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -15768,7 +15771,7 @@
         <v>-1</v>
       </c>
       <c r="O77" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P77">
         <v>0</v>
@@ -15914,19 +15917,19 @@
         <v>46150</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F78" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -15953,7 +15956,7 @@
         <v>-1</v>
       </c>
       <c r="O78" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P78">
         <v>0</v>
@@ -16099,19 +16102,19 @@
         <v>46150</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -16138,7 +16141,7 @@
         <v>-1</v>
       </c>
       <c r="O79" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P79">
         <v>0</v>
@@ -16284,19 +16287,19 @@
         <v>46150</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D80" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F80" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -16323,7 +16326,7 @@
         <v>-1</v>
       </c>
       <c r="O80" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P80">
         <v>0</v>
@@ -16469,19 +16472,19 @@
         <v>46150</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F81" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -16508,7 +16511,7 @@
         <v>-1</v>
       </c>
       <c r="O81" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P81">
         <v>0</v>
@@ -16657,16 +16660,16 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
       </c>
       <c r="E82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F82" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -16693,7 +16696,7 @@
         <v>-1</v>
       </c>
       <c r="O82" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P82">
         <v>0</v>
@@ -16831,7 +16834,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3">
-        <v>46150.65625</v>
+        <v>46150.64583333334</v>
       </c>
     </row>
     <row r="83" spans="1:61">
@@ -16839,19 +16842,19 @@
         <v>46150</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F83" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -16878,7 +16881,7 @@
         <v>-1</v>
       </c>
       <c r="O83" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P83">
         <v>0</v>
@@ -17024,19 +17027,19 @@
         <v>46150</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D84" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F84" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -17063,7 +17066,7 @@
         <v>-1</v>
       </c>
       <c r="O84" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P84">
         <v>0</v>
@@ -17209,19 +17212,19 @@
         <v>46150</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D85" t="s">
         <v>145</v>
       </c>
       <c r="E85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F85" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -17248,7 +17251,7 @@
         <v>-1</v>
       </c>
       <c r="O85" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P85">
         <v>0</v>
@@ -17394,19 +17397,19 @@
         <v>46150</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F86" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -17433,7 +17436,7 @@
         <v>-1</v>
       </c>
       <c r="O86" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -17579,19 +17582,19 @@
         <v>46150</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -17618,7 +17621,7 @@
         <v>-1</v>
       </c>
       <c r="O87" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P87">
         <v>0</v>
@@ -17764,19 +17767,19 @@
         <v>46150</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D88" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E88" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F88" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -17803,16 +17806,16 @@
         <v>-1</v>
       </c>
       <c r="O88" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P88">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17949,19 +17952,19 @@
         <v>46150</v>
       </c>
       <c r="B89" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
         <v>145</v>
       </c>
       <c r="E89" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F89" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -17988,16 +17991,16 @@
         <v>-1</v>
       </c>
       <c r="O89" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18134,19 +18137,19 @@
         <v>46150</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D90" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F90" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -18173,7 +18176,7 @@
         <v>-1</v>
       </c>
       <c r="O90" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P90">
         <v>0</v>
@@ -18319,19 +18322,19 @@
         <v>46150</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C91" t="s">
         <v>130</v>
       </c>
       <c r="D91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -18358,7 +18361,7 @@
         <v>-1</v>
       </c>
       <c r="O91" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P91">
         <v>0</v>
@@ -18504,19 +18507,19 @@
         <v>46150</v>
       </c>
       <c r="B92" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E92" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -18543,7 +18546,7 @@
         <v>-1</v>
       </c>
       <c r="O92" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P92">
         <v>0</v>
@@ -18689,19 +18692,19 @@
         <v>46150</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F93" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -18728,7 +18731,7 @@
         <v>-1</v>
       </c>
       <c r="O93" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -18877,16 +18880,16 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F94" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -18913,7 +18916,7 @@
         <v>-1</v>
       </c>
       <c r="O94" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -19051,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3">
-        <v>46150.66666666666</v>
+        <v>46150.65625</v>
       </c>
     </row>
     <row r="95" spans="1:61">
@@ -19059,19 +19062,19 @@
         <v>46150</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
         <v>145</v>
       </c>
       <c r="E95" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F95" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -19098,7 +19101,7 @@
         <v>-1</v>
       </c>
       <c r="O95" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -19244,19 +19247,19 @@
         <v>46150</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -19283,7 +19286,7 @@
         <v>-1</v>
       </c>
       <c r="O96" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -19432,16 +19435,16 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F97" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -19468,7 +19471,7 @@
         <v>-1</v>
       </c>
       <c r="O97" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P97">
         <v>0</v>
@@ -19606,7 +19609,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3">
-        <v>46150.67708333334</v>
+        <v>46150.66666666666</v>
       </c>
     </row>
     <row r="98" spans="1:61">
@@ -19614,19 +19617,19 @@
         <v>46150</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F98" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -19653,7 +19656,7 @@
         <v>-1</v>
       </c>
       <c r="O98" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -19799,19 +19802,19 @@
         <v>46150</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E99" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F99" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -19838,7 +19841,7 @@
         <v>-1</v>
       </c>
       <c r="O99" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -19984,19 +19987,19 @@
         <v>46150</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D100" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E100" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F100" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -20023,7 +20026,7 @@
         <v>-1</v>
       </c>
       <c r="O100" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -20172,16 +20175,16 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E101" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F101" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -20208,7 +20211,7 @@
         <v>-1</v>
       </c>
       <c r="O101" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -20346,7 +20349,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3">
-        <v>46150.70833333334</v>
+        <v>46150.67708333334</v>
       </c>
     </row>
     <row r="102" spans="1:61">
@@ -20357,16 +20360,16 @@
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D102" t="s">
         <v>145</v>
       </c>
       <c r="E102" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F102" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -20393,7 +20396,7 @@
         <v>-1</v>
       </c>
       <c r="O102" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -20531,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3">
-        <v>46150.8125</v>
+        <v>46150.70833333334</v>
       </c>
     </row>
     <row r="103" spans="1:61">
@@ -20542,16 +20545,16 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F103" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -20578,7 +20581,7 @@
         <v>-1</v>
       </c>
       <c r="O103" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -20716,7 +20719,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3">
-        <v>46150.83333333334</v>
+        <v>46150.8125</v>
       </c>
     </row>
     <row r="104" spans="1:61">
@@ -20724,19 +20727,19 @@
         <v>46150</v>
       </c>
       <c r="B104" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D104" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F104" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -20763,7 +20766,7 @@
         <v>-1</v>
       </c>
       <c r="O104" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P104">
         <v>0</v>
@@ -20912,16 +20915,16 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E105" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F105" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -20948,7 +20951,7 @@
         <v>-1</v>
       </c>
       <c r="O105" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -21086,7 +21089,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3">
-        <v>46150.85416666666</v>
+        <v>46150.83333333334</v>
       </c>
     </row>
     <row r="106" spans="1:61">
@@ -21097,16 +21100,16 @@
         <v>87</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D106" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E106" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F106" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -21133,7 +21136,7 @@
         <v>-1</v>
       </c>
       <c r="O106" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -21271,7 +21274,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3">
-        <v>46150.875</v>
+        <v>46150.85416666666</v>
       </c>
     </row>
     <row r="107" spans="1:61">
@@ -21279,19 +21282,19 @@
         <v>46150</v>
       </c>
       <c r="B107" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E107" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F107" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -21318,7 +21321,7 @@
         <v>-1</v>
       </c>
       <c r="O107" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P107">
         <v>0</v>
@@ -21464,19 +21467,19 @@
         <v>46150</v>
       </c>
       <c r="B108" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C108" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="D108" t="s">
         <v>145</v>
       </c>
       <c r="E108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F108" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -21503,7 +21506,7 @@
         <v>-1</v>
       </c>
       <c r="O108" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -21649,19 +21652,19 @@
         <v>46150</v>
       </c>
       <c r="B109" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F109" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -21688,7 +21691,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21834,19 +21837,19 @@
         <v>46150</v>
       </c>
       <c r="B110" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="D110" t="s">
         <v>145</v>
       </c>
       <c r="E110" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F110" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -21873,7 +21876,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -22019,19 +22022,19 @@
         <v>46150</v>
       </c>
       <c r="B111" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>145</v>
       </c>
       <c r="E111" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F111" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -22058,7 +22061,7 @@
         <v>-1</v>
       </c>
       <c r="O111" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -22204,19 +22207,19 @@
         <v>46150</v>
       </c>
       <c r="B112" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="D112" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F112" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -22243,7 +22246,7 @@
         <v>-1</v>
       </c>
       <c r="O112" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -22389,19 +22392,19 @@
         <v>46150</v>
       </c>
       <c r="B113" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="D113" t="s">
         <v>145</v>
       </c>
       <c r="E113" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F113" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -22428,7 +22431,7 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -22574,19 +22577,19 @@
         <v>46150</v>
       </c>
       <c r="B114" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="D114" t="s">
         <v>145</v>
       </c>
       <c r="E114" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F114" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -22613,7 +22616,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22759,19 +22762,19 @@
         <v>46150</v>
       </c>
       <c r="B115" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="D115" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F115" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -22798,7 +22801,7 @@
         <v>-1</v>
       </c>
       <c r="O115" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -22944,19 +22947,19 @@
         <v>46150</v>
       </c>
       <c r="B116" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D116" t="s">
         <v>145</v>
       </c>
       <c r="E116" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F116" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -22983,7 +22986,7 @@
         <v>-1</v>
       </c>
       <c r="O116" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -23129,19 +23132,19 @@
         <v>46150</v>
       </c>
       <c r="B117" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F117" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -23168,7 +23171,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23314,19 +23317,19 @@
         <v>46150</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D118" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F118" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -23353,7 +23356,7 @@
         <v>-1</v>
       </c>
       <c r="O118" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -23499,19 +23502,19 @@
         <v>46150</v>
       </c>
       <c r="B119" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C119" t="s">
         <v>141</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F119" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -23538,7 +23541,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23684,19 +23687,19 @@
         <v>46150</v>
       </c>
       <c r="B120" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F120" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -23723,7 +23726,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23869,19 +23872,19 @@
         <v>46150</v>
       </c>
       <c r="B121" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
       </c>
       <c r="E121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F121" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -23908,7 +23911,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24054,19 +24057,19 @@
         <v>46150</v>
       </c>
       <c r="B122" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F122" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -24093,7 +24096,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24239,19 +24242,19 @@
         <v>46150</v>
       </c>
       <c r="B123" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C123" t="s">
         <v>140</v>
       </c>
       <c r="D123" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F123" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -24278,7 +24281,7 @@
         <v>-1</v>
       </c>
       <c r="O123" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -24424,19 +24427,19 @@
         <v>46150</v>
       </c>
       <c r="B124" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F124" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -24463,7 +24466,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24609,19 +24612,19 @@
         <v>46150</v>
       </c>
       <c r="B125" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F125" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -24648,7 +24651,7 @@
         <v>-1</v>
       </c>
       <c r="O125" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P125">
         <v>0</v>
@@ -24794,19 +24797,19 @@
         <v>46150</v>
       </c>
       <c r="B126" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D126" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F126" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -24833,7 +24836,7 @@
         <v>-1</v>
       </c>
       <c r="O126" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -24979,19 +24982,19 @@
         <v>46150</v>
       </c>
       <c r="B127" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F127" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -25018,7 +25021,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25164,19 +25167,19 @@
         <v>46150</v>
       </c>
       <c r="B128" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F128" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -25203,7 +25206,7 @@
         <v>-1</v>
       </c>
       <c r="O128" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -25349,19 +25352,19 @@
         <v>46150</v>
       </c>
       <c r="B129" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D129" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F129" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -25388,7 +25391,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -25534,19 +25537,19 @@
         <v>46150</v>
       </c>
       <c r="B130" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
       </c>
       <c r="E130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F130" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -25573,7 +25576,7 @@
         <v>-1</v>
       </c>
       <c r="O130" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -25719,19 +25722,19 @@
         <v>46150</v>
       </c>
       <c r="B131" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F131" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -25758,7 +25761,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25904,19 +25907,19 @@
         <v>46150</v>
       </c>
       <c r="B132" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C132" t="s">
         <v>142</v>
       </c>
       <c r="D132" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F132" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -25943,7 +25946,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26089,19 +26092,19 @@
         <v>46150</v>
       </c>
       <c r="B133" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E133" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F133" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -26128,7 +26131,7 @@
         <v>-1</v>
       </c>
       <c r="O133" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -26274,19 +26277,19 @@
         <v>46150</v>
       </c>
       <c r="B134" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F134" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -26313,7 +26316,7 @@
         <v>-1</v>
       </c>
       <c r="O134" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -26459,19 +26462,19 @@
         <v>46150</v>
       </c>
       <c r="B135" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E135" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F135" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -26498,7 +26501,7 @@
         <v>-1</v>
       </c>
       <c r="O135" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -26644,19 +26647,19 @@
         <v>46150</v>
       </c>
       <c r="B136" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D136" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F136" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -26683,7 +26686,7 @@
         <v>-1</v>
       </c>
       <c r="O136" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P136">
         <v>0</v>
@@ -26829,19 +26832,19 @@
         <v>46150</v>
       </c>
       <c r="B137" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="D137" t="s">
         <v>145</v>
       </c>
       <c r="E137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F137" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -26868,7 +26871,7 @@
         <v>-1</v>
       </c>
       <c r="O137" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P137">
         <v>0</v>
@@ -27014,19 +27017,19 @@
         <v>46150</v>
       </c>
       <c r="B138" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D138" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E138" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F138" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -27053,7 +27056,7 @@
         <v>-1</v>
       </c>
       <c r="O138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P138">
         <v>0</v>
@@ -27199,19 +27202,19 @@
         <v>46150</v>
       </c>
       <c r="B139" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C139" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D139" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E139" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F139" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -27384,19 +27387,19 @@
         <v>46150</v>
       </c>
       <c r="B140" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C140" t="s">
         <v>142</v>
       </c>
       <c r="D140" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E140" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F140" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -27423,7 +27426,7 @@
         <v>-1</v>
       </c>
       <c r="O140" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P140">
         <v>0</v>
@@ -27569,19 +27572,19 @@
         <v>46150</v>
       </c>
       <c r="B141" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C141" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F141" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -27608,7 +27611,7 @@
         <v>-1</v>
       </c>
       <c r="O141" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P141">
         <v>0</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,6 +316,9 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -325,61 +328,61 @@
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Netherlands Eredivisie Women</t>
@@ -388,42 +391,39 @@
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,18 +484,21 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
@@ -505,66 +508,63 @@
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
     <t>Austria Salzburg</t>
   </si>
   <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
@@ -574,189 +574,189 @@
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
     <t>PSV W</t>
   </si>
   <si>
     <t>Ajax W</t>
   </si>
   <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
     <t>PEC Zwolle W</t>
   </si>
   <si>
-    <t>Rijeka</t>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Wil</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Rapperswil-Jona</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Aarau</t>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
     <t>Venezia</t>
   </si>
   <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>Lens</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
     <t>Standard Liège</t>
   </si>
   <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Lens</t>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Torino</t>
+    <t>Levante UD</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>ÍA</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -772,108 +772,108 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
     <t>Radnički Niš</t>
   </si>
   <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Posusje</t>
   </si>
   <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
     <t>Željezničar</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -904,18 +904,21 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
     <t>New York RB II</t>
   </si>
   <si>
@@ -925,66 +928,63 @@
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>First Vienna</t>
   </si>
   <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
     <t>Austria Lustenau</t>
   </si>
   <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
     <t>Lyn W</t>
   </si>
   <si>
@@ -994,189 +994,189 @@
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Pharco</t>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>HB</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
     <t>AZ W</t>
   </si>
   <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
     <t>Feyenoord W</t>
   </si>
   <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
     <t>HERA</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Bellinzona</t>
+    <t>Neuchâtel Xamax</t>
   </si>
   <si>
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
     <t>Palermo</t>
   </si>
   <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
     <t>Mantova</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
+    <t>Cobh Ramblers</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
+    <t>Nantes</t>
+  </si>
+  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Derry City</t>
+  </si>
+  <si>
     <t>OH Leuven</t>
   </si>
   <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Nantes</t>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
+    <t>Waterford</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
-    <t>Waterford</t>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1192,106 +1192,106 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
     <t>LFK Mladost Lučani</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Napredak</t>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
   </si>
   <si>
     <t>Velež</t>
   </si>
   <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Confiança</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4268,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4453,7 +4453,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -5560,7 +5560,7 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
         <v>145</v>
@@ -5745,10 +5745,10 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5930,7 +5930,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -6115,10 +6115,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6300,7 +6300,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6670,7 +6670,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6855,10 +6855,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7040,7 +7040,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7225,10 +7225,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7410,7 +7410,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -7595,7 +7595,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7780,10 +7780,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7965,7 +7965,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -8150,7 +8150,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -8335,10 +8335,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8520,7 +8520,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -9075,10 +9075,10 @@
         <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
         <v>186</v>
@@ -9260,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
         <v>145</v>
@@ -9445,7 +9445,7 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
         <v>146</v>
@@ -9630,10 +9630,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9815,10 +9815,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -10003,7 +10003,7 @@
         <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10185,7 +10185,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
         <v>146</v>
@@ -10370,10 +10370,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10555,10 +10555,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10740,7 +10740,7 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -10925,10 +10925,10 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -11110,7 +11110,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11146,7 +11146,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11331,7 +11331,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11480,10 +11480,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11665,10 +11665,10 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11850,7 +11850,7 @@
         <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D56" t="s">
         <v>145</v>
@@ -12220,7 +12220,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12405,7 +12405,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12590,7 +12590,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12775,7 +12775,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -13145,7 +13145,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13330,7 +13330,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -14479,13 +14479,13 @@
         <v>427</v>
       </c>
       <c r="P70">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14530,10 +14530,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14625,7 +14625,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14810,7 +14810,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14995,7 +14995,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15365,7 +15365,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15550,7 +15550,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15735,7 +15735,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15920,7 +15920,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -16105,7 +16105,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16144,13 +16144,13 @@
         <v>427</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16195,10 +16195,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH79">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16475,7 +16475,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16660,7 +16660,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -17030,7 +17030,7 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D84" t="s">
         <v>146</v>
@@ -17215,7 +17215,7 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D85" t="s">
         <v>145</v>
@@ -17254,13 +17254,13 @@
         <v>427</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17400,7 +17400,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17585,7 +17585,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17770,10 +17770,10 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -17955,7 +17955,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
         <v>145</v>
@@ -17994,13 +17994,13 @@
         <v>427</v>
       </c>
       <c r="P89">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18140,7 +18140,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18325,7 +18325,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18695,7 +18695,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18880,10 +18880,10 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
         <v>239</v>
@@ -19250,10 +19250,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19435,10 +19435,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19620,7 +19620,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19805,7 +19805,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19990,7 +19990,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20175,7 +20175,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20360,7 +20360,7 @@
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D102" t="s">
         <v>145</v>
@@ -20730,7 +20730,7 @@
         <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D104" t="s">
         <v>146</v>
@@ -21470,10 +21470,10 @@
         <v>88</v>
       </c>
       <c r="C108" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
@@ -21840,10 +21840,10 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -22025,7 +22025,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D111" t="s">
         <v>145</v>
@@ -22210,7 +22210,7 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="D112" t="s">
         <v>145</v>
@@ -22395,10 +22395,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22580,7 +22580,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D114" t="s">
         <v>145</v>
@@ -22765,7 +22765,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D115" t="s">
         <v>145</v>
@@ -22950,10 +22950,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23135,10 +23135,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23320,10 +23320,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23505,10 +23505,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23541,7 +23541,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23690,10 +23690,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23875,7 +23875,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
@@ -24060,10 +24060,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24245,7 +24245,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D123" t="s">
         <v>145</v>
@@ -24430,7 +24430,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -24615,10 +24615,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24800,10 +24800,10 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24985,10 +24985,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25170,10 +25170,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25355,7 +25355,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25540,10 +25540,10 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130" t="s">
         <v>275</v>
@@ -25725,7 +25725,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -25910,7 +25910,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
         <v>146</v>
@@ -26095,7 +26095,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26280,10 +26280,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
@@ -26465,7 +26465,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D135" t="s">
         <v>146</v>
@@ -26650,10 +26650,10 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
@@ -26686,7 +26686,7 @@
         <v>-1</v>
       </c>
       <c r="O136" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P136">
         <v>0</v>
@@ -26835,10 +26835,10 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="D137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
@@ -27020,10 +27020,10 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="D138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>
@@ -27208,7 +27208,7 @@
         <v>140</v>
       </c>
       <c r="D139" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E139" t="s">
         <v>284</v>
@@ -27390,10 +27390,10 @@
         <v>88</v>
       </c>
       <c r="C140" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D140" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E140" t="s">
         <v>285</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,10 +310,16 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>Russia FNL</t>
@@ -322,75 +328,69 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
+    <t>Netherlands Eredivisie Women</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Netherlands Eredivisie Women</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -403,27 +403,27 @@
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -439,18 +439,18 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -475,25 +475,31 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>Terengganu</t>
+  </si>
+  <si>
     <t>PDRM</t>
   </si>
   <si>
-    <t>Terengganu</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
+    <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
   </si>
   <si>
     <t>Fakel</t>
@@ -502,121 +508,133 @@
     <t>Toronto II</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
     <t>Brann W</t>
   </si>
   <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
     <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Coca-Cola</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>Villefranche</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
   </si>
   <si>
     <t>CFR Cluj</t>
@@ -625,255 +643,237 @@
     <t>Rijeka</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
     <t>Aarau</t>
   </si>
   <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Étoile Carouge</t>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
   </si>
   <si>
     <t>Monza</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>Torino</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
+    <t>Wisła Kraków</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Levante UD</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Wisła Kraków</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>ÍA</t>
+  </si>
+  <si>
+    <t>Fram</t>
   </si>
   <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
     <t>Itabaiana</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
     <t>Inter de Limeira</t>
   </si>
   <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
   </si>
   <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -895,25 +895,31 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Imigresen</t>
+  </si>
+  <si>
     <t>Pulau Pinang</t>
   </si>
   <si>
-    <t>Imigresen</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
+    <t>Arda</t>
   </si>
   <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Arda</t>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>SKA Khabarovsk</t>
@@ -922,121 +928,133 @@
     <t>New York RB II</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
     <t>Admira</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>Thór</t>
   </si>
   <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Ajaccio</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>HERA</t>
   </si>
   <si>
     <t>CS U Craiova</t>
@@ -1045,253 +1063,235 @@
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
     <t>Feyenoord W</t>
   </si>
   <si>
-    <t>HERA</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
   </si>
   <si>
     <t>Empoli</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Mantova</t>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Kerry</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
+    <t>Chrobry Głogów</t>
+  </si>
+  <si>
+    <t>Waterford</t>
   </si>
   <si>
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Chrobry Głogów</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
+  </si>
+  <si>
+    <t>Valur</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
     <t>Floresta</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Santa Cruz</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Napredak</t>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
   </si>
   <si>
     <t>Almagro</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
     <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3898,7 +3898,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4083,7 +4083,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4453,7 +4453,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -4823,7 +4823,7 @@
         <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -5563,7 +5563,7 @@
         <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5745,7 +5745,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5930,10 +5930,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6115,7 +6115,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -6300,7 +6300,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6670,10 +6670,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6855,7 +6855,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -7040,10 +7040,10 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -7225,7 +7225,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -7410,7 +7410,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -7595,10 +7595,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7780,10 +7780,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7968,7 +7968,7 @@
         <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8150,10 +8150,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8335,7 +8335,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8520,7 +8520,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -9075,10 +9075,10 @@
         <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
         <v>186</v>
@@ -9260,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
         <v>145</v>
@@ -9445,10 +9445,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9630,10 +9630,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9815,10 +9815,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -10000,10 +10000,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10185,7 +10185,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
         <v>146</v>
@@ -10370,10 +10370,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10558,7 +10558,7 @@
         <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10743,7 +10743,7 @@
         <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -11110,7 +11110,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11146,7 +11146,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11480,10 +11480,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11665,7 +11665,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
         <v>145</v>
@@ -11701,7 +11701,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11850,7 +11850,7 @@
         <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D56" t="s">
         <v>145</v>
@@ -12220,7 +12220,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12590,7 +12590,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12775,7 +12775,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12960,7 +12960,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13145,7 +13145,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13330,7 +13330,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -14625,7 +14625,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14995,7 +14995,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15034,13 +15034,13 @@
         <v>427</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15085,10 +15085,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15920,7 +15920,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -16105,7 +16105,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16144,13 +16144,13 @@
         <v>427</v>
       </c>
       <c r="P79">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16195,10 +16195,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH79">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16848,7 +16848,7 @@
         <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E83" t="s">
         <v>228</v>
@@ -17030,7 +17030,7 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D84" t="s">
         <v>146</v>
@@ -17218,7 +17218,7 @@
         <v>130</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17254,13 +17254,13 @@
         <v>427</v>
       </c>
       <c r="P85">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17400,7 +17400,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17588,7 +17588,7 @@
         <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17624,13 +17624,13 @@
         <v>427</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17770,10 +17770,10 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -17955,10 +17955,10 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
@@ -18140,7 +18140,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18325,7 +18325,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18510,7 +18510,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18695,10 +18695,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18880,7 +18880,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19250,7 +19250,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
         <v>146</v>
@@ -20360,7 +20360,7 @@
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D102" t="s">
         <v>145</v>
@@ -20730,7 +20730,7 @@
         <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D104" t="s">
         <v>146</v>
@@ -20915,7 +20915,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21470,7 +21470,7 @@
         <v>88</v>
       </c>
       <c r="C108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
         <v>146</v>
@@ -21655,7 +21655,7 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
         <v>146</v>
@@ -21840,10 +21840,10 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -21876,7 +21876,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -22025,10 +22025,10 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22210,10 +22210,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22395,10 +22395,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22580,7 +22580,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="D114" t="s">
         <v>145</v>
@@ -22765,7 +22765,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D115" t="s">
         <v>145</v>
@@ -22950,10 +22950,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="D116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23135,7 +23135,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="D117" t="s">
         <v>145</v>
@@ -23320,10 +23320,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23505,10 +23505,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23541,7 +23541,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23690,10 +23690,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23875,7 +23875,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
@@ -24060,10 +24060,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24245,10 +24245,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24430,10 +24430,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24615,10 +24615,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24800,7 +24800,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D126" t="s">
         <v>145</v>
@@ -24985,7 +24985,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D127" t="s">
         <v>145</v>
@@ -25170,7 +25170,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -25355,7 +25355,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25540,7 +25540,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25725,10 +25725,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25910,7 +25910,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
         <v>146</v>
@@ -26095,10 +26095,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26280,10 +26280,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
@@ -26835,7 +26835,7 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D137" t="s">
         <v>146</v>
@@ -27020,10 +27020,10 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D138" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>
@@ -27390,7 +27390,7 @@
         <v>88</v>
       </c>
       <c r="C140" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D140" t="s">
         <v>145</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,45 +310,45 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
@@ -358,16 +358,22 @@
     <t>Denmark Superliga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
@@ -376,12 +382,6 @@
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -394,30 +394,30 @@
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -490,390 +490,390 @@
     <t>Petrojet</t>
   </si>
   <si>
+    <t>BFC Daugavpils</t>
+  </si>
+  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>BFC Daugavpils</t>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
   </si>
   <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
   </si>
   <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Brann W</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
   </si>
   <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
     <t>Elfsborg</t>
   </si>
   <si>
+    <t>HamKam</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>HamKam</t>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
   </si>
   <si>
     <t>NAC Breda W</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
     <t>Aarau</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
   </si>
   <si>
     <t>Frosinone</t>
   </si>
   <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
     <t>Cádiz</t>
   </si>
   <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
     <t>Pescara</t>
   </si>
   <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Monza</t>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
   </si>
   <si>
     <t>Standard Liège</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Drogheda United</t>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Lens</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
     <t>Levante UD</t>
   </si>
   <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>Stjarnan</t>
   </si>
   <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
     <t>Brusque</t>
   </si>
   <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
     <t>Atlético Rafaela</t>
   </si>
   <si>
-    <t>Domžale</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -910,388 +910,388 @@
     <t>Wadi Degla</t>
   </si>
   <si>
+    <t>Riga</t>
+  </si>
+  <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Riga</t>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
     <t>First Vienna</t>
   </si>
   <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
     <t>Haugesund W</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
   </si>
   <si>
     <t>Lyn W</t>
   </si>
   <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
   </si>
   <si>
     <t>Twente W</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
     <t>Vaduz</t>
   </si>
   <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
   </si>
   <si>
     <t>Mantova</t>
   </si>
   <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
     <t>Deportivo La Coruña</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
     <t>Spezia</t>
   </si>
   <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Empoli</t>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Derry City</t>
   </si>
   <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Derry City</t>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Nantes</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Waterford</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
     <t>CA Osasuna</t>
   </si>
   <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>Valur</t>
+  </si>
+  <si>
     <t>KR</t>
   </si>
   <si>
     <t>Keflavík</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Celje</t>
-  </si>
-  <si>
     <t>Floresta</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3898,7 +3898,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4083,7 +4083,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4268,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4823,7 +4823,7 @@
         <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -5378,7 +5378,7 @@
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>166</v>
@@ -5745,7 +5745,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5930,10 +5930,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6115,10 +6115,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6485,7 +6485,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6670,7 +6670,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
         <v>146</v>
@@ -6855,10 +6855,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7040,10 +7040,10 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -7228,7 +7228,7 @@
         <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7410,10 +7410,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7595,10 +7595,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7780,7 +7780,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
@@ -7965,10 +7965,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8150,7 +8150,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -8338,7 +8338,7 @@
         <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8520,7 +8520,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -9260,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
         <v>145</v>
@@ -9445,7 +9445,7 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>145</v>
@@ -9815,10 +9815,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -10000,10 +10000,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10370,10 +10370,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10558,7 +10558,7 @@
         <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10928,7 +10928,7 @@
         <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -10961,7 +10961,7 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -11110,7 +11110,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11298,7 +11298,7 @@
         <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11701,7 +11701,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12405,7 +12405,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12960,7 +12960,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13145,7 +13145,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13330,7 +13330,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -14440,7 +14440,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
         <v>145</v>
@@ -14625,7 +14625,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14664,13 +14664,13 @@
         <v>427</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14715,10 +14715,10 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14810,7 +14810,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14995,7 +14995,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15034,13 +15034,13 @@
         <v>427</v>
       </c>
       <c r="P73">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15085,10 +15085,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH73">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15365,7 +15365,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15550,7 +15550,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15735,7 +15735,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15920,7 +15920,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -16105,7 +16105,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16290,7 +16290,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16475,7 +16475,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16660,7 +16660,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16848,7 +16848,7 @@
         <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E83" t="s">
         <v>228</v>
@@ -17400,10 +17400,10 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>231</v>
@@ -17585,10 +17585,10 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17624,13 +17624,13 @@
         <v>427</v>
       </c>
       <c r="P87">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17955,7 +17955,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18143,7 +18143,7 @@
         <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18325,7 +18325,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18510,7 +18510,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18695,10 +18695,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18880,10 +18880,10 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
         <v>239</v>
@@ -18919,13 +18919,13 @@
         <v>427</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19065,10 +19065,10 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
@@ -19250,10 +19250,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19620,7 +19620,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19805,7 +19805,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19990,7 +19990,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20175,7 +20175,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20730,7 +20730,7 @@
         <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D104" t="s">
         <v>146</v>
@@ -20915,7 +20915,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21285,10 +21285,10 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E107" t="s">
         <v>252</v>
@@ -21655,10 +21655,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21840,10 +21840,10 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -21876,7 +21876,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -22025,7 +22025,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22210,10 +22210,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22395,7 +22395,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D113" t="s">
         <v>145</v>
@@ -22580,10 +22580,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22765,7 +22765,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D115" t="s">
         <v>145</v>
@@ -22950,7 +22950,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="D116" t="s">
         <v>145</v>
@@ -23135,7 +23135,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D117" t="s">
         <v>145</v>
@@ -23320,7 +23320,7 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D118" t="s">
         <v>146</v>
@@ -23505,7 +23505,7 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
         <v>146</v>
@@ -23690,7 +23690,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D120" t="s">
         <v>146</v>
@@ -23875,7 +23875,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
@@ -23911,7 +23911,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24060,10 +24060,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24245,10 +24245,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24430,7 +24430,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="D124" t="s">
         <v>145</v>
@@ -24615,7 +24615,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24800,7 +24800,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="D126" t="s">
         <v>145</v>
@@ -24985,10 +24985,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25170,10 +25170,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25355,7 +25355,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25540,7 +25540,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25725,7 +25725,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -25910,10 +25910,10 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -26095,10 +26095,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26280,7 +26280,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D134" t="s">
         <v>145</v>
@@ -26465,10 +26465,10 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="D135" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E135" t="s">
         <v>280</v>
@@ -26650,7 +26650,7 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D136" t="s">
         <v>146</v>
@@ -26835,7 +26835,7 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D137" t="s">
         <v>146</v>
@@ -27020,10 +27020,10 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>
@@ -27205,7 +27205,7 @@
         <v>88</v>
       </c>
       <c r="C139" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D139" t="s">
         <v>146</v>
@@ -27390,10 +27390,10 @@
         <v>88</v>
       </c>
       <c r="C140" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D140" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E140" t="s">
         <v>285</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,72 +316,72 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -394,30 +394,30 @@
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -475,109 +475,124 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
     <t>Brann W</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Liefering</t>
+    <t>Fortuna Ålesund</t>
   </si>
   <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
+    <t>Coca-Cola</t>
   </si>
   <si>
     <t>Viborg</t>
@@ -586,45 +601,33 @@
     <t>Kahraba Ismailia</t>
   </si>
   <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>Ranheim</t>
   </si>
   <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>Villefranche</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Durban City</t>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
   </si>
   <si>
     <t>PEC Zwolle W</t>
   </si>
   <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
@@ -634,9 +637,6 @@
     <t>Utrecht W</t>
   </si>
   <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
     <t>PSV W</t>
   </si>
   <si>
@@ -661,219 +661,219 @@
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Pescara</t>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Cork City</t>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Torino</t>
-  </si>
-  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Lens</t>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
     <t>Levante UD</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Fram</t>
+    <t>ÍA</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
     <t>Partizan</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -895,109 +895,124 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Admira</t>
+    <t>Lyn W</t>
   </si>
   <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
     <t>Liepāja</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>CSKA Sofia</t>
+    <t>Al Ittihad</t>
   </si>
   <si>
     <t>SønderjyskE</t>
@@ -1006,45 +1021,33 @@
     <t>Pharco</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Ajaccio</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>HB</t>
-  </si>
-  <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
   </si>
   <si>
     <t>HERA</t>
   </si>
   <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
@@ -1054,9 +1057,6 @@
     <t>Heerenveen W</t>
   </si>
   <si>
-    <t>AZ W</t>
-  </si>
-  <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
@@ -1081,217 +1081,217 @@
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Spezia</t>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Derry City</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>UCD</t>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Nantes</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
     <t>CA Osasuna</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
     <t>FH</t>
   </si>
   <si>
-    <t>Valur</t>
+    <t>Keflavík</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>OFK Beograd</t>
   </si>
   <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
     <t>Rangers</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Floresta</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4268,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4638,7 +4638,7 @@
         <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -5378,7 +5378,7 @@
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
         <v>166</v>
@@ -5560,10 +5560,10 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5745,7 +5745,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5930,7 +5930,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -6115,10 +6115,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6300,7 +6300,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6485,7 +6485,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6673,7 +6673,7 @@
         <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6855,7 +6855,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -7040,7 +7040,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7225,7 +7225,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
         <v>146</v>
@@ -7410,10 +7410,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7595,7 +7595,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7780,10 +7780,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7965,7 +7965,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -8150,10 +8150,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8335,10 +8335,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8520,7 +8520,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -9260,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
         <v>145</v>
@@ -9445,10 +9445,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9630,7 +9630,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -9815,10 +9815,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -10000,10 +10000,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10185,10 +10185,10 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -10370,10 +10370,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10555,10 +10555,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10925,7 +10925,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10961,7 +10961,7 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -11110,7 +11110,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11483,7 +11483,7 @@
         <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11516,7 +11516,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -12220,7 +12220,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12405,7 +12405,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12590,7 +12590,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -13554,13 +13554,13 @@
         <v>427</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13605,10 +13605,10 @@
         <v>0</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH65">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI65">
         <v>0</v>
@@ -14440,7 +14440,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D70" t="s">
         <v>145</v>
@@ -14664,13 +14664,13 @@
         <v>427</v>
       </c>
       <c r="P71">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14715,10 +14715,10 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH71">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14810,7 +14810,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14995,7 +14995,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15180,7 +15180,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15365,7 +15365,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15550,7 +15550,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15735,7 +15735,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15920,7 +15920,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -16105,7 +16105,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16329,13 +16329,13 @@
         <v>427</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16380,10 +16380,10 @@
         <v>0</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI80">
         <v>0</v>
@@ -16660,7 +16660,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16848,7 +16848,7 @@
         <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E83" t="s">
         <v>228</v>
@@ -17439,13 +17439,13 @@
         <v>427</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17770,7 +17770,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17955,7 +17955,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18143,7 +18143,7 @@
         <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18325,7 +18325,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18695,7 +18695,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18919,13 +18919,13 @@
         <v>427</v>
       </c>
       <c r="P94">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19065,10 +19065,10 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
@@ -19250,10 +19250,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19620,7 +19620,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19805,7 +19805,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19990,7 +19990,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20175,7 +20175,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20730,7 +20730,7 @@
         <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D104" t="s">
         <v>146</v>
@@ -20915,7 +20915,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21285,10 +21285,10 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E107" t="s">
         <v>252</v>
@@ -21655,10 +21655,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -22025,7 +22025,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22210,10 +22210,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22395,7 +22395,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D113" t="s">
         <v>145</v>
@@ -22580,7 +22580,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22765,7 +22765,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D115" t="s">
         <v>145</v>
@@ -22950,7 +22950,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D116" t="s">
         <v>145</v>
@@ -23135,10 +23135,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23320,10 +23320,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23505,10 +23505,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23690,7 +23690,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D120" t="s">
         <v>146</v>
@@ -23875,7 +23875,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
@@ -23911,7 +23911,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24060,7 +24060,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D122" t="s">
         <v>145</v>
@@ -24245,10 +24245,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24430,7 +24430,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="D124" t="s">
         <v>145</v>
@@ -24615,10 +24615,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24800,7 +24800,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="D126" t="s">
         <v>145</v>
@@ -24985,10 +24985,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25021,7 +25021,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D128" t="s">
         <v>146</v>
@@ -25355,7 +25355,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25540,7 +25540,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25725,7 +25725,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -25910,7 +25910,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -26095,7 +26095,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26280,10 +26280,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
@@ -26465,7 +26465,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26653,7 +26653,7 @@
         <v>140</v>
       </c>
       <c r="D136" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
@@ -26838,7 +26838,7 @@
         <v>140</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
@@ -27020,7 +27020,7 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D138" t="s">
         <v>146</v>
@@ -27205,7 +27205,7 @@
         <v>88</v>
       </c>
       <c r="C139" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D139" t="s">
         <v>146</v>
@@ -27390,7 +27390,7 @@
         <v>88</v>
       </c>
       <c r="C140" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D140" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,84 +310,84 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
@@ -397,10 +397,13 @@
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Italy Serie A</t>
@@ -409,21 +412,18 @@
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Spain La Liga</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+    <t>Slovenia PrvaLiga</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
+    <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>Terengganu</t>
+  </si>
+  <si>
     <t>PDRM</t>
   </si>
   <si>
-    <t>Terengganu</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
@@ -490,250 +490,253 @@
     <t>Al Mokawloon</t>
   </si>
   <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
   </si>
   <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
     <t>Amstetten</t>
   </si>
   <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Örebro</t>
+    <t>Kahraba Ismailia</t>
   </si>
   <si>
     <t>Coca-Cola</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
     <t>Durban City</t>
   </si>
   <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
   </si>
   <si>
     <t>Ajax W</t>
   </si>
   <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
     <t>Utrecht W</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Catanzaro</t>
   </si>
   <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
     <t>Cesena</t>
   </si>
   <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
     <t>Südtirol</t>
   </si>
   <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Torino</t>
   </si>
   <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Lens</t>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
+    <t>Levante UD</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
@@ -742,7 +745,7 @@
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
+    <t>Stjarnan</t>
   </si>
   <si>
     <t>Fram</t>
@@ -754,9 +757,6 @@
     <t>ÍA</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -772,108 +772,108 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
     <t>Maranhão</t>
   </si>
   <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Brusque</t>
   </si>
   <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -895,12 +895,12 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Imigresen</t>
+  </si>
+  <si>
     <t>Pulau Pinang</t>
   </si>
   <si>
-    <t>Imigresen</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -910,250 +910,253 @@
     <t>El Gounah</t>
   </si>
   <si>
+    <t>Arda</t>
+  </si>
+  <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Arda</t>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
   </si>
   <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
     <t>Austria Klagenfurt</t>
   </si>
   <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brage</t>
+    <t>Pharco</t>
   </si>
   <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>Thór</t>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
   </si>
   <si>
     <t>AZ W</t>
   </si>
   <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
     <t>Heerenveen W</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
+    <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Bari 1908</t>
   </si>
   <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
     <t>Calcio Padova</t>
   </si>
   <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
     <t>Juve Stabia</t>
   </si>
   <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Sassuolo</t>
   </si>
   <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Nantes</t>
+    <t>Cobh Ramblers</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
+    <t>CA Osasuna</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
@@ -1162,7 +1165,7 @@
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
+    <t>KR</t>
   </si>
   <si>
     <t>Valur</t>
@@ -1174,9 +1177,6 @@
     <t>Keflavík</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1192,106 +1192,106 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Rangers</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3898,7 +3898,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4083,7 +4083,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -5378,7 +5378,7 @@
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>166</v>
@@ -5563,7 +5563,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5748,7 +5748,7 @@
         <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5930,7 +5930,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -6115,7 +6115,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -6300,7 +6300,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6485,7 +6485,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6673,7 +6673,7 @@
         <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6855,10 +6855,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7040,7 +7040,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7225,10 +7225,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7410,10 +7410,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7595,10 +7595,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7780,7 +7780,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7968,7 +7968,7 @@
         <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8150,7 +8150,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -8520,10 +8520,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -9114,13 +9114,13 @@
         <v>427</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9260,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D42" t="s">
         <v>145</v>
@@ -9445,7 +9445,7 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>146</v>
@@ -9630,10 +9630,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -10000,7 +10000,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
         <v>146</v>
@@ -10185,7 +10185,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10370,7 +10370,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10740,10 +10740,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -12035,7 +12035,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12220,7 +12220,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12405,7 +12405,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12590,7 +12590,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12775,7 +12775,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12960,7 +12960,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13145,7 +13145,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13330,7 +13330,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13554,13 +13554,13 @@
         <v>427</v>
       </c>
       <c r="P65">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13605,10 +13605,10 @@
         <v>0</v>
       </c>
       <c r="AG65">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH65">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI65">
         <v>0</v>
@@ -14294,13 +14294,13 @@
         <v>427</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14345,10 +14345,10 @@
         <v>0</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI69">
         <v>0</v>
@@ -14440,7 +14440,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D70" t="s">
         <v>145</v>
@@ -15365,7 +15365,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -16290,7 +16290,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16475,7 +16475,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16660,7 +16660,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16848,7 +16848,7 @@
         <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E83" t="s">
         <v>228</v>
@@ -17030,7 +17030,7 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D84" t="s">
         <v>146</v>
@@ -17215,7 +17215,7 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
         <v>146</v>
@@ -17400,7 +17400,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
         <v>145</v>
@@ -17439,13 +17439,13 @@
         <v>427</v>
       </c>
       <c r="P86">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17585,7 +17585,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17770,7 +17770,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17958,7 +17958,7 @@
         <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
@@ -18140,10 +18140,10 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18179,13 +18179,13 @@
         <v>427</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18325,7 +18325,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18510,7 +18510,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18695,7 +18695,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18880,10 +18880,10 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
         <v>239</v>
@@ -19250,10 +19250,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19435,10 +19435,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19620,7 +19620,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19805,7 +19805,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19990,7 +19990,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20175,7 +20175,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20360,7 +20360,7 @@
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D102" t="s">
         <v>145</v>
@@ -21285,10 +21285,10 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E107" t="s">
         <v>252</v>
@@ -21473,7 +21473,7 @@
         <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
@@ -21658,7 +21658,7 @@
         <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21843,7 +21843,7 @@
         <v>139</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -22025,7 +22025,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22213,7 +22213,7 @@
         <v>139</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22580,10 +22580,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22765,10 +22765,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -23135,10 +23135,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23505,10 +23505,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23690,10 +23690,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23875,7 +23875,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
@@ -24063,7 +24063,7 @@
         <v>140</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24245,7 +24245,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24430,10 +24430,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24615,10 +24615,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24800,7 +24800,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="D126" t="s">
         <v>145</v>
@@ -24836,7 +24836,7 @@
         <v>-1</v>
       </c>
       <c r="O126" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -24988,7 +24988,7 @@
         <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25021,7 +25021,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25355,7 +25355,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25540,7 +25540,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25725,10 +25725,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25910,10 +25910,10 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -26095,7 +26095,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26280,7 +26280,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
         <v>146</v>
@@ -26465,7 +26465,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26653,7 +26653,7 @@
         <v>140</v>
       </c>
       <c r="D136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
@@ -26835,7 +26835,7 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="D137" t="s">
         <v>145</v>
@@ -27020,10 +27020,10 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="D138" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>
@@ -27205,7 +27205,7 @@
         <v>88</v>
       </c>
       <c r="C139" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D139" t="s">
         <v>146</v>
@@ -27390,7 +27390,7 @@
         <v>88</v>
       </c>
       <c r="C140" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D140" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="423">
   <si>
     <t>Date</t>
   </si>
@@ -316,12 +316,12 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -331,63 +331,63 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
+    <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Netherlands Eredivisie Women</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
@@ -418,12 +418,12 @@
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -436,21 +436,21 @@
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,24 +484,24 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Toronto II</t>
   </si>
   <si>
@@ -514,142 +514,145 @@
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
     <t>Molde W</t>
   </si>
   <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
     <t>Kapfenberger SV</t>
   </si>
   <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
     <t>Tammeka</t>
   </si>
   <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
+    <t>Varberg</t>
   </si>
   <si>
     <t>Örebro</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
-    <t>Durban City</t>
+    <t>Villefranche</t>
   </si>
   <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
   </si>
   <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
     <t>NAC Breda W</t>
   </si>
   <si>
-    <t>CFR Cluj</t>
+    <t>Ajax W</t>
   </si>
   <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
+    <t>Wil</t>
   </si>
   <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Wil</t>
+    <t>Aarau</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
@@ -658,105 +661,102 @@
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Aarau</t>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Catanzaro</t>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Avellino</t>
   </si>
   <si>
     <t>Monza</t>
   </si>
   <si>
-    <t>Avellino</t>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Cesena</t>
   </si>
   <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
-    <t>Cesena</t>
-  </si>
-  <si>
     <t>Südtirol</t>
   </si>
   <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>Wisła Kraków</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Levante UD</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>ÍA</t>
+  </si>
+  <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -772,108 +772,99 @@
     <t>Lexington</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
   </si>
   <si>
     <t>Radnik Bijeljina</t>
   </si>
   <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -904,24 +895,24 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
-  </si>
-  <si>
     <t>Arda</t>
   </si>
   <si>
     <t>Riga</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>New York RB II</t>
   </si>
   <si>
@@ -934,142 +925,145 @@
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
     <t>Røa Women</t>
   </si>
   <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>St. Pölten</t>
   </si>
   <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>CSKA Sofia</t>
+    <t>Värnamo</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
+    <t>Ajaccio</t>
   </si>
   <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>HB</t>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
   </si>
   <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
     <t>Twente W</t>
   </si>
   <si>
-    <t>CS U Craiova</t>
+    <t>AZ W</t>
   </si>
   <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
+    <t>Stade Nyonnais</t>
   </si>
   <si>
     <t>Bellinzona</t>
@@ -1078,105 +1072,102 @@
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Stade Nyonnais</t>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
   </si>
   <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Bari 1908</t>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Modena</t>
   </si>
   <si>
     <t>Empoli</t>
   </si>
   <si>
-    <t>Modena</t>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
   </si>
   <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
     <t>Mantova</t>
   </si>
   <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
     <t>Juve Stabia</t>
   </si>
   <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Chrobry Głogów</t>
+  </si>
+  <si>
+    <t>Waterford</t>
   </si>
   <si>
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
-    <t>Waterford</t>
+    <t>FH</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
+    <t>Keflavík</t>
+  </si>
+  <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1192,106 +1183,97 @@
     <t>Monterey Bay</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
   </si>
   <si>
     <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -1664,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI141"/>
+  <dimension ref="A1:BI138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1869,7 +1851,7 @@
         <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1896,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2054,7 +2036,7 @@
         <v>148</v>
       </c>
       <c r="F3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2081,7 +2063,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2239,7 +2221,7 @@
         <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2266,7 +2248,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2424,7 +2406,7 @@
         <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2451,7 +2433,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2609,7 +2591,7 @@
         <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2636,7 +2618,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2794,7 +2776,7 @@
         <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2821,7 +2803,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2979,7 +2961,7 @@
         <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3006,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3164,7 +3146,7 @@
         <v>154</v>
       </c>
       <c r="F9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3191,7 +3173,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3349,7 +3331,7 @@
         <v>155</v>
       </c>
       <c r="F10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3376,7 +3358,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3534,7 +3516,7 @@
         <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3561,7 +3543,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3719,7 +3701,7 @@
         <v>157</v>
       </c>
       <c r="F12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3746,7 +3728,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3904,7 +3886,7 @@
         <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3931,7 +3913,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4089,7 +4071,7 @@
         <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4116,7 +4098,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4274,7 +4256,7 @@
         <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -4301,7 +4283,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4459,7 +4441,7 @@
         <v>161</v>
       </c>
       <c r="F16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4486,7 +4468,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4644,7 +4626,7 @@
         <v>162</v>
       </c>
       <c r="F17" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4671,7 +4653,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4829,7 +4811,7 @@
         <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4856,7 +4838,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5014,7 +4996,7 @@
         <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -5041,7 +5023,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5199,7 +5181,7 @@
         <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -5226,7 +5208,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5378,13 +5360,13 @@
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
         <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -5411,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5560,7 +5542,7 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -5569,7 +5551,7 @@
         <v>167</v>
       </c>
       <c r="F22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5596,7 +5578,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5745,7 +5727,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5754,7 +5736,7 @@
         <v>168</v>
       </c>
       <c r="F23" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5781,7 +5763,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5933,13 +5915,13 @@
         <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
       </c>
       <c r="F24" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5966,7 +5948,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -6115,7 +6097,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -6124,7 +6106,7 @@
         <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -6151,7 +6133,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -6300,7 +6282,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6309,7 +6291,7 @@
         <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6336,7 +6318,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -6485,7 +6467,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6494,7 +6476,7 @@
         <v>172</v>
       </c>
       <c r="F27" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6521,7 +6503,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6670,16 +6652,16 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
       </c>
       <c r="F28" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6706,7 +6688,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6855,7 +6837,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -6864,7 +6846,7 @@
         <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6891,7 +6873,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -7040,16 +7022,16 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7076,7 +7058,7 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -7225,7 +7207,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -7234,7 +7216,7 @@
         <v>176</v>
       </c>
       <c r="F31" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7261,7 +7243,7 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -7410,7 +7392,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -7419,7 +7401,7 @@
         <v>177</v>
       </c>
       <c r="F32" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7446,7 +7428,7 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -7595,16 +7577,16 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
       </c>
       <c r="F33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7631,7 +7613,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7780,16 +7762,16 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
       </c>
       <c r="F34" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7816,7 +7798,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7965,7 +7947,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
         <v>145</v>
@@ -7974,7 +7956,7 @@
         <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -8001,7 +7983,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -8150,16 +8132,16 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -8186,7 +8168,7 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -8335,7 +8317,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8344,7 +8326,7 @@
         <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -8371,7 +8353,7 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -8520,16 +8502,16 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
       </c>
       <c r="F38" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -8556,7 +8538,7 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -8714,7 +8696,7 @@
         <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8741,7 +8723,7 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -8899,7 +8881,7 @@
         <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8926,7 +8908,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -9078,13 +9060,13 @@
         <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
         <v>186</v>
       </c>
       <c r="F41" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -9111,16 +9093,16 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P41">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9260,16 +9242,16 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -9296,16 +9278,16 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9445,16 +9427,16 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
       </c>
       <c r="F43" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -9481,7 +9463,7 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -9639,7 +9621,7 @@
         <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -9666,16 +9648,16 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9824,7 +9806,7 @@
         <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9851,7 +9833,7 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -10000,7 +9982,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
         <v>146</v>
@@ -10009,7 +9991,7 @@
         <v>191</v>
       </c>
       <c r="F46" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -10036,7 +10018,7 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -10194,7 +10176,7 @@
         <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -10221,7 +10203,7 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -10370,7 +10352,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10379,7 +10361,7 @@
         <v>193</v>
       </c>
       <c r="F48" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -10406,7 +10388,7 @@
         <v>-1</v>
       </c>
       <c r="O48" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -10564,7 +10546,7 @@
         <v>194</v>
       </c>
       <c r="F49" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -10591,7 +10573,7 @@
         <v>-1</v>
       </c>
       <c r="O49" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -10740,16 +10722,16 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
       </c>
       <c r="F50" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -10776,7 +10758,7 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -10925,7 +10907,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10934,7 +10916,7 @@
         <v>196</v>
       </c>
       <c r="F51" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -10961,7 +10943,7 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -11110,16 +11092,16 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
       </c>
       <c r="F52" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -11146,7 +11128,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11295,16 +11277,16 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
       </c>
       <c r="F53" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -11331,7 +11313,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11489,7 +11471,7 @@
         <v>199</v>
       </c>
       <c r="F54" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -11516,7 +11498,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11674,7 +11656,7 @@
         <v>200</v>
       </c>
       <c r="F55" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -11701,7 +11683,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11850,7 +11832,7 @@
         <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
         <v>145</v>
@@ -11859,7 +11841,7 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -11886,7 +11868,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12035,7 +12017,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12044,7 +12026,7 @@
         <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -12071,7 +12053,7 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -12220,7 +12202,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12229,7 +12211,7 @@
         <v>203</v>
       </c>
       <c r="F58" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -12256,7 +12238,7 @@
         <v>-1</v>
       </c>
       <c r="O58" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -12405,7 +12387,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12414,7 +12396,7 @@
         <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12441,7 +12423,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12590,7 +12572,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12599,7 +12581,7 @@
         <v>205</v>
       </c>
       <c r="F60" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12626,7 +12608,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12775,7 +12757,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12784,7 +12766,7 @@
         <v>206</v>
       </c>
       <c r="F61" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12811,7 +12793,7 @@
         <v>-1</v>
       </c>
       <c r="O61" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -12960,7 +12942,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -12969,7 +12951,7 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12996,7 +12978,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -13145,7 +13127,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13154,7 +13136,7 @@
         <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -13181,7 +13163,7 @@
         <v>-1</v>
       </c>
       <c r="O63" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -13330,7 +13312,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13339,7 +13321,7 @@
         <v>209</v>
       </c>
       <c r="F64" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -13366,7 +13348,7 @@
         <v>-1</v>
       </c>
       <c r="O64" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -13524,7 +13506,7 @@
         <v>210</v>
       </c>
       <c r="F65" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13551,7 +13533,7 @@
         <v>-1</v>
       </c>
       <c r="O65" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -13709,7 +13691,7 @@
         <v>211</v>
       </c>
       <c r="F66" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13736,7 +13718,7 @@
         <v>-1</v>
       </c>
       <c r="O66" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -13894,7 +13876,7 @@
         <v>212</v>
       </c>
       <c r="F67" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13921,16 +13903,16 @@
         <v>-1</v>
       </c>
       <c r="O67" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13975,10 +13957,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14079,7 +14061,7 @@
         <v>213</v>
       </c>
       <c r="F68" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -14106,7 +14088,7 @@
         <v>-1</v>
       </c>
       <c r="O68" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -14264,7 +14246,7 @@
         <v>214</v>
       </c>
       <c r="F69" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14291,16 +14273,16 @@
         <v>-1</v>
       </c>
       <c r="O69" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P69">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14345,10 +14327,10 @@
         <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH69">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI69">
         <v>0</v>
@@ -14440,7 +14422,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D70" t="s">
         <v>145</v>
@@ -14449,7 +14431,7 @@
         <v>215</v>
       </c>
       <c r="F70" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14476,7 +14458,7 @@
         <v>-1</v>
       </c>
       <c r="O70" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P70">
         <v>0</v>
@@ -14634,7 +14616,7 @@
         <v>216</v>
       </c>
       <c r="F71" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -14661,7 +14643,7 @@
         <v>-1</v>
       </c>
       <c r="O71" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -14810,7 +14792,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14819,7 +14801,7 @@
         <v>217</v>
       </c>
       <c r="F72" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -14846,7 +14828,7 @@
         <v>-1</v>
       </c>
       <c r="O72" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -15004,7 +14986,7 @@
         <v>218</v>
       </c>
       <c r="F73" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -15031,7 +15013,7 @@
         <v>-1</v>
       </c>
       <c r="O73" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P73">
         <v>0</v>
@@ -15189,7 +15171,7 @@
         <v>219</v>
       </c>
       <c r="F74" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -15216,7 +15198,7 @@
         <v>-1</v>
       </c>
       <c r="O74" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P74">
         <v>0</v>
@@ -15365,7 +15347,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15374,7 +15356,7 @@
         <v>220</v>
       </c>
       <c r="F75" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -15401,7 +15383,7 @@
         <v>-1</v>
       </c>
       <c r="O75" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P75">
         <v>0</v>
@@ -15559,7 +15541,7 @@
         <v>221</v>
       </c>
       <c r="F76" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -15586,7 +15568,7 @@
         <v>-1</v>
       </c>
       <c r="O76" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P76">
         <v>0</v>
@@ -15735,7 +15717,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15744,7 +15726,7 @@
         <v>222</v>
       </c>
       <c r="F77" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -15771,7 +15753,7 @@
         <v>-1</v>
       </c>
       <c r="O77" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P77">
         <v>0</v>
@@ -15929,7 +15911,7 @@
         <v>223</v>
       </c>
       <c r="F78" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -15956,7 +15938,7 @@
         <v>-1</v>
       </c>
       <c r="O78" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P78">
         <v>0</v>
@@ -16114,7 +16096,7 @@
         <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -16141,7 +16123,7 @@
         <v>-1</v>
       </c>
       <c r="O79" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P79">
         <v>0</v>
@@ -16290,7 +16272,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16299,7 +16281,7 @@
         <v>225</v>
       </c>
       <c r="F80" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -16326,16 +16308,16 @@
         <v>-1</v>
       </c>
       <c r="O80" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P80">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16380,10 +16362,10 @@
         <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH80">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI80">
         <v>0</v>
@@ -16475,7 +16457,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16484,7 +16466,7 @@
         <v>226</v>
       </c>
       <c r="F81" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -16511,16 +16493,16 @@
         <v>-1</v>
       </c>
       <c r="O81" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16565,10 +16547,10 @@
         <v>0</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI81">
         <v>0</v>
@@ -16669,7 +16651,7 @@
         <v>227</v>
       </c>
       <c r="F82" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -16696,7 +16678,7 @@
         <v>-1</v>
       </c>
       <c r="O82" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P82">
         <v>0</v>
@@ -16854,7 +16836,7 @@
         <v>228</v>
       </c>
       <c r="F83" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -16881,7 +16863,7 @@
         <v>-1</v>
       </c>
       <c r="O83" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P83">
         <v>0</v>
@@ -17030,16 +17012,16 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
       </c>
       <c r="F84" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -17066,7 +17048,7 @@
         <v>-1</v>
       </c>
       <c r="O84" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P84">
         <v>0</v>
@@ -17215,7 +17197,7 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D85" t="s">
         <v>146</v>
@@ -17224,7 +17206,7 @@
         <v>230</v>
       </c>
       <c r="F85" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -17251,7 +17233,7 @@
         <v>-1</v>
       </c>
       <c r="O85" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P85">
         <v>0</v>
@@ -17400,7 +17382,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D86" t="s">
         <v>145</v>
@@ -17409,7 +17391,7 @@
         <v>231</v>
       </c>
       <c r="F86" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -17436,7 +17418,7 @@
         <v>-1</v>
       </c>
       <c r="O86" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -17585,7 +17567,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17594,7 +17576,7 @@
         <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -17621,7 +17603,7 @@
         <v>-1</v>
       </c>
       <c r="O87" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P87">
         <v>0</v>
@@ -17770,7 +17752,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17779,7 +17761,7 @@
         <v>233</v>
       </c>
       <c r="F88" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -17806,7 +17788,7 @@
         <v>-1</v>
       </c>
       <c r="O88" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P88">
         <v>0</v>
@@ -17955,7 +17937,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
         <v>145</v>
@@ -17964,7 +17946,7 @@
         <v>234</v>
       </c>
       <c r="F89" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -17991,16 +17973,16 @@
         <v>-1</v>
       </c>
       <c r="O89" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18140,16 +18122,16 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
       </c>
       <c r="F90" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -18176,16 +18158,16 @@
         <v>-1</v>
       </c>
       <c r="O90" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P90">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18325,7 +18307,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18334,7 +18316,7 @@
         <v>236</v>
       </c>
       <c r="F91" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -18361,7 +18343,7 @@
         <v>-1</v>
       </c>
       <c r="O91" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P91">
         <v>0</v>
@@ -18519,7 +18501,7 @@
         <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -18546,7 +18528,7 @@
         <v>-1</v>
       </c>
       <c r="O92" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P92">
         <v>0</v>
@@ -18695,7 +18677,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18704,7 +18686,7 @@
         <v>238</v>
       </c>
       <c r="F93" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -18731,7 +18713,7 @@
         <v>-1</v>
       </c>
       <c r="O93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -18889,7 +18871,7 @@
         <v>239</v>
       </c>
       <c r="F94" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -18916,7 +18898,7 @@
         <v>-1</v>
       </c>
       <c r="O94" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -19074,7 +19056,7 @@
         <v>240</v>
       </c>
       <c r="F95" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -19101,7 +19083,7 @@
         <v>-1</v>
       </c>
       <c r="O95" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -19250,16 +19232,16 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -19286,7 +19268,7 @@
         <v>-1</v>
       </c>
       <c r="O96" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -19435,16 +19417,16 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
       </c>
       <c r="F97" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -19471,7 +19453,7 @@
         <v>-1</v>
       </c>
       <c r="O97" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P97">
         <v>0</v>
@@ -19620,7 +19602,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19629,7 +19611,7 @@
         <v>243</v>
       </c>
       <c r="F98" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -19656,7 +19638,7 @@
         <v>-1</v>
       </c>
       <c r="O98" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -19805,7 +19787,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19814,7 +19796,7 @@
         <v>244</v>
       </c>
       <c r="F99" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -19841,7 +19823,7 @@
         <v>-1</v>
       </c>
       <c r="O99" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -19990,7 +19972,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -19999,7 +19981,7 @@
         <v>245</v>
       </c>
       <c r="F100" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -20026,7 +20008,7 @@
         <v>-1</v>
       </c>
       <c r="O100" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -20175,7 +20157,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20184,7 +20166,7 @@
         <v>246</v>
       </c>
       <c r="F101" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -20211,7 +20193,7 @@
         <v>-1</v>
       </c>
       <c r="O101" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -20360,7 +20342,7 @@
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D102" t="s">
         <v>145</v>
@@ -20369,7 +20351,7 @@
         <v>247</v>
       </c>
       <c r="F102" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -20396,7 +20378,7 @@
         <v>-1</v>
       </c>
       <c r="O102" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -20554,7 +20536,7 @@
         <v>248</v>
       </c>
       <c r="F103" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -20581,7 +20563,7 @@
         <v>-1</v>
       </c>
       <c r="O103" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -20739,7 +20721,7 @@
         <v>249</v>
       </c>
       <c r="F104" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -20766,7 +20748,7 @@
         <v>-1</v>
       </c>
       <c r="O104" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P104">
         <v>0</v>
@@ -20924,7 +20906,7 @@
         <v>250</v>
       </c>
       <c r="F105" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -20951,7 +20933,7 @@
         <v>-1</v>
       </c>
       <c r="O105" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -21109,7 +21091,7 @@
         <v>251</v>
       </c>
       <c r="F106" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -21136,7 +21118,7 @@
         <v>-1</v>
       </c>
       <c r="O106" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -21285,16 +21267,16 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E107" t="s">
         <v>252</v>
       </c>
       <c r="F107" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -21321,7 +21303,7 @@
         <v>-1</v>
       </c>
       <c r="O107" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P107">
         <v>0</v>
@@ -21479,7 +21461,7 @@
         <v>253</v>
       </c>
       <c r="F108" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -21506,7 +21488,7 @@
         <v>-1</v>
       </c>
       <c r="O108" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -21655,16 +21637,16 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
       </c>
       <c r="F109" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -21691,7 +21673,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21840,16 +21822,16 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
       </c>
       <c r="F110" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -21876,7 +21858,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -22025,7 +22007,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22034,7 +22016,7 @@
         <v>256</v>
       </c>
       <c r="F111" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -22061,7 +22043,7 @@
         <v>-1</v>
       </c>
       <c r="O111" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -22210,16 +22192,16 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
       </c>
       <c r="F112" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -22246,7 +22228,7 @@
         <v>-1</v>
       </c>
       <c r="O112" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -22395,16 +22377,16 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
       </c>
       <c r="F113" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -22431,7 +22413,7 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -22580,16 +22562,16 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
       </c>
       <c r="F114" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -22616,7 +22598,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22774,7 +22756,7 @@
         <v>260</v>
       </c>
       <c r="F115" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -22801,7 +22783,7 @@
         <v>-1</v>
       </c>
       <c r="O115" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -22950,16 +22932,16 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
       </c>
       <c r="F116" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -22986,7 +22968,7 @@
         <v>-1</v>
       </c>
       <c r="O116" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -23135,16 +23117,16 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
       </c>
       <c r="F117" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -23171,7 +23153,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23320,7 +23302,7 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
         <v>145</v>
@@ -23329,7 +23311,7 @@
         <v>263</v>
       </c>
       <c r="F118" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -23356,7 +23338,7 @@
         <v>-1</v>
       </c>
       <c r="O118" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -23505,16 +23487,16 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
       </c>
       <c r="F119" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -23541,7 +23523,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23690,16 +23672,16 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
       </c>
       <c r="F120" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -23726,7 +23708,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23875,16 +23857,16 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
       </c>
       <c r="F121" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -23911,7 +23893,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24060,16 +24042,16 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
       </c>
       <c r="F122" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -24096,7 +24078,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24245,7 +24227,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24254,7 +24236,7 @@
         <v>268</v>
       </c>
       <c r="F123" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -24281,7 +24263,7 @@
         <v>-1</v>
       </c>
       <c r="O123" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -24439,7 +24421,7 @@
         <v>269</v>
       </c>
       <c r="F124" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -24466,7 +24448,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24624,7 +24606,7 @@
         <v>270</v>
       </c>
       <c r="F125" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -24651,7 +24633,7 @@
         <v>-1</v>
       </c>
       <c r="O125" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P125">
         <v>0</v>
@@ -24800,7 +24782,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D126" t="s">
         <v>145</v>
@@ -24809,7 +24791,7 @@
         <v>271</v>
       </c>
       <c r="F126" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -24836,7 +24818,7 @@
         <v>-1</v>
       </c>
       <c r="O126" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -24985,16 +24967,16 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
       </c>
       <c r="F127" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -25021,7 +25003,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25170,7 +25152,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D128" t="s">
         <v>146</v>
@@ -25179,7 +25161,7 @@
         <v>273</v>
       </c>
       <c r="F128" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -25206,7 +25188,7 @@
         <v>-1</v>
       </c>
       <c r="O128" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -25355,16 +25337,16 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
       </c>
       <c r="F129" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -25391,7 +25373,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -25540,7 +25522,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25549,7 +25531,7 @@
         <v>275</v>
       </c>
       <c r="F130" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -25576,7 +25558,7 @@
         <v>-1</v>
       </c>
       <c r="O130" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -25725,16 +25707,16 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
       </c>
       <c r="F131" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -25761,7 +25743,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25910,16 +25892,16 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
       </c>
       <c r="F132" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -25946,7 +25928,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26095,16 +26077,16 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
       </c>
       <c r="F133" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -26131,7 +26113,7 @@
         <v>-1</v>
       </c>
       <c r="O133" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -26280,16 +26262,16 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
       </c>
       <c r="F134" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -26316,7 +26298,7 @@
         <v>-1</v>
       </c>
       <c r="O134" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -26465,7 +26447,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26474,7 +26456,7 @@
         <v>280</v>
       </c>
       <c r="F135" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -26501,7 +26483,7 @@
         <v>-1</v>
       </c>
       <c r="O135" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -26650,7 +26632,7 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D136" t="s">
         <v>146</v>
@@ -26659,34 +26641,34 @@
         <v>281</v>
       </c>
       <c r="F136" t="s">
+        <v>418</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>-1</v>
+      </c>
+      <c r="N136">
+        <v>-1</v>
+      </c>
+      <c r="O136" t="s">
         <v>421</v>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>-1</v>
-      </c>
-      <c r="N136">
-        <v>-1</v>
-      </c>
-      <c r="O136" t="s">
-        <v>427</v>
       </c>
       <c r="P136">
         <v>0</v>
@@ -26835,7 +26817,7 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D137" t="s">
         <v>145</v>
@@ -26844,7 +26826,7 @@
         <v>282</v>
       </c>
       <c r="F137" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -26871,7 +26853,7 @@
         <v>-1</v>
       </c>
       <c r="O137" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P137">
         <v>0</v>
@@ -27017,19 +26999,19 @@
         <v>46150</v>
       </c>
       <c r="B138" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C138" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>
       </c>
       <c r="F138" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -27056,7 +27038,7 @@
         <v>-1</v>
       </c>
       <c r="O138" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P138">
         <v>0</v>
@@ -27194,561 +27176,6 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="139" spans="1:61">
-      <c r="A139" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B139" t="s">
-        <v>88</v>
-      </c>
-      <c r="C139" t="s">
-        <v>140</v>
-      </c>
-      <c r="D139" t="s">
-        <v>146</v>
-      </c>
-      <c r="E139" t="s">
-        <v>284</v>
-      </c>
-      <c r="F139" t="s">
-        <v>424</v>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>-1</v>
-      </c>
-      <c r="N139">
-        <v>-1</v>
-      </c>
-      <c r="O139" t="s">
-        <v>427</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139">
-        <v>0</v>
-      </c>
-      <c r="AI139">
-        <v>0</v>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>0</v>
-      </c>
-      <c r="AN139">
-        <v>0</v>
-      </c>
-      <c r="AO139">
-        <v>0</v>
-      </c>
-      <c r="AP139">
-        <v>0</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139">
-        <v>0</v>
-      </c>
-      <c r="AV139">
-        <v>0</v>
-      </c>
-      <c r="AW139">
-        <v>0</v>
-      </c>
-      <c r="AX139">
-        <v>0</v>
-      </c>
-      <c r="AY139">
-        <v>0</v>
-      </c>
-      <c r="AZ139">
-        <v>0</v>
-      </c>
-      <c r="BA139">
-        <v>0</v>
-      </c>
-      <c r="BB139">
-        <v>0</v>
-      </c>
-      <c r="BC139">
-        <v>0</v>
-      </c>
-      <c r="BD139">
-        <v>0</v>
-      </c>
-      <c r="BE139">
-        <v>0</v>
-      </c>
-      <c r="BF139">
-        <v>0</v>
-      </c>
-      <c r="BG139">
-        <v>0</v>
-      </c>
-      <c r="BH139">
-        <v>0</v>
-      </c>
-      <c r="BI139" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="140" spans="1:61">
-      <c r="A140" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B140" t="s">
-        <v>88</v>
-      </c>
-      <c r="C140" t="s">
-        <v>140</v>
-      </c>
-      <c r="D140" t="s">
-        <v>146</v>
-      </c>
-      <c r="E140" t="s">
-        <v>285</v>
-      </c>
-      <c r="F140" t="s">
-        <v>425</v>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>-1</v>
-      </c>
-      <c r="N140">
-        <v>-1</v>
-      </c>
-      <c r="O140" t="s">
-        <v>427</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140">
-        <v>0</v>
-      </c>
-      <c r="AI140">
-        <v>0</v>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>0</v>
-      </c>
-      <c r="AN140">
-        <v>0</v>
-      </c>
-      <c r="AO140">
-        <v>0</v>
-      </c>
-      <c r="AP140">
-        <v>0</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140">
-        <v>0</v>
-      </c>
-      <c r="AV140">
-        <v>0</v>
-      </c>
-      <c r="AW140">
-        <v>0</v>
-      </c>
-      <c r="AX140">
-        <v>0</v>
-      </c>
-      <c r="AY140">
-        <v>0</v>
-      </c>
-      <c r="AZ140">
-        <v>0</v>
-      </c>
-      <c r="BA140">
-        <v>0</v>
-      </c>
-      <c r="BB140">
-        <v>0</v>
-      </c>
-      <c r="BC140">
-        <v>0</v>
-      </c>
-      <c r="BD140">
-        <v>0</v>
-      </c>
-      <c r="BE140">
-        <v>0</v>
-      </c>
-      <c r="BF140">
-        <v>0</v>
-      </c>
-      <c r="BG140">
-        <v>0</v>
-      </c>
-      <c r="BH140">
-        <v>0</v>
-      </c>
-      <c r="BI140" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="141" spans="1:61">
-      <c r="A141" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B141" t="s">
-        <v>89</v>
-      </c>
-      <c r="C141" t="s">
-        <v>138</v>
-      </c>
-      <c r="D141" t="s">
-        <v>146</v>
-      </c>
-      <c r="E141" t="s">
-        <v>286</v>
-      </c>
-      <c r="F141" t="s">
-        <v>426</v>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>-1</v>
-      </c>
-      <c r="N141">
-        <v>-1</v>
-      </c>
-      <c r="O141" t="s">
-        <v>427</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141">
-        <v>0</v>
-      </c>
-      <c r="AI141">
-        <v>0</v>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>0</v>
-      </c>
-      <c r="AN141">
-        <v>0</v>
-      </c>
-      <c r="AO141">
-        <v>0</v>
-      </c>
-      <c r="AP141">
-        <v>0</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141">
-        <v>0</v>
-      </c>
-      <c r="AV141">
-        <v>0</v>
-      </c>
-      <c r="AW141">
-        <v>0</v>
-      </c>
-      <c r="AX141">
-        <v>0</v>
-      </c>
-      <c r="AY141">
-        <v>0</v>
-      </c>
-      <c r="AZ141">
-        <v>0</v>
-      </c>
-      <c r="BA141">
-        <v>0</v>
-      </c>
-      <c r="BB141">
-        <v>0</v>
-      </c>
-      <c r="BC141">
-        <v>0</v>
-      </c>
-      <c r="BD141">
-        <v>0</v>
-      </c>
-      <c r="BE141">
-        <v>0</v>
-      </c>
-      <c r="BF141">
-        <v>0</v>
-      </c>
-      <c r="BG141">
-        <v>0</v>
-      </c>
-      <c r="BH141">
-        <v>0</v>
-      </c>
-      <c r="BI141" s="3">
         <v>46150.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,66 +310,66 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -403,27 +403,27 @@
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -490,120 +490,120 @@
     <t>Petrojet</t>
   </si>
   <si>
+    <t>BFC Daugavpils</t>
+  </si>
+  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>BFC Daugavpils</t>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
   </si>
   <si>
     <t>Fakel</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
   </si>
   <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
     <t>HamKam</t>
   </si>
   <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
@@ -619,10 +619,22 @@
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>PSV W</t>
+  </si>
+  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>PSV W</t>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
   </si>
   <si>
     <t>Excelsior Barendrecht W</t>
@@ -631,97 +643,91 @@
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
     <t>Rijeka</t>
   </si>
   <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
     <t>Wil</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
     <t>Virtus Entella</t>
   </si>
   <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
     <t>Catanzaro</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Torino</t>
   </si>
   <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Standard Liège</t>
   </si>
   <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
@@ -730,33 +736,27 @@
     <t>Wexford</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
+    <t>Levante UD</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Levante UD</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>Fram</t>
   </si>
   <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -772,99 +772,99 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
     <t>Orlando Pride</t>
   </si>
   <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Maringá</t>
   </si>
   <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -901,120 +901,120 @@
     <t>Wadi Degla</t>
   </si>
   <si>
+    <t>Riga</t>
+  </si>
+  <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Riga</t>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
   </si>
   <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
     <t>Austria Wien II</t>
   </si>
   <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
     <t>Lyn W</t>
   </si>
   <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
     <t>Haugesund W</t>
   </si>
   <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
@@ -1030,10 +1030,22 @@
     <t>Thór</t>
   </si>
   <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>AZ W</t>
   </si>
   <si>
     <t>Feyenoord W</t>
@@ -1042,97 +1054,91 @@
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
+    <t>Bellinzona</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
     <t>Vaduz</t>
   </si>
   <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
     <t>Carrarese</t>
   </si>
   <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
     <t>Bari 1908</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>OH Leuven</t>
   </si>
   <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
+    <t>Bohemians</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
@@ -1141,33 +1147,27 @@
     <t>Longford Town</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Kerry</t>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
+    <t>Waterford</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>CA Osasuna</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Valur</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>Keflavík</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1183,97 +1183,97 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>North Carolina Courage</t>
   </si>
   <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Almagro</t>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Guarani</t>
   </si>
   <si>
     <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3880,7 +3880,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4065,7 +4065,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4435,7 +4435,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -4620,7 +4620,7 @@
         <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -5357,10 +5357,10 @@
         <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>166</v>
@@ -5542,10 +5542,10 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5730,7 +5730,7 @@
         <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5766,13 +5766,13 @@
         <v>421</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5912,10 +5912,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6097,10 +6097,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6282,7 +6282,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6467,10 +6467,10 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
@@ -6652,10 +6652,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6837,10 +6837,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7022,7 +7022,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -7207,7 +7207,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -7392,10 +7392,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7577,10 +7577,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7762,10 +7762,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7947,10 +7947,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8132,7 +8132,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -8317,7 +8317,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8502,7 +8502,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -9096,13 +9096,13 @@
         <v>421</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9281,13 +9281,13 @@
         <v>421</v>
       </c>
       <c r="P42">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9427,10 +9427,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9466,13 +9466,13 @@
         <v>421</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9612,10 +9612,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9651,13 +9651,13 @@
         <v>421</v>
       </c>
       <c r="P44">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9797,7 +9797,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9982,7 +9982,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
         <v>146</v>
@@ -10167,7 +10167,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10537,10 +10537,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10576,13 +10576,13 @@
         <v>421</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10722,10 +10722,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -10761,13 +10761,13 @@
         <v>421</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11277,7 +11277,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11832,7 +11832,7 @@
         <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D56" t="s">
         <v>145</v>
@@ -12017,7 +12017,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12387,7 +12387,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -13127,7 +13127,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13906,13 +13906,13 @@
         <v>421</v>
       </c>
       <c r="P67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13957,10 +13957,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14091,13 +14091,13 @@
         <v>421</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14142,10 +14142,10 @@
         <v>0</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI68">
         <v>0</v>
@@ -14461,13 +14461,13 @@
         <v>421</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14506,10 +14506,10 @@
         <v>0</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG70">
         <v>0</v>
@@ -14646,13 +14646,13 @@
         <v>421</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14691,10 +14691,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14792,7 +14792,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14831,13 +14831,13 @@
         <v>421</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14876,10 +14876,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14977,7 +14977,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15016,13 +15016,13 @@
         <v>421</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15201,13 +15201,13 @@
         <v>421</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15386,13 +15386,13 @@
         <v>421</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15431,10 +15431,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15571,13 +15571,13 @@
         <v>421</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15616,10 +15616,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15717,7 +15717,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15756,13 +15756,13 @@
         <v>421</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15941,13 +15941,13 @@
         <v>421</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15986,10 +15986,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16126,13 +16126,13 @@
         <v>421</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16171,10 +16171,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16272,7 +16272,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16311,13 +16311,13 @@
         <v>421</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16681,13 +16681,13 @@
         <v>421</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16726,10 +16726,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17382,10 +17382,10 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E86" t="s">
         <v>231</v>
@@ -17567,7 +17567,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17752,10 +17752,10 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -18122,7 +18122,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18862,7 +18862,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19232,7 +19232,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
         <v>146</v>
@@ -20897,7 +20897,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21267,7 +21267,7 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
         <v>146</v>
@@ -21452,7 +21452,7 @@
         <v>88</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D108" t="s">
         <v>145</v>
@@ -21640,7 +21640,7 @@
         <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21673,7 +21673,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21822,7 +21822,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -22192,7 +22192,7 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D112" t="s">
         <v>146</v>
@@ -22377,10 +22377,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22562,7 +22562,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22747,10 +22747,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -22932,7 +22932,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -23117,7 +23117,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23302,10 +23302,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23487,10 +23487,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23672,7 +23672,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D120" t="s">
         <v>146</v>
@@ -23857,7 +23857,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24042,7 +24042,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D122" t="s">
         <v>145</v>
@@ -24078,7 +24078,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24230,7 +24230,7 @@
         <v>142</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24412,7 +24412,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -24597,7 +24597,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24782,10 +24782,10 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24967,7 +24967,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D127" t="s">
         <v>145</v>
@@ -25152,10 +25152,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25337,7 +25337,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -25522,7 +25522,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25707,7 +25707,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -25892,7 +25892,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -26077,10 +26077,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26262,7 +26262,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D134" t="s">
         <v>145</v>
@@ -26447,7 +26447,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26632,7 +26632,7 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D136" t="s">
         <v>146</v>
@@ -26820,7 +26820,7 @@
         <v>139</v>
       </c>
       <c r="D137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="425">
   <si>
     <t>Date</t>
   </si>
@@ -310,10 +310,13 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Russia FNL</t>
   </si>
   <si>
     <t>Serbia Prva Liga</t>
@@ -325,99 +328,96 @@
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
+    <t>Germany 3. Liga</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -436,21 +436,21 @@
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,16 +484,22 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
+    <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Chayka</t>
   </si>
   <si>
     <t>Kabel Novi Sad</t>
@@ -505,145 +511,148 @@
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Anorthosis</t>
   </si>
   <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Kapfenberger SV</t>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
   </si>
   <si>
     <t>Amstetten</t>
   </si>
   <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
   </si>
   <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Varberg</t>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
   </si>
   <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Durban City</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
     <t>PSV W</t>
   </si>
   <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
     <t>PEC Zwolle W</t>
   </si>
   <si>
-    <t>Ajax W</t>
+    <t>Olympique Dcheïra</t>
   </si>
   <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Rapperswil-Jona</t>
@@ -655,102 +664,96 @@
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Étoile Carouge</t>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
   </si>
   <si>
     <t>Südtirol</t>
   </si>
   <si>
-    <t>Cesena</t>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Avellino</t>
   </si>
   <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
     <t>Virtus Entella</t>
   </si>
   <si>
     <t>Venezia</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
     <t>Monza</t>
   </si>
   <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Torino</t>
   </si>
   <si>
-    <t>Drogheda United</t>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
     <t>Wexford</t>
   </si>
   <si>
     <t>Levante UD</t>
   </si>
   <si>
+    <t>Wisła Kraków</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
+    <t>Fram</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -763,108 +766,108 @@
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
     <t>Voždovac</t>
   </si>
   <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
   </si>
   <si>
     <t>Željezničar</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -895,16 +898,22 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
+    <t>Arda</t>
   </si>
   <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Arda</t>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
     <t>Trajal Krusevac</t>
@@ -916,145 +925,148 @@
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
     <t>Liepāja</t>
   </si>
   <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Digenis Ypsonas</t>
   </si>
   <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>St. Pölten</t>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
   </si>
   <si>
     <t>Austria Klagenfurt</t>
   </si>
   <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
     <t>Austria Wien II</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
     <t>Admira</t>
   </si>
   <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
   </si>
   <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Värnamo</t>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
     <t>Thór</t>
   </si>
   <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
     <t>HERA</t>
   </si>
   <si>
-    <t>AZ W</t>
+    <t>Yacoub El Mansour</t>
   </si>
   <si>
     <t>Feyenoord W</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
@@ -1066,102 +1078,96 @@
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Stade Nyonnais</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
   </si>
   <si>
     <t>Juve Stabia</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Modena</t>
   </si>
   <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
     <t>Carrarese</t>
   </si>
   <si>
     <t>Palermo</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
     <t>Empoli</t>
   </si>
   <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
     <t>Sassuolo</t>
   </si>
   <si>
-    <t>Derry City</t>
+    <t>Kerry</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
     <t>Longford Town</t>
   </si>
   <si>
     <t>CA Osasuna</t>
   </si>
   <si>
+    <t>Chrobry Głogów</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
+    <t>Valur</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
@@ -1174,106 +1180,106 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Anápolis</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
     <t>OFK Vršac</t>
   </si>
   <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -1646,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI138"/>
+  <dimension ref="A1:BI139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1851,7 +1857,7 @@
         <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1878,7 +1884,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2036,7 +2042,7 @@
         <v>148</v>
       </c>
       <c r="F3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2063,7 +2069,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2221,7 +2227,7 @@
         <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2248,7 +2254,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2406,7 +2412,7 @@
         <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2433,7 +2439,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2591,7 +2597,7 @@
         <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2618,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2776,7 +2782,7 @@
         <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2803,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2961,7 +2967,7 @@
         <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2988,7 +2994,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3146,7 +3152,7 @@
         <v>154</v>
       </c>
       <c r="F9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3173,7 +3179,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3331,7 +3337,7 @@
         <v>155</v>
       </c>
       <c r="F10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3358,7 +3364,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3516,7 +3522,7 @@
         <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3543,7 +3549,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3701,7 +3707,7 @@
         <v>157</v>
       </c>
       <c r="F12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3728,7 +3734,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3880,13 +3886,13 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3913,7 +3919,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4065,13 +4071,13 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4098,7 +4104,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4256,7 +4262,7 @@
         <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -4283,7 +4289,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4432,16 +4438,16 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
       </c>
       <c r="F16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4468,7 +4474,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4617,7 +4623,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>145</v>
@@ -4626,7 +4632,7 @@
         <v>162</v>
       </c>
       <c r="F17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4653,7 +4659,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4802,16 +4808,16 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4838,7 +4844,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4984,10 +4990,10 @@
         <v>46150</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4996,7 +5002,7 @@
         <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -5023,7 +5029,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5161,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3">
-        <v>46150.52083333334</v>
+        <v>46150.5</v>
       </c>
     </row>
     <row r="20" spans="1:61">
@@ -5169,10 +5175,10 @@
         <v>46150</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>145</v>
@@ -5181,7 +5187,7 @@
         <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -5208,7 +5214,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5346,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3">
-        <v>46150.53125</v>
+        <v>46150.52083333334</v>
       </c>
     </row>
     <row r="21" spans="1:61">
@@ -5354,19 +5360,19 @@
         <v>46150</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
         <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -5393,7 +5399,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5531,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3">
-        <v>46150.54166666666</v>
+        <v>46150.53125</v>
       </c>
     </row>
     <row r="22" spans="1:61">
@@ -5545,13 +5551,13 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
       </c>
       <c r="F22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5578,7 +5584,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5727,16 +5733,16 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
       </c>
       <c r="F23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5763,16 +5769,16 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P23">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5912,16 +5918,16 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
       </c>
       <c r="F24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5948,7 +5954,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -6097,7 +6103,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6106,7 +6112,7 @@
         <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -6133,7 +6139,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -6291,7 +6297,7 @@
         <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6318,7 +6324,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -6467,7 +6473,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -6476,7 +6482,7 @@
         <v>172</v>
       </c>
       <c r="F27" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6503,7 +6509,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6652,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
         <v>146</v>
@@ -6661,7 +6667,7 @@
         <v>173</v>
       </c>
       <c r="F28" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6688,7 +6694,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6837,7 +6843,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -6846,7 +6852,7 @@
         <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6873,16 +6879,16 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7031,7 +7037,7 @@
         <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7058,7 +7064,7 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -7207,7 +7213,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -7216,7 +7222,7 @@
         <v>176</v>
       </c>
       <c r="F31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7243,7 +7249,7 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -7392,16 +7398,16 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
       </c>
       <c r="F32" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7428,7 +7434,7 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -7577,16 +7583,16 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
       </c>
       <c r="F33" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7613,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7762,16 +7768,16 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
       </c>
       <c r="F34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7798,7 +7804,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7947,7 +7953,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -7956,7 +7962,7 @@
         <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7983,7 +7989,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -8132,7 +8138,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -8141,7 +8147,7 @@
         <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -8168,7 +8174,7 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -8317,7 +8323,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8326,7 +8332,7 @@
         <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -8353,7 +8359,7 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -8502,16 +8508,16 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
       </c>
       <c r="F38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -8538,7 +8544,7 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -8684,10 +8690,10 @@
         <v>46150</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8696,7 +8702,7 @@
         <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8723,7 +8729,7 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -8861,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3">
-        <v>46150.5625</v>
+        <v>46150.54166666666</v>
       </c>
     </row>
     <row r="40" spans="1:61">
@@ -8881,7 +8887,7 @@
         <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8908,7 +8914,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -9054,10 +9060,10 @@
         <v>46150</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
         <v>145</v>
@@ -9066,7 +9072,7 @@
         <v>186</v>
       </c>
       <c r="F41" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -9093,16 +9099,16 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P41">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9231,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3">
-        <v>46150.58333333334</v>
+        <v>46150.5625</v>
       </c>
     </row>
     <row r="42" spans="1:61">
@@ -9242,7 +9248,7 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
         <v>146</v>
@@ -9251,7 +9257,7 @@
         <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -9278,7 +9284,7 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -9427,16 +9433,16 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
       </c>
       <c r="F43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -9463,16 +9469,16 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P43">
+        <v>3.03</v>
+      </c>
+      <c r="Q43">
         <v>3.15</v>
       </c>
-      <c r="Q43">
-        <v>3.76</v>
-      </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9612,16 +9618,16 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -9648,16 +9654,16 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9797,7 +9803,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9806,7 +9812,7 @@
         <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9833,7 +9839,7 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -9982,7 +9988,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
         <v>146</v>
@@ -9991,7 +9997,7 @@
         <v>191</v>
       </c>
       <c r="F46" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -10018,7 +10024,7 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -10167,7 +10173,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10176,7 +10182,7 @@
         <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -10203,16 +10209,16 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10361,7 +10367,7 @@
         <v>193</v>
       </c>
       <c r="F48" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -10388,7 +10394,7 @@
         <v>-1</v>
       </c>
       <c r="O48" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -10537,16 +10543,16 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
       </c>
       <c r="F49" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -10573,16 +10579,16 @@
         <v>-1</v>
       </c>
       <c r="O49" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P49">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10722,7 +10728,7 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -10731,7 +10737,7 @@
         <v>195</v>
       </c>
       <c r="F50" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -10758,16 +10764,16 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P50">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10904,19 +10910,19 @@
         <v>46150</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
       </c>
       <c r="F51" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -10943,16 +10949,16 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11081,7 +11087,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3">
-        <v>46150.60416666666</v>
+        <v>46150.58333333334</v>
       </c>
     </row>
     <row r="52" spans="1:61">
@@ -11092,16 +11098,16 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
       </c>
       <c r="F52" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -11128,7 +11134,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11277,7 +11283,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11286,7 +11292,7 @@
         <v>198</v>
       </c>
       <c r="F53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -11313,7 +11319,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11462,16 +11468,16 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
       </c>
       <c r="F54" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -11498,7 +11504,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11647,16 +11653,16 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
       </c>
       <c r="F55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -11683,7 +11689,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11829,19 +11835,19 @@
         <v>46150</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -11868,7 +11874,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12006,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3">
-        <v>46150.625</v>
+        <v>46150.60416666666</v>
       </c>
     </row>
     <row r="57" spans="1:61">
@@ -12017,7 +12023,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12026,7 +12032,7 @@
         <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -12053,7 +12059,7 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -12211,7 +12217,7 @@
         <v>203</v>
       </c>
       <c r="F58" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -12238,7 +12244,7 @@
         <v>-1</v>
       </c>
       <c r="O58" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -12396,7 +12402,7 @@
         <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12423,7 +12429,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12572,7 +12578,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12581,7 +12587,7 @@
         <v>205</v>
       </c>
       <c r="F60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12608,7 +12614,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12757,7 +12763,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12766,7 +12772,7 @@
         <v>206</v>
       </c>
       <c r="F61" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12793,7 +12799,7 @@
         <v>-1</v>
       </c>
       <c r="O61" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -12951,7 +12957,7 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12978,7 +12984,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -13127,7 +13133,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13136,7 +13142,7 @@
         <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -13163,7 +13169,7 @@
         <v>-1</v>
       </c>
       <c r="O63" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -13321,7 +13327,7 @@
         <v>209</v>
       </c>
       <c r="F64" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -13348,7 +13354,7 @@
         <v>-1</v>
       </c>
       <c r="O64" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -13494,10 +13500,10 @@
         <v>46150</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13506,7 +13512,7 @@
         <v>210</v>
       </c>
       <c r="F65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13533,7 +13539,7 @@
         <v>-1</v>
       </c>
       <c r="O65" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -13671,7 +13677,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3">
-        <v>46150.63541666666</v>
+        <v>46150.625</v>
       </c>
     </row>
     <row r="66" spans="1:61">
@@ -13691,7 +13697,7 @@
         <v>211</v>
       </c>
       <c r="F66" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13718,16 +13724,16 @@
         <v>-1</v>
       </c>
       <c r="O66" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13772,10 +13778,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -13876,7 +13882,7 @@
         <v>212</v>
       </c>
       <c r="F67" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13903,7 +13909,7 @@
         <v>-1</v>
       </c>
       <c r="O67" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -14061,7 +14067,7 @@
         <v>213</v>
       </c>
       <c r="F68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -14088,16 +14094,16 @@
         <v>-1</v>
       </c>
       <c r="O68" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P68">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14142,10 +14148,10 @@
         <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH68">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI68">
         <v>0</v>
@@ -14246,7 +14252,7 @@
         <v>214</v>
       </c>
       <c r="F69" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14273,7 +14279,7 @@
         <v>-1</v>
       </c>
       <c r="O69" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -14419,10 +14425,10 @@
         <v>46150</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D70" t="s">
         <v>145</v>
@@ -14431,7 +14437,7 @@
         <v>215</v>
       </c>
       <c r="F70" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14458,16 +14464,16 @@
         <v>-1</v>
       </c>
       <c r="O70" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P70">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14506,10 +14512,10 @@
         <v>0</v>
       </c>
       <c r="AE70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG70">
         <v>0</v>
@@ -14596,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3">
-        <v>46150.64583333334</v>
+        <v>46150.63541666666</v>
       </c>
     </row>
     <row r="71" spans="1:61">
@@ -14607,7 +14613,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14616,7 +14622,7 @@
         <v>216</v>
       </c>
       <c r="F71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -14643,16 +14649,16 @@
         <v>-1</v>
       </c>
       <c r="O71" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P71">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="Q71">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="R71">
-        <v>4.3</v>
+        <v>6.14</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14691,10 +14697,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14801,7 +14807,7 @@
         <v>217</v>
       </c>
       <c r="F72" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -14828,16 +14834,16 @@
         <v>-1</v>
       </c>
       <c r="O72" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P72">
-        <v>3.41</v>
+        <v>1.76</v>
       </c>
       <c r="Q72">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="R72">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14876,10 +14882,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AF72">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14986,7 +14992,7 @@
         <v>218</v>
       </c>
       <c r="F73" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -15013,16 +15019,16 @@
         <v>-1</v>
       </c>
       <c r="O73" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P73">
-        <v>3.57</v>
+        <v>1.57</v>
       </c>
       <c r="Q73">
-        <v>3.42</v>
+        <v>5.03</v>
       </c>
       <c r="R73">
-        <v>2.13</v>
+        <v>5.63</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15067,10 +15073,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15171,7 +15177,7 @@
         <v>219</v>
       </c>
       <c r="F74" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -15198,16 +15204,16 @@
         <v>-1</v>
       </c>
       <c r="O74" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P74">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="Q74">
-        <v>4.5</v>
+        <v>3.38</v>
       </c>
       <c r="R74">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15246,10 +15252,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15356,7 +15362,7 @@
         <v>220</v>
       </c>
       <c r="F75" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -15383,16 +15389,16 @@
         <v>-1</v>
       </c>
       <c r="O75" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P75">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="Q75">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15431,10 +15437,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15541,7 +15547,7 @@
         <v>221</v>
       </c>
       <c r="F76" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -15568,16 +15574,16 @@
         <v>-1</v>
       </c>
       <c r="O76" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P76">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="Q76">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="R76">
-        <v>4.08</v>
+        <v>3.05</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15616,10 +15622,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF76">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15717,7 +15723,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15726,7 +15732,7 @@
         <v>222</v>
       </c>
       <c r="F77" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -15753,16 +15759,16 @@
         <v>-1</v>
       </c>
       <c r="O77" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P77">
-        <v>2.18</v>
+        <v>3.57</v>
       </c>
       <c r="Q77">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="R77">
-        <v>3.05</v>
+        <v>2.13</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15801,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15911,7 +15917,7 @@
         <v>223</v>
       </c>
       <c r="F78" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -15938,16 +15944,16 @@
         <v>-1</v>
       </c>
       <c r="O78" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P78">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="Q78">
-        <v>4.3</v>
+        <v>3.78</v>
       </c>
       <c r="R78">
-        <v>6.11</v>
+        <v>4.22</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15986,10 +15992,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16096,7 +16102,7 @@
         <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -16123,7 +16129,7 @@
         <v>-1</v>
       </c>
       <c r="O79" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P79">
         <v>2.3</v>
@@ -16272,7 +16278,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16281,7 +16287,7 @@
         <v>225</v>
       </c>
       <c r="F80" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -16308,16 +16314,16 @@
         <v>-1</v>
       </c>
       <c r="O80" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P80">
-        <v>1.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q80">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="R80">
-        <v>6.14</v>
+        <v>2.16</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16356,10 +16362,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16457,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16466,7 +16472,7 @@
         <v>226</v>
       </c>
       <c r="F81" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -16493,16 +16499,16 @@
         <v>-1</v>
       </c>
       <c r="O81" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P81">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="Q81">
-        <v>5.03</v>
+        <v>3.18</v>
       </c>
       <c r="R81">
-        <v>5.63</v>
+        <v>4</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16541,16 +16547,16 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH81">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI81">
         <v>0</v>
@@ -16651,7 +16657,7 @@
         <v>227</v>
       </c>
       <c r="F82" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -16678,16 +16684,16 @@
         <v>-1</v>
       </c>
       <c r="O82" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P82">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q82">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="R82">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16726,10 +16732,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF82">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16824,19 +16830,19 @@
         <v>46150</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E83" t="s">
         <v>228</v>
       </c>
       <c r="F83" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -16863,16 +16869,16 @@
         <v>-1</v>
       </c>
       <c r="O83" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16911,10 +16917,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17001,7 +17007,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3">
-        <v>46150.65625</v>
+        <v>46150.64583333334</v>
       </c>
     </row>
     <row r="84" spans="1:61">
@@ -17012,7 +17018,7 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D84" t="s">
         <v>145</v>
@@ -17021,7 +17027,7 @@
         <v>229</v>
       </c>
       <c r="F84" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -17048,16 +17054,16 @@
         <v>-1</v>
       </c>
       <c r="O84" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17197,7 +17203,7 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D85" t="s">
         <v>146</v>
@@ -17206,7 +17212,7 @@
         <v>230</v>
       </c>
       <c r="F85" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -17233,7 +17239,7 @@
         <v>-1</v>
       </c>
       <c r="O85" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P85">
         <v>0</v>
@@ -17382,7 +17388,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17391,7 +17397,7 @@
         <v>231</v>
       </c>
       <c r="F86" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -17418,7 +17424,7 @@
         <v>-1</v>
       </c>
       <c r="O86" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -17576,7 +17582,7 @@
         <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -17603,7 +17609,7 @@
         <v>-1</v>
       </c>
       <c r="O87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P87">
         <v>0</v>
@@ -17761,7 +17767,7 @@
         <v>233</v>
       </c>
       <c r="F88" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -17788,7 +17794,7 @@
         <v>-1</v>
       </c>
       <c r="O88" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P88">
         <v>0</v>
@@ -17937,16 +17943,16 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
       </c>
       <c r="F89" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -17973,16 +17979,16 @@
         <v>-1</v>
       </c>
       <c r="O89" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P89">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18122,7 +18128,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18131,7 +18137,7 @@
         <v>235</v>
       </c>
       <c r="F90" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -18158,7 +18164,7 @@
         <v>-1</v>
       </c>
       <c r="O90" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P90">
         <v>0</v>
@@ -18316,7 +18322,7 @@
         <v>236</v>
       </c>
       <c r="F91" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -18343,7 +18349,7 @@
         <v>-1</v>
       </c>
       <c r="O91" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P91">
         <v>0</v>
@@ -18492,16 +18498,16 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -18528,7 +18534,7 @@
         <v>-1</v>
       </c>
       <c r="O92" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P92">
         <v>0</v>
@@ -18677,7 +18683,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18686,7 +18692,7 @@
         <v>238</v>
       </c>
       <c r="F93" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -18713,7 +18719,7 @@
         <v>-1</v>
       </c>
       <c r="O93" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -18862,7 +18868,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -18871,7 +18877,7 @@
         <v>239</v>
       </c>
       <c r="F94" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -18898,7 +18904,7 @@
         <v>-1</v>
       </c>
       <c r="O94" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -19044,19 +19050,19 @@
         <v>46150</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
       </c>
       <c r="F95" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -19083,7 +19089,7 @@
         <v>-1</v>
       </c>
       <c r="O95" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -19221,7 +19227,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3">
-        <v>46150.66666666666</v>
+        <v>46150.65625</v>
       </c>
     </row>
     <row r="96" spans="1:61">
@@ -19232,16 +19238,16 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -19268,7 +19274,7 @@
         <v>-1</v>
       </c>
       <c r="O96" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -19426,7 +19432,7 @@
         <v>242</v>
       </c>
       <c r="F97" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -19453,7 +19459,7 @@
         <v>-1</v>
       </c>
       <c r="O97" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P97">
         <v>0</v>
@@ -19599,10 +19605,10 @@
         <v>46150</v>
       </c>
       <c r="B98" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19611,7 +19617,7 @@
         <v>243</v>
       </c>
       <c r="F98" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -19638,7 +19644,7 @@
         <v>-1</v>
       </c>
       <c r="O98" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -19776,7 +19782,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3">
-        <v>46150.67708333334</v>
+        <v>46150.66666666666</v>
       </c>
     </row>
     <row r="99" spans="1:61">
@@ -19796,7 +19802,7 @@
         <v>244</v>
       </c>
       <c r="F99" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -19823,7 +19829,7 @@
         <v>-1</v>
       </c>
       <c r="O99" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -19981,7 +19987,7 @@
         <v>245</v>
       </c>
       <c r="F100" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -20008,7 +20014,7 @@
         <v>-1</v>
       </c>
       <c r="O100" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -20166,7 +20172,7 @@
         <v>246</v>
       </c>
       <c r="F101" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -20193,7 +20199,7 @@
         <v>-1</v>
       </c>
       <c r="O101" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -20339,19 +20345,19 @@
         <v>46150</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D102" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E102" t="s">
         <v>247</v>
       </c>
       <c r="F102" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -20378,7 +20384,7 @@
         <v>-1</v>
       </c>
       <c r="O102" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -20516,7 +20522,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3">
-        <v>46150.70833333334</v>
+        <v>46150.67708333334</v>
       </c>
     </row>
     <row r="103" spans="1:61">
@@ -20524,19 +20530,19 @@
         <v>46150</v>
       </c>
       <c r="B103" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D103" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E103" t="s">
         <v>248</v>
       </c>
       <c r="F103" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -20563,7 +20569,7 @@
         <v>-1</v>
       </c>
       <c r="O103" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -20701,7 +20707,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3">
-        <v>46150.8125</v>
+        <v>46150.70833333334</v>
       </c>
     </row>
     <row r="104" spans="1:61">
@@ -20709,10 +20715,10 @@
         <v>46150</v>
       </c>
       <c r="B104" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D104" t="s">
         <v>146</v>
@@ -20721,7 +20727,7 @@
         <v>249</v>
       </c>
       <c r="F104" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -20748,7 +20754,7 @@
         <v>-1</v>
       </c>
       <c r="O104" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P104">
         <v>0</v>
@@ -20886,7 +20892,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3">
-        <v>46150.83333333334</v>
+        <v>46150.8125</v>
       </c>
     </row>
     <row r="105" spans="1:61">
@@ -20897,7 +20903,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -20906,7 +20912,7 @@
         <v>250</v>
       </c>
       <c r="F105" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -20933,7 +20939,7 @@
         <v>-1</v>
       </c>
       <c r="O105" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -21079,10 +21085,10 @@
         <v>46150</v>
       </c>
       <c r="B106" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21091,7 +21097,7 @@
         <v>251</v>
       </c>
       <c r="F106" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -21118,7 +21124,7 @@
         <v>-1</v>
       </c>
       <c r="O106" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -21256,7 +21262,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3">
-        <v>46150.85416666666</v>
+        <v>46150.83333333334</v>
       </c>
     </row>
     <row r="107" spans="1:61">
@@ -21264,10 +21270,10 @@
         <v>46150</v>
       </c>
       <c r="B107" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D107" t="s">
         <v>146</v>
@@ -21276,7 +21282,7 @@
         <v>252</v>
       </c>
       <c r="F107" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -21303,7 +21309,7 @@
         <v>-1</v>
       </c>
       <c r="O107" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P107">
         <v>0</v>
@@ -21441,7 +21447,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3">
-        <v>46150.875</v>
+        <v>46150.85416666666</v>
       </c>
     </row>
     <row r="108" spans="1:61">
@@ -21452,16 +21458,16 @@
         <v>88</v>
       </c>
       <c r="C108" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
       </c>
       <c r="F108" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -21488,7 +21494,7 @@
         <v>-1</v>
       </c>
       <c r="O108" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -21637,16 +21643,16 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
       </c>
       <c r="F109" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -21673,7 +21679,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21831,7 +21837,7 @@
         <v>255</v>
       </c>
       <c r="F110" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -21858,7 +21864,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -22007,7 +22013,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22016,7 +22022,7 @@
         <v>256</v>
       </c>
       <c r="F111" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -22043,7 +22049,7 @@
         <v>-1</v>
       </c>
       <c r="O111" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -22201,7 +22207,7 @@
         <v>257</v>
       </c>
       <c r="F112" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -22228,7 +22234,7 @@
         <v>-1</v>
       </c>
       <c r="O112" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -22377,16 +22383,16 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
       </c>
       <c r="F113" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -22413,7 +22419,7 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -22562,7 +22568,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22571,7 +22577,7 @@
         <v>259</v>
       </c>
       <c r="F114" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -22598,7 +22604,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22747,16 +22753,16 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
       </c>
       <c r="F115" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -22783,7 +22789,7 @@
         <v>-1</v>
       </c>
       <c r="O115" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -22932,7 +22938,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -22941,7 +22947,7 @@
         <v>261</v>
       </c>
       <c r="F116" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -22968,7 +22974,7 @@
         <v>-1</v>
       </c>
       <c r="O116" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -23117,7 +23123,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23126,7 +23132,7 @@
         <v>262</v>
       </c>
       <c r="F117" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -23153,7 +23159,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23302,16 +23308,16 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
       </c>
       <c r="F118" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -23338,7 +23344,7 @@
         <v>-1</v>
       </c>
       <c r="O118" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -23487,7 +23493,7 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
         <v>146</v>
@@ -23496,7 +23502,7 @@
         <v>264</v>
       </c>
       <c r="F119" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -23523,7 +23529,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23672,7 +23678,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
         <v>146</v>
@@ -23681,7 +23687,7 @@
         <v>265</v>
       </c>
       <c r="F120" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -23708,7 +23714,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23857,7 +23863,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -23866,7 +23872,7 @@
         <v>266</v>
       </c>
       <c r="F121" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -23893,7 +23899,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24042,16 +24048,16 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
       </c>
       <c r="F122" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -24078,7 +24084,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24227,16 +24233,16 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
       </c>
       <c r="F123" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -24263,7 +24269,7 @@
         <v>-1</v>
       </c>
       <c r="O123" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -24412,7 +24418,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -24421,7 +24427,7 @@
         <v>269</v>
       </c>
       <c r="F124" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -24448,7 +24454,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24597,7 +24603,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24606,7 +24612,7 @@
         <v>270</v>
       </c>
       <c r="F125" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -24633,7 +24639,7 @@
         <v>-1</v>
       </c>
       <c r="O125" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P125">
         <v>0</v>
@@ -24782,7 +24788,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D126" t="s">
         <v>146</v>
@@ -24791,7 +24797,7 @@
         <v>271</v>
       </c>
       <c r="F126" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -24818,7 +24824,7 @@
         <v>-1</v>
       </c>
       <c r="O126" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -24967,7 +24973,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
         <v>145</v>
@@ -24976,7 +24982,7 @@
         <v>272</v>
       </c>
       <c r="F127" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -25003,7 +25009,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25152,7 +25158,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -25161,7 +25167,7 @@
         <v>273</v>
       </c>
       <c r="F128" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -25188,7 +25194,7 @@
         <v>-1</v>
       </c>
       <c r="O128" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -25337,7 +25343,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -25346,7 +25352,7 @@
         <v>274</v>
       </c>
       <c r="F129" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -25373,7 +25379,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -25522,16 +25528,16 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130" t="s">
         <v>275</v>
       </c>
       <c r="F130" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -25558,7 +25564,7 @@
         <v>-1</v>
       </c>
       <c r="O130" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -25707,7 +25713,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -25716,7 +25722,7 @@
         <v>276</v>
       </c>
       <c r="F131" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -25743,7 +25749,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25892,7 +25898,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -25901,7 +25907,7 @@
         <v>277</v>
       </c>
       <c r="F132" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -25928,7 +25934,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26077,16 +26083,16 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
       </c>
       <c r="F133" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -26113,7 +26119,7 @@
         <v>-1</v>
       </c>
       <c r="O133" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -26262,7 +26268,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="D134" t="s">
         <v>145</v>
@@ -26271,7 +26277,7 @@
         <v>279</v>
       </c>
       <c r="F134" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -26298,7 +26304,7 @@
         <v>-1</v>
       </c>
       <c r="O134" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -26447,7 +26453,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26456,7 +26462,7 @@
         <v>280</v>
       </c>
       <c r="F135" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -26483,7 +26489,7 @@
         <v>-1</v>
       </c>
       <c r="O135" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -26632,16 +26638,16 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D136" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
       </c>
       <c r="F136" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -26668,7 +26674,7 @@
         <v>-1</v>
       </c>
       <c r="O136" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P136">
         <v>0</v>
@@ -26817,16 +26823,16 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
       </c>
       <c r="F137" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -26853,7 +26859,7 @@
         <v>-1</v>
       </c>
       <c r="O137" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P137">
         <v>0</v>
@@ -26999,19 +27005,19 @@
         <v>46150</v>
       </c>
       <c r="B138" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D138" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>
       </c>
       <c r="F138" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -27038,7 +27044,7 @@
         <v>-1</v>
       </c>
       <c r="O138" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P138">
         <v>0</v>
@@ -27176,6 +27182,191 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3">
+        <v>46150.875</v>
+      </c>
+    </row>
+    <row r="139" spans="1:61">
+      <c r="A139" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B139" t="s">
+        <v>89</v>
+      </c>
+      <c r="C139" t="s">
+        <v>138</v>
+      </c>
+      <c r="D139" t="s">
+        <v>146</v>
+      </c>
+      <c r="E139" t="s">
+        <v>284</v>
+      </c>
+      <c r="F139" t="s">
+        <v>422</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>-1</v>
+      </c>
+      <c r="N139">
+        <v>-1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>423</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139">
+        <v>0</v>
+      </c>
+      <c r="AI139">
+        <v>0</v>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>0</v>
+      </c>
+      <c r="AN139">
+        <v>0</v>
+      </c>
+      <c r="AO139">
+        <v>0</v>
+      </c>
+      <c r="AP139">
+        <v>0</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139">
+        <v>0</v>
+      </c>
+      <c r="AV139">
+        <v>0</v>
+      </c>
+      <c r="AW139">
+        <v>0</v>
+      </c>
+      <c r="AX139">
+        <v>0</v>
+      </c>
+      <c r="AY139">
+        <v>0</v>
+      </c>
+      <c r="AZ139">
+        <v>0</v>
+      </c>
+      <c r="BA139">
+        <v>0</v>
+      </c>
+      <c r="BB139">
+        <v>0</v>
+      </c>
+      <c r="BC139">
+        <v>0</v>
+      </c>
+      <c r="BD139">
+        <v>0</v>
+      </c>
+      <c r="BE139">
+        <v>0</v>
+      </c>
+      <c r="BF139">
+        <v>0</v>
+      </c>
+      <c r="BG139">
+        <v>0</v>
+      </c>
+      <c r="BH139">
+        <v>0</v>
+      </c>
+      <c r="BI139" s="3">
         <v>46150.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,10 +310,16 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Russia FNL</t>
@@ -322,19 +328,19 @@
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
@@ -343,43 +349,40 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
+    <t>Norway First Division</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
+    <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
     <t>France National</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Netherlands Eredivisie Women</t>
@@ -388,36 +391,33 @@
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -439,15 +439,15 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
@@ -475,151 +475,160 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
+    <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>BFC Daugavpils</t>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Chayka</t>
   </si>
   <si>
     <t>Fakel</t>
   </si>
   <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>Molde W</t>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
   </si>
   <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
     <t>Anorthosis</t>
   </si>
   <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Liefering</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Örebro</t>
   </si>
   <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
     <t>Coca-Cola</t>
   </si>
   <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Víkingur Reykjavík</t>
   </si>
   <si>
     <t>Villefranche</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
+    <t>Durban City</t>
   </si>
   <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
   </si>
   <si>
     <t>Ajax W</t>
@@ -628,7 +637,10 @@
     <t>Utrecht W</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
   </si>
   <si>
     <t>CFR Cluj</t>
@@ -637,24 +649,12 @@
     <t>Rijeka</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
@@ -664,52 +664,73 @@
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
     <t>Monza</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>Lens</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Shelbourne</t>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Cork City</t>
@@ -718,27 +739,6 @@
     <t>Standard Liège</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Levante UD</t>
   </si>
   <si>
@@ -751,12 +751,12 @@
     <t>Fram</t>
   </si>
   <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>ÍA</t>
   </si>
   <si>
@@ -766,84 +766,84 @@
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
     <t>Orlando Pride</t>
   </si>
   <si>
     <t>Loznica</t>
   </si>
   <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
     <t>Posusje</t>
   </si>
   <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
     <t>Jedinstvo Ub</t>
   </si>
   <si>
@@ -889,151 +889,160 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
+    <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Riga</t>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Røa Women</t>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
   </si>
   <si>
     <t>Liepāja</t>
   </si>
   <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
     <t>Digenis Ypsonas</t>
   </si>
   <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Admira</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Thór</t>
   </si>
   <si>
     <t>Ajaccio</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Thór</t>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
   </si>
   <si>
     <t>AZ W</t>
@@ -1042,7 +1051,10 @@
     <t>Heerenveen W</t>
   </si>
   <si>
-    <t>Twente W</t>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>HERA</t>
   </si>
   <si>
     <t>CS U Craiova</t>
@@ -1051,24 +1063,12 @@
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
@@ -1078,52 +1078,73 @@
     <t>Bellinzona</t>
   </si>
   <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
     <t>Empoli</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>Nantes</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
   </si>
   <si>
     <t>UCD</t>
@@ -1132,27 +1153,6 @@
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
     <t>CA Osasuna</t>
   </si>
   <si>
@@ -1165,12 +1165,12 @@
     <t>Valur</t>
   </si>
   <si>
+    <t>FH</t>
+  </si>
+  <si>
     <t>KR</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>Keflavík</t>
   </si>
   <si>
@@ -1180,82 +1180,82 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>North Carolina Courage</t>
   </si>
   <si>
     <t>Mačva Šabac</t>
   </si>
   <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Sarajevo</t>
   </si>
   <si>
     <t>Velež</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
   </si>
   <si>
     <t>Zemun</t>
@@ -3886,7 +3886,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4071,7 +4071,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4256,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4438,7 +4438,7 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>145</v>
@@ -4623,7 +4623,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>145</v>
@@ -4811,7 +4811,7 @@
         <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -5551,7 +5551,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5733,10 +5733,10 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5918,10 +5918,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6103,7 +6103,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6291,7 +6291,7 @@
         <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -6476,7 +6476,7 @@
         <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
@@ -6658,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>146</v>
@@ -6843,7 +6843,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -6882,13 +6882,13 @@
         <v>423</v>
       </c>
       <c r="P29">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7028,10 +7028,10 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -7213,10 +7213,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7398,10 +7398,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7583,7 +7583,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7768,10 +7768,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7953,7 +7953,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -8138,10 +8138,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8323,7 +8323,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8508,7 +8508,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
         <v>145</v>
@@ -8547,13 +8547,13 @@
         <v>423</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -9433,10 +9433,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9472,13 +9472,13 @@
         <v>423</v>
       </c>
       <c r="P43">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9618,10 +9618,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9657,13 +9657,13 @@
         <v>423</v>
       </c>
       <c r="P44">
-        <v>2.94</v>
+        <v>1.77</v>
       </c>
       <c r="Q44">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="R44">
-        <v>2.32</v>
+        <v>3.96</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9803,7 +9803,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9842,13 +9842,13 @@
         <v>423</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -10173,10 +10173,10 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -10212,13 +10212,13 @@
         <v>423</v>
       </c>
       <c r="P47">
-        <v>1.77</v>
+        <v>3.15</v>
       </c>
       <c r="Q47">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R47">
-        <v>3.96</v>
+        <v>2.04</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10358,7 +10358,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10543,7 +10543,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
         <v>145</v>
@@ -10582,13 +10582,13 @@
         <v>423</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -10913,10 +10913,10 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -10952,13 +10952,13 @@
         <v>423</v>
       </c>
       <c r="P51">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11098,7 +11098,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11134,7 +11134,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11283,10 +11283,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11471,7 +11471,7 @@
         <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11504,7 +11504,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12393,7 +12393,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12578,7 +12578,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12948,7 +12948,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13133,7 +13133,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13318,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13503,7 +13503,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13727,13 +13727,13 @@
         <v>423</v>
       </c>
       <c r="P66">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13778,10 +13778,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH66">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -13912,13 +13912,13 @@
         <v>423</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13963,10 +13963,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14613,7 +14613,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14652,13 +14652,13 @@
         <v>423</v>
       </c>
       <c r="P71">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q71">
-        <v>4.35</v>
+        <v>5.03</v>
       </c>
       <c r="R71">
-        <v>6.14</v>
+        <v>5.63</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14703,10 +14703,10 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14798,7 +14798,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14983,7 +14983,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15022,13 +15022,13 @@
         <v>423</v>
       </c>
       <c r="P73">
-        <v>1.57</v>
+        <v>3.57</v>
       </c>
       <c r="Q73">
-        <v>5.03</v>
+        <v>3.42</v>
       </c>
       <c r="R73">
-        <v>5.63</v>
+        <v>2.13</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15073,10 +15073,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH73">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15168,7 +15168,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15353,7 +15353,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15392,13 +15392,13 @@
         <v>423</v>
       </c>
       <c r="P75">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q75">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>4.08</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15437,10 +15437,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15538,7 +15538,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15577,13 +15577,13 @@
         <v>423</v>
       </c>
       <c r="P76">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="Q76">
-        <v>3.56</v>
+        <v>3.18</v>
       </c>
       <c r="R76">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15622,10 +15622,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF76">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15723,7 +15723,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15762,13 +15762,13 @@
         <v>423</v>
       </c>
       <c r="P77">
-        <v>3.57</v>
+        <v>2.18</v>
       </c>
       <c r="Q77">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="R77">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15947,13 +15947,13 @@
         <v>423</v>
       </c>
       <c r="P78">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>3.78</v>
+        <v>3.16</v>
       </c>
       <c r="R78">
-        <v>4.22</v>
+        <v>3.16</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15992,10 +15992,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF78">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16093,7 +16093,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16132,13 +16132,13 @@
         <v>423</v>
       </c>
       <c r="P79">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="Q79">
-        <v>3.16</v>
+        <v>4.5</v>
       </c>
       <c r="R79">
-        <v>3.16</v>
+        <v>5</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16177,10 +16177,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16278,7 +16278,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16463,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16502,13 +16502,13 @@
         <v>423</v>
       </c>
       <c r="P81">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="Q81">
-        <v>3.18</v>
+        <v>3.78</v>
       </c>
       <c r="R81">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16547,10 +16547,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AF81">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16648,7 +16648,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16687,13 +16687,13 @@
         <v>423</v>
       </c>
       <c r="P82">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q82">
-        <v>3.84</v>
+        <v>4.35</v>
       </c>
       <c r="R82">
-        <v>4.08</v>
+        <v>6.14</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16732,10 +16732,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16833,7 +16833,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -17021,7 +17021,7 @@
         <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
@@ -17057,13 +17057,13 @@
         <v>423</v>
       </c>
       <c r="P84">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17206,7 +17206,7 @@
         <v>130</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17242,13 +17242,13 @@
         <v>423</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17758,10 +17758,10 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -17943,7 +17943,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18128,7 +18128,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18313,7 +18313,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18498,7 +18498,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
         <v>145</v>
@@ -19053,10 +19053,10 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
@@ -19608,7 +19608,7 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19793,7 +19793,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19978,7 +19978,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20163,7 +20163,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20348,7 +20348,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20533,7 +20533,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20903,7 +20903,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21088,7 +21088,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -22013,7 +22013,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -23123,7 +23123,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23308,10 +23308,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23344,7 +23344,7 @@
         <v>-1</v>
       </c>
       <c r="O118" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -23678,7 +23678,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D120" t="s">
         <v>146</v>
@@ -23863,7 +23863,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24048,7 +24048,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D122" t="s">
         <v>146</v>
@@ -24418,10 +24418,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24454,7 +24454,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24973,7 +24973,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D127" t="s">
         <v>145</v>
@@ -25158,7 +25158,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -25528,7 +25528,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -25713,7 +25713,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -25898,7 +25898,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -26083,7 +26083,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D133" t="s">
         <v>145</v>
@@ -26453,7 +26453,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26638,7 +26638,7 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D136" t="s">
         <v>145</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,48 +310,57 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -361,13 +370,10 @@
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
@@ -376,54 +382,48 @@
     <t>France National</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
+    <t>Netherlands Eredivisie Women</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Netherlands Eredivisie Women</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,13 +433,16 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
     <t>Chile Primera B</t>
@@ -448,9 +451,6 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,99 +484,120 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
+    <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
   </si>
   <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Amstetten</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
     <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Varberg</t>
   </si>
   <si>
@@ -586,67 +607,55 @@
     <t>Viborg</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
     <t>Villefranche</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
   </si>
   <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
@@ -655,111 +664,102 @@
     <t>Aarau</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
   </si>
   <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
-    <t>Cesena</t>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Cádiz</t>
   </si>
   <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
     <t>Pescara</t>
   </si>
   <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
+    <t>Monza</t>
   </si>
   <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Lens</t>
   </si>
   <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Standard Liège</t>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>Levante UD</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
+    <t>ÍA</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -775,99 +775,99 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
     <t>Inter de Limeira</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
     <t>Maranhão</t>
   </si>
   <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -898,99 +898,120 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
+    <t>Arda</t>
   </si>
   <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Arda</t>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
   </si>
   <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Austria Klagenfurt</t>
   </si>
   <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
     <t>Liepāja</t>
   </si>
   <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Värnamo</t>
   </si>
   <si>
@@ -1000,67 +1021,55 @@
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>Thór</t>
   </si>
   <si>
     <t>Ajaccio</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>HB</t>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
   </si>
   <si>
     <t>Vaduz</t>
@@ -1069,111 +1078,102 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
   </si>
   <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Deportivo La Coruña</t>
   </si>
   <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
     <t>Spezia</t>
   </si>
   <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Mantova</t>
+    <t>Empoli</t>
   </si>
   <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
     <t>Nantes</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
     <t>Bohemians</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>OH Leuven</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
     <t>Waterford</t>
   </si>
   <si>
+    <t>Keflavík</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1189,97 +1189,97 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Santa Cruz</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
     <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3886,7 +3886,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4071,7 +4071,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4256,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4623,7 +4623,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>145</v>
@@ -4996,7 +4996,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5736,7 +5736,7 @@
         <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5918,10 +5918,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6103,7 +6103,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6291,7 +6291,7 @@
         <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -6473,7 +6473,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6661,7 +6661,7 @@
         <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6843,10 +6843,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7028,7 +7028,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7213,7 +7213,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
         <v>146</v>
@@ -7398,7 +7398,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -7583,7 +7583,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7771,7 +7771,7 @@
         <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7953,10 +7953,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8138,7 +8138,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -8362,13 +8362,13 @@
         <v>423</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8547,13 +8547,13 @@
         <v>423</v>
       </c>
       <c r="P38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8693,10 +8693,10 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
         <v>184</v>
@@ -9287,13 +9287,13 @@
         <v>423</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9433,10 +9433,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9472,13 +9472,13 @@
         <v>423</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9618,7 +9618,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -9657,13 +9657,13 @@
         <v>423</v>
       </c>
       <c r="P44">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9803,10 +9803,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -9842,13 +9842,13 @@
         <v>423</v>
       </c>
       <c r="P45">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9988,10 +9988,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10173,7 +10173,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
         <v>146</v>
@@ -10212,13 +10212,13 @@
         <v>423</v>
       </c>
       <c r="P47">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="Q47">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="R47">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10543,10 +10543,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10582,13 +10582,13 @@
         <v>423</v>
       </c>
       <c r="P49">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10728,10 +10728,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -10913,7 +10913,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10952,13 +10952,13 @@
         <v>423</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11098,7 +11098,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11504,7 +11504,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11656,7 +11656,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11841,7 +11841,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11874,7 +11874,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12393,7 +12393,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12578,7 +12578,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12763,7 +12763,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12948,7 +12948,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13133,7 +13133,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13318,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13912,13 +13912,13 @@
         <v>423</v>
       </c>
       <c r="P67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13963,10 +13963,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14467,13 +14467,13 @@
         <v>423</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14518,10 +14518,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14652,13 +14652,13 @@
         <v>423</v>
       </c>
       <c r="P71">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q71">
-        <v>5.03</v>
+        <v>3.75</v>
       </c>
       <c r="R71">
-        <v>5.63</v>
+        <v>4.3</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14697,16 +14697,16 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH71">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14798,7 +14798,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14837,13 +14837,13 @@
         <v>423</v>
       </c>
       <c r="P72">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q72">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R72">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14882,10 +14882,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF72">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14983,7 +14983,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15022,13 +15022,13 @@
         <v>423</v>
       </c>
       <c r="P73">
-        <v>3.57</v>
+        <v>1.57</v>
       </c>
       <c r="Q73">
-        <v>3.42</v>
+        <v>5.03</v>
       </c>
       <c r="R73">
-        <v>2.13</v>
+        <v>5.63</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15073,10 +15073,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15168,7 +15168,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15207,13 +15207,13 @@
         <v>423</v>
       </c>
       <c r="P74">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Q74">
-        <v>3.38</v>
+        <v>3.16</v>
       </c>
       <c r="R74">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>2</v>
       </c>
       <c r="AF74">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15353,7 +15353,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15538,7 +15538,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15577,13 +15577,13 @@
         <v>423</v>
       </c>
       <c r="P76">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="Q76">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="R76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15622,10 +15622,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15723,7 +15723,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15762,13 +15762,13 @@
         <v>423</v>
       </c>
       <c r="P77">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="Q77">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="R77">
-        <v>3.05</v>
+        <v>4.22</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF77">
         <v>2.15</v>
@@ -15908,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15947,13 +15947,13 @@
         <v>423</v>
       </c>
       <c r="P78">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q78">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="R78">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15992,10 +15992,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF78">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16093,7 +16093,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16132,13 +16132,13 @@
         <v>423</v>
       </c>
       <c r="P79">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q79">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="R79">
-        <v>5</v>
+        <v>6.14</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16278,7 +16278,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16317,13 +16317,13 @@
         <v>423</v>
       </c>
       <c r="P80">
-        <v>3.41</v>
+        <v>3.57</v>
       </c>
       <c r="Q80">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R80">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16362,10 +16362,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16463,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16502,13 +16502,13 @@
         <v>423</v>
       </c>
       <c r="P81">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="Q81">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="R81">
-        <v>4.22</v>
+        <v>3.05</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16547,7 +16547,7 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF81">
         <v>2.15</v>
@@ -16648,7 +16648,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16687,13 +16687,13 @@
         <v>423</v>
       </c>
       <c r="P82">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q82">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="R82">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16732,10 +16732,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16833,7 +16833,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16872,13 +16872,13 @@
         <v>423</v>
       </c>
       <c r="P83">
-        <v>1.49</v>
+        <v>3.41</v>
       </c>
       <c r="Q83">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="R83">
-        <v>6.11</v>
+        <v>2.16</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16917,10 +16917,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AF83">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17242,13 +17242,13 @@
         <v>423</v>
       </c>
       <c r="P85">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17576,7 +17576,7 @@
         <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17758,7 +17758,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17943,7 +17943,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18128,10 +18128,10 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18167,13 +18167,13 @@
         <v>423</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18313,10 +18313,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18498,10 +18498,10 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
@@ -18683,7 +18683,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18868,7 +18868,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19053,10 +19053,10 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
@@ -19793,7 +19793,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19978,7 +19978,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20163,7 +20163,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20348,7 +20348,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20533,7 +20533,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -21088,7 +21088,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21643,7 +21643,7 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
         <v>146</v>
@@ -21828,10 +21828,10 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -22013,10 +22013,10 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D111" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22198,10 +22198,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22383,7 +22383,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D113" t="s">
         <v>146</v>
@@ -22568,7 +22568,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22753,7 +22753,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D115" t="s">
         <v>146</v>
@@ -22938,10 +22938,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23123,10 +23123,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23308,10 +23308,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23493,10 +23493,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23678,10 +23678,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23866,7 +23866,7 @@
         <v>142</v>
       </c>
       <c r="D121" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
@@ -24048,7 +24048,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D122" t="s">
         <v>146</v>
@@ -24233,7 +24233,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24418,7 +24418,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D124" t="s">
         <v>145</v>
@@ -24454,7 +24454,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24603,7 +24603,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24788,10 +24788,10 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24973,10 +24973,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25158,7 +25158,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -25343,10 +25343,10 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -25528,10 +25528,10 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130" t="s">
         <v>275</v>
@@ -25713,10 +25713,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25898,7 +25898,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -25934,7 +25934,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26083,10 +26083,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26268,10 +26268,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
@@ -26453,10 +26453,10 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E135" t="s">
         <v>280</v>
@@ -26638,10 +26638,10 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="D136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
@@ -26823,10 +26823,10 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
@@ -27008,10 +27008,10 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E138" t="s">
         <v>283</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,10 +310,16 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Serbia Prva Liga</t>
@@ -322,66 +328,60 @@
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>France National</t>
   </si>
   <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -397,18 +397,18 @@
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
+    <t>Republic of Ireland First Division</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,16 +484,22 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
+    <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>BFC Daugavpils</t>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
   </si>
   <si>
     <t>Kabel Novi Sad</t>
@@ -505,31 +511,58 @@
     <t>Chayka</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
     <t>Anorthosis</t>
   </si>
   <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Molde W</t>
   </si>
   <si>
     <t>Amstetten</t>
@@ -538,207 +571,174 @@
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
     <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
   </si>
   <si>
     <t>Ajax W</t>
   </si>
   <si>
-    <t>Utrecht W</t>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
   </si>
   <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Wil</t>
   </si>
   <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Aarau</t>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
   </si>
   <si>
     <t>Cesena</t>
   </si>
   <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
@@ -748,126 +748,126 @@
     <t>St Patrick's Athl.</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>ÍA</t>
   </si>
   <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
     <t>Orense SC</t>
   </si>
   <si>
-    <t>Atlético Rafaela</t>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
   </si>
   <si>
     <t>Voždovac</t>
   </si>
   <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -898,16 +898,22 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
+    <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Riga</t>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
   </si>
   <si>
     <t>Trajal Krusevac</t>
@@ -919,31 +925,58 @@
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
     <t>Digenis Ypsonas</t>
   </si>
   <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
   </si>
   <si>
     <t>Austria Klagenfurt</t>
@@ -952,207 +985,174 @@
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
   </si>
   <si>
     <t>AZ W</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>HERA</t>
   </si>
   <si>
     <t>CS U Craiova</t>
   </si>
   <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
   </si>
   <si>
     <t>Calcio Padova</t>
   </si>
   <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
@@ -1162,124 +1162,124 @@
     <t>Waterford</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
     <t>Keflavík</t>
   </si>
   <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>FH</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
     <t>Leones del Norte</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Zemun</t>
   </si>
   <si>
     <t>OFK Vršac</t>
   </si>
   <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
     <t>Rangers</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3886,7 +3886,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4071,7 +4071,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4441,7 +4441,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -4623,7 +4623,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>145</v>
@@ -4808,7 +4808,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4996,7 +4996,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5551,7 +5551,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5736,7 +5736,7 @@
         <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5772,13 +5772,13 @@
         <v>423</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
         <v>146</v>
@@ -6103,10 +6103,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6512,13 +6512,13 @@
         <v>423</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6557,10 +6557,10 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6843,10 +6843,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -6882,13 +6882,13 @@
         <v>423</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
         <v>146</v>
@@ -7398,10 +7398,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7583,7 +7583,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7768,10 +7768,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7992,13 +7992,13 @@
         <v>423</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8037,10 +8037,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8138,7 +8138,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -8323,10 +8323,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8362,13 +8362,13 @@
         <v>423</v>
       </c>
       <c r="P37">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8508,7 +8508,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
         <v>145</v>
@@ -8693,10 +8693,10 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
         <v>184</v>
@@ -9248,10 +9248,10 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
@@ -9287,13 +9287,13 @@
         <v>423</v>
       </c>
       <c r="P42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9433,10 +9433,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9472,13 +9472,13 @@
         <v>423</v>
       </c>
       <c r="P43">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9618,7 +9618,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -9657,13 +9657,13 @@
         <v>423</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9803,10 +9803,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -9988,10 +9988,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10173,10 +10173,10 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -10212,13 +10212,13 @@
         <v>423</v>
       </c>
       <c r="P47">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10397,13 +10397,13 @@
         <v>423</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10543,10 +10543,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10582,13 +10582,13 @@
         <v>423</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10767,13 +10767,13 @@
         <v>423</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10952,13 +10952,13 @@
         <v>423</v>
       </c>
       <c r="P51">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11098,7 +11098,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11286,7 +11286,7 @@
         <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11471,7 +11471,7 @@
         <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11656,7 +11656,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11689,7 +11689,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11841,7 +11841,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11874,7 +11874,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12393,7 +12393,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12763,7 +12763,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -13318,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13503,7 +13503,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13727,13 +13727,13 @@
         <v>423</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13778,10 +13778,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -14467,13 +14467,13 @@
         <v>423</v>
       </c>
       <c r="P70">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14518,10 +14518,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14652,13 +14652,13 @@
         <v>423</v>
       </c>
       <c r="P71">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="Q71">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R71">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14697,10 +14697,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14837,13 +14837,13 @@
         <v>423</v>
       </c>
       <c r="P72">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R72">
-        <v>3.58</v>
+        <v>4.08</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14882,10 +14882,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AF72">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -15022,13 +15022,13 @@
         <v>423</v>
       </c>
       <c r="P73">
-        <v>1.57</v>
+        <v>3.57</v>
       </c>
       <c r="Q73">
-        <v>5.03</v>
+        <v>3.42</v>
       </c>
       <c r="R73">
-        <v>5.63</v>
+        <v>2.13</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15073,10 +15073,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH73">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15207,13 +15207,13 @@
         <v>423</v>
       </c>
       <c r="P74">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q74">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="R74">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15252,10 +15252,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF74">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15353,7 +15353,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15392,13 +15392,13 @@
         <v>423</v>
       </c>
       <c r="P75">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Q75">
-        <v>3.84</v>
+        <v>5.03</v>
       </c>
       <c r="R75">
-        <v>4.08</v>
+        <v>5.63</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15437,16 +15437,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -15538,7 +15538,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15577,13 +15577,13 @@
         <v>423</v>
       </c>
       <c r="P76">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q76">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="R76">
-        <v>5</v>
+        <v>6.14</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15947,13 +15947,13 @@
         <v>423</v>
       </c>
       <c r="P78">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="R78">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15992,10 +15992,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF78">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16093,7 +16093,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16132,13 +16132,13 @@
         <v>423</v>
       </c>
       <c r="P79">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q79">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="R79">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16177,10 +16177,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16278,7 +16278,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16317,13 +16317,13 @@
         <v>423</v>
       </c>
       <c r="P80">
-        <v>3.57</v>
+        <v>2.18</v>
       </c>
       <c r="Q80">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="R80">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16362,10 +16362,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16502,13 +16502,13 @@
         <v>423</v>
       </c>
       <c r="P81">
-        <v>2.18</v>
+        <v>3.41</v>
       </c>
       <c r="Q81">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="R81">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16547,10 +16547,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
+        <v>2.15</v>
+      </c>
+      <c r="AF81">
         <v>1.61</v>
-      </c>
-      <c r="AF81">
-        <v>2.15</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16687,13 +16687,13 @@
         <v>423</v>
       </c>
       <c r="P82">
-        <v>1.49</v>
+        <v>2.03</v>
       </c>
       <c r="Q82">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="R82">
-        <v>6.11</v>
+        <v>3.58</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16732,10 +16732,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF82">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16872,13 +16872,13 @@
         <v>423</v>
       </c>
       <c r="P83">
-        <v>3.41</v>
+        <v>1.76</v>
       </c>
       <c r="Q83">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="R83">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16917,10 +16917,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AF83">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17203,7 +17203,7 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D85" t="s">
         <v>146</v>
@@ -17388,7 +17388,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17573,10 +17573,10 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -18128,10 +18128,10 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18167,13 +18167,13 @@
         <v>423</v>
       </c>
       <c r="P90">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18313,7 +18313,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
         <v>145</v>
@@ -18498,10 +18498,10 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
@@ -18537,13 +18537,13 @@
         <v>423</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19053,10 +19053,10 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
@@ -19092,13 +19092,13 @@
         <v>423</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19608,7 +19608,7 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
         <v>146</v>
@@ -19793,7 +19793,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19978,7 +19978,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20163,7 +20163,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20348,7 +20348,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20903,7 +20903,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21088,7 +21088,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21643,10 +21643,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21828,7 +21828,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D110" t="s">
         <v>145</v>
@@ -22013,10 +22013,10 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22198,10 +22198,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22383,10 +22383,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22568,7 +22568,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22753,7 +22753,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
         <v>146</v>
@@ -22938,7 +22938,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D116" t="s">
         <v>145</v>
@@ -23123,10 +23123,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23308,7 +23308,7 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D118" t="s">
         <v>145</v>
@@ -23493,10 +23493,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23678,7 +23678,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D120" t="s">
         <v>145</v>
@@ -23714,7 +23714,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23863,10 +23863,10 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
@@ -24048,10 +24048,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24233,7 +24233,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24418,10 +24418,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24603,10 +24603,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24788,10 +24788,10 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24973,10 +24973,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25158,10 +25158,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25343,7 +25343,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25528,7 +25528,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25713,7 +25713,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -25898,10 +25898,10 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -25934,7 +25934,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26083,10 +26083,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26268,7 +26268,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D134" t="s">
         <v>146</v>
@@ -26453,10 +26453,10 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D135" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E135" t="s">
         <v>280</v>
@@ -26638,10 +26638,10 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D136" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
@@ -26823,10 +26823,10 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
@@ -27008,7 +27008,7 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D138" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,30 +316,30 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -352,36 +352,36 @@
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -403,15 +403,15 @@
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>Terengganu</t>
+  </si>
+  <si>
     <t>PDRM</t>
   </si>
   <si>
-    <t>Terengganu</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Chayka</t>
   </si>
   <si>
@@ -517,94 +517,103 @@
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
     <t>Brann W</t>
   </si>
   <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
     <t>Amstetten</t>
   </si>
   <si>
-    <t>Rapid Wien II</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
   </si>
   <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Varberg</t>
   </si>
   <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
@@ -613,150 +622,141 @@
     <t>Durban City</t>
   </si>
   <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
+    <t>NAC Breda W</t>
   </si>
   <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>PSV W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
   </si>
   <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
+    <t>Pescara</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
     <t>Monza</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Cesena</t>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Torino</t>
   </si>
   <si>
     <t>Athlone Town</t>
   </si>
   <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
     <t>Levante UD</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
     <t>Fram</t>
   </si>
   <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -775,99 +775,99 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
     <t>Atlético Rafaela</t>
   </si>
   <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
     <t>Spartak Subotica</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Maringá</t>
+    <t>Široki Brijeg</t>
   </si>
   <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Loznica</t>
-  </si>
-  <si>
     <t>Orlando Pride</t>
   </si>
   <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -889,12 +889,12 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Imigresen</t>
+  </si>
+  <si>
     <t>Pulau Pinang</t>
   </si>
   <si>
-    <t>Imigresen</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -910,18 +910,18 @@
     <t>Arda</t>
   </si>
   <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
     <t>Csikszereda</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
@@ -931,94 +931,103 @@
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
     <t>Korona Kielce</t>
   </si>
   <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Haugesund W</t>
   </si>
   <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
     <t>Austria Klagenfurt</t>
   </si>
   <si>
-    <t>First Vienna</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Pharco</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Värnamo</t>
   </si>
   <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
@@ -1027,150 +1036,141 @@
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>HB</t>
+    <t>Twente W</t>
   </si>
   <si>
     <t>Feyenoord W</t>
   </si>
   <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Bellinzona</t>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
   </si>
   <si>
     <t>Mantova</t>
   </si>
   <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
+    <t>Spezia</t>
   </si>
   <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
     <t>Empoli</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
+    <t>Waterford</t>
+  </si>
+  <si>
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>Keflavík</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
@@ -1189,97 +1189,97 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
     <t>Napredak</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Guarani</t>
+    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Almagro</t>
   </si>
   <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
     <t>North Carolina Courage</t>
   </si>
   <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
     <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Rangers</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4441,7 +4441,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -4477,13 +4477,13 @@
         <v>423</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -4993,7 +4993,7 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -5551,7 +5551,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5587,13 +5587,13 @@
         <v>423</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5632,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -5733,7 +5733,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5772,13 +5772,13 @@
         <v>423</v>
       </c>
       <c r="P23">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5921,7 +5921,7 @@
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6106,7 +6106,7 @@
         <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6142,13 +6142,13 @@
         <v>423</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6187,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -6288,10 +6288,10 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -6473,10 +6473,10 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
@@ -6512,13 +6512,13 @@
         <v>423</v>
       </c>
       <c r="P27">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6557,10 +6557,10 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6697,13 +6697,13 @@
         <v>423</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6843,10 +6843,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -6882,13 +6882,13 @@
         <v>423</v>
       </c>
       <c r="P29">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7028,7 +7028,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7213,10 +7213,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7398,10 +7398,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7583,10 +7583,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7768,7 +7768,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7953,10 +7953,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -7992,13 +7992,13 @@
         <v>423</v>
       </c>
       <c r="P35">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8037,10 +8037,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8138,7 +8138,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -8326,7 +8326,7 @@
         <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8362,13 +8362,13 @@
         <v>423</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -8693,7 +8693,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -9248,10 +9248,10 @@
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
@@ -9287,13 +9287,13 @@
         <v>423</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9433,10 +9433,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9618,7 +9618,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -9657,13 +9657,13 @@
         <v>423</v>
       </c>
       <c r="P44">
-        <v>1.77</v>
+        <v>3.03</v>
       </c>
       <c r="Q44">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R44">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9988,10 +9988,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10543,10 +10543,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10582,13 +10582,13 @@
         <v>423</v>
       </c>
       <c r="P49">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10767,13 +10767,13 @@
         <v>423</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10952,13 +10952,13 @@
         <v>423</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11098,10 +11098,10 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
@@ -11283,7 +11283,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11319,7 +11319,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11468,7 +11468,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
         <v>146</v>
@@ -11653,7 +11653,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D55" t="s">
         <v>145</v>
@@ -11689,7 +11689,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11841,7 +11841,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -12208,7 +12208,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12393,7 +12393,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12432,13 +12432,13 @@
         <v>423</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -12763,7 +12763,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -13318,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13503,7 +13503,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13727,13 +13727,13 @@
         <v>423</v>
       </c>
       <c r="P66">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13778,10 +13778,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH66">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -14282,13 +14282,13 @@
         <v>423</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14333,10 +14333,10 @@
         <v>0</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI69">
         <v>0</v>
@@ -14652,13 +14652,13 @@
         <v>423</v>
       </c>
       <c r="P71">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="R71">
-        <v>5</v>
+        <v>3.16</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14697,10 +14697,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14798,7 +14798,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14837,13 +14837,13 @@
         <v>423</v>
       </c>
       <c r="P72">
-        <v>1.78</v>
+        <v>3.57</v>
       </c>
       <c r="Q72">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="R72">
-        <v>4.08</v>
+        <v>2.13</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14882,10 +14882,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14983,7 +14983,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15022,13 +15022,13 @@
         <v>423</v>
       </c>
       <c r="P73">
-        <v>3.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q73">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R73">
-        <v>2.13</v>
+        <v>4.3</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15067,10 +15067,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15207,13 +15207,13 @@
         <v>423</v>
       </c>
       <c r="P74">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="Q74">
-        <v>3.18</v>
+        <v>3.78</v>
       </c>
       <c r="R74">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15252,10 +15252,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AF74">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15353,7 +15353,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15392,13 +15392,13 @@
         <v>423</v>
       </c>
       <c r="P75">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="Q75">
-        <v>5.03</v>
+        <v>3.18</v>
       </c>
       <c r="R75">
-        <v>5.63</v>
+        <v>4</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15437,16 +15437,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG75">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -15538,7 +15538,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15577,13 +15577,13 @@
         <v>423</v>
       </c>
       <c r="P76">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q76">
-        <v>4.35</v>
+        <v>3.38</v>
       </c>
       <c r="R76">
-        <v>6.14</v>
+        <v>3.58</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15622,10 +15622,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15762,13 +15762,13 @@
         <v>423</v>
       </c>
       <c r="P77">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q77">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="R77">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15947,13 +15947,13 @@
         <v>423</v>
       </c>
       <c r="P78">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Q78">
-        <v>3.16</v>
+        <v>5.03</v>
       </c>
       <c r="R78">
-        <v>3.16</v>
+        <v>5.63</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15992,16 +15992,16 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF78">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16132,13 +16132,13 @@
         <v>423</v>
       </c>
       <c r="P79">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q79">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R79">
-        <v>6.11</v>
+        <v>5</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16177,10 +16177,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16463,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16502,13 +16502,13 @@
         <v>423</v>
       </c>
       <c r="P81">
-        <v>3.41</v>
+        <v>1.47</v>
       </c>
       <c r="Q81">
-        <v>3.22</v>
+        <v>4.35</v>
       </c>
       <c r="R81">
-        <v>2.16</v>
+        <v>6.14</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16547,10 +16547,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16687,13 +16687,13 @@
         <v>423</v>
       </c>
       <c r="P82">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="Q82">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="R82">
-        <v>3.58</v>
+        <v>6.11</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16732,10 +16732,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF82">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16872,13 +16872,13 @@
         <v>423</v>
       </c>
       <c r="P83">
-        <v>1.76</v>
+        <v>3.41</v>
       </c>
       <c r="Q83">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="R83">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16917,10 +16917,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AF83">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17206,7 +17206,7 @@
         <v>130</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17242,13 +17242,13 @@
         <v>423</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17287,10 +17287,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17573,7 +17573,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17758,7 +17758,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17943,7 +17943,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18313,7 +18313,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>145</v>
@@ -18352,13 +18352,13 @@
         <v>423</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18498,10 +18498,10 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
@@ -18537,13 +18537,13 @@
         <v>423</v>
       </c>
       <c r="P92">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18683,10 +18683,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18722,13 +18722,13 @@
         <v>423</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18868,7 +18868,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19053,10 +19053,10 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E95" t="s">
         <v>240</v>
@@ -19092,13 +19092,13 @@
         <v>423</v>
       </c>
       <c r="P95">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19423,10 +19423,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19608,10 +19608,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -19793,7 +19793,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19978,7 +19978,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20163,7 +20163,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20348,7 +20348,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20903,7 +20903,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21461,7 +21461,7 @@
         <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
@@ -21643,7 +21643,7 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
         <v>145</v>
@@ -21828,10 +21828,10 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -22013,7 +22013,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22198,10 +22198,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22383,10 +22383,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22568,7 +22568,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22753,7 +22753,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D115" t="s">
         <v>146</v>
@@ -22938,10 +22938,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23123,7 +23123,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23308,10 +23308,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23493,7 +23493,7 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D119" t="s">
         <v>146</v>
@@ -23678,7 +23678,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="D120" t="s">
         <v>145</v>
@@ -23714,7 +23714,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23863,7 +23863,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24048,7 +24048,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="D122" t="s">
         <v>145</v>
@@ -24233,10 +24233,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24418,10 +24418,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24454,7 +24454,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24603,7 +24603,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="D125" t="s">
         <v>145</v>
@@ -24788,7 +24788,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D126" t="s">
         <v>146</v>
@@ -24973,10 +24973,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25158,10 +25158,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25343,10 +25343,10 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -25528,7 +25528,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25713,7 +25713,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -25898,7 +25898,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
         <v>146</v>
@@ -26083,7 +26083,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="D133" t="s">
         <v>145</v>
@@ -26268,10 +26268,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
@@ -26453,7 +26453,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26638,10 +26638,10 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="D136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E136" t="s">
         <v>281</v>
@@ -26823,10 +26823,10 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="D137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
@@ -27008,7 +27008,7 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D138" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -319,54 +319,54 @@
     <t>Serbia Prva Liga</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
@@ -376,48 +376,48 @@
     <t>France National</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
@@ -499,375 +499,375 @@
     <t>Kabel Novi Sad</t>
   </si>
   <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Ranheim</t>
   </si>
   <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
     <t>Villefranche</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Durban City</t>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
   </si>
   <si>
     <t>NAC Breda W</t>
   </si>
   <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
     <t>PEC Zwolle W</t>
   </si>
   <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>PSV W</t>
-  </si>
-  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
     <t>Wil</t>
   </si>
   <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
   </si>
   <si>
     <t>Avellino</t>
   </si>
   <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
     <t>Reggiana</t>
   </si>
   <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
+    <t>Levante UD</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
     <t>Fram</t>
   </si>
   <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
     <t>Stjarnan</t>
   </si>
   <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
     <t>Radnik Bijeljina</t>
   </si>
   <si>
+    <t>Loznica</t>
+  </si>
+  <si>
     <t>San Telmo</t>
   </si>
   <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
     <t>Voždovac</t>
   </si>
   <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -889,12 +889,12 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -913,373 +913,373 @@
     <t>Trajal Krusevac</t>
   </si>
   <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
     <t>Admira</t>
   </si>
   <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Liepāja</t>
   </si>
   <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>Vålerenga</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>Thór</t>
   </si>
   <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
     <t>Ajaccio</t>
   </si>
   <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
   </si>
   <si>
     <t>Twente W</t>
   </si>
   <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
     <t>HERA</t>
   </si>
   <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
   </si>
   <si>
     <t>Modena</t>
   </si>
   <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
     <t>Mantova</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
     <t>Sampdoria</t>
   </si>
   <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
   </si>
   <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
+    <t>FH</t>
+  </si>
+  <si>
     <t>KR</t>
   </si>
   <si>
     <t>Keflavík</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
     <t>Sarajevo</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
     <t>Zrinjski</t>
   </si>
   <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
     <t>OFK Vršac</t>
   </si>
   <si>
     <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4477,13 +4477,13 @@
         <v>423</v>
       </c>
       <c r="P16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -4808,10 +4808,10 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -4993,7 +4993,7 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -5032,13 +5032,13 @@
         <v>423</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5551,7 +5551,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5587,13 +5587,13 @@
         <v>423</v>
       </c>
       <c r="P22">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5632,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -5733,10 +5733,10 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5921,7 +5921,7 @@
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6103,7 +6103,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6142,13 +6142,13 @@
         <v>423</v>
       </c>
       <c r="P25">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6187,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -6288,7 +6288,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -6473,7 +6473,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -6658,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6697,13 +6697,13 @@
         <v>423</v>
       </c>
       <c r="P28">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6843,10 +6843,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7028,7 +7028,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7213,7 +7213,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -7252,13 +7252,13 @@
         <v>423</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7297,10 +7297,10 @@
         <v>0</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -7398,10 +7398,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7437,13 +7437,13 @@
         <v>423</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7482,10 +7482,10 @@
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -7583,10 +7583,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7768,7 +7768,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7953,10 +7953,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8138,10 +8138,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8177,13 +8177,13 @@
         <v>423</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8323,7 +8323,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8508,7 +8508,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -8693,7 +8693,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -9287,13 +9287,13 @@
         <v>423</v>
       </c>
       <c r="P42">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="Q42">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9436,7 +9436,7 @@
         <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9472,13 +9472,13 @@
         <v>423</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9618,10 +9618,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9657,13 +9657,13 @@
         <v>423</v>
       </c>
       <c r="P44">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9803,7 +9803,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9988,7 +9988,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
         <v>145</v>
@@ -10173,7 +10173,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10212,13 +10212,13 @@
         <v>423</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10397,13 +10397,13 @@
         <v>423</v>
       </c>
       <c r="P48">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10543,10 +10543,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10728,7 +10728,7 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
         <v>146</v>
@@ -10913,7 +10913,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10952,13 +10952,13 @@
         <v>423</v>
       </c>
       <c r="P51">
-        <v>1.77</v>
+        <v>3.03</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R51">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11283,7 +11283,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11319,7 +11319,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11468,10 +11468,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11504,7 +11504,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11653,7 +11653,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
         <v>145</v>
@@ -11841,7 +11841,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -12393,7 +12393,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12432,13 +12432,13 @@
         <v>423</v>
       </c>
       <c r="P59">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q59">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -12763,7 +12763,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12802,13 +12802,13 @@
         <v>423</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13318,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -14652,13 +14652,13 @@
         <v>423</v>
       </c>
       <c r="P71">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="Q71">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="R71">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14697,10 +14697,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF71">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14798,7 +14798,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14837,13 +14837,13 @@
         <v>423</v>
       </c>
       <c r="P72">
-        <v>3.57</v>
+        <v>1.49</v>
       </c>
       <c r="Q72">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="R72">
-        <v>2.13</v>
+        <v>6.11</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14882,10 +14882,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -15022,13 +15022,13 @@
         <v>423</v>
       </c>
       <c r="P73">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q73">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R73">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15067,10 +15067,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF73">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15168,7 +15168,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15207,13 +15207,13 @@
         <v>423</v>
       </c>
       <c r="P74">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="Q74">
-        <v>3.78</v>
+        <v>5.03</v>
       </c>
       <c r="R74">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15252,16 +15252,16 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF74">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -15353,7 +15353,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15392,13 +15392,13 @@
         <v>423</v>
       </c>
       <c r="P75">
-        <v>1.99</v>
+        <v>3.57</v>
       </c>
       <c r="Q75">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15437,10 +15437,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15577,13 +15577,13 @@
         <v>423</v>
       </c>
       <c r="P76">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="Q76">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R76">
-        <v>3.58</v>
+        <v>4.08</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15622,10 +15622,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AF76">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15762,13 +15762,13 @@
         <v>423</v>
       </c>
       <c r="P77">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q77">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="R77">
-        <v>4.08</v>
+        <v>4.3</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF77">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15947,13 +15947,13 @@
         <v>423</v>
       </c>
       <c r="P78">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="Q78">
-        <v>5.03</v>
+        <v>3.56</v>
       </c>
       <c r="R78">
-        <v>5.63</v>
+        <v>3.05</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15992,16 +15992,16 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG78">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH78">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16093,7 +16093,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16132,13 +16132,13 @@
         <v>423</v>
       </c>
       <c r="P79">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q79">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="R79">
-        <v>5</v>
+        <v>6.14</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16317,13 +16317,13 @@
         <v>423</v>
       </c>
       <c r="P80">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="Q80">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="R80">
-        <v>3.05</v>
+        <v>4.22</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF80">
         <v>2.15</v>
@@ -16463,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16502,13 +16502,13 @@
         <v>423</v>
       </c>
       <c r="P81">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q81">
-        <v>4.35</v>
+        <v>3.16</v>
       </c>
       <c r="R81">
-        <v>6.14</v>
+        <v>3.16</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16547,10 +16547,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16687,13 +16687,13 @@
         <v>423</v>
       </c>
       <c r="P82">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q82">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R82">
-        <v>6.11</v>
+        <v>5</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16732,10 +16732,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17242,13 +17242,13 @@
         <v>423</v>
       </c>
       <c r="P85">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q85">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="R85">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17287,10 +17287,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17576,7 +17576,7 @@
         <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17612,13 +17612,13 @@
         <v>423</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17657,10 +17657,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -17758,7 +17758,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17943,10 +17943,10 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
@@ -17982,13 +17982,13 @@
         <v>423</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18128,7 +18128,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18313,10 +18313,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18352,13 +18352,13 @@
         <v>423</v>
       </c>
       <c r="P91">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18498,7 +18498,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18683,10 +18683,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18722,13 +18722,13 @@
         <v>423</v>
       </c>
       <c r="P93">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18868,7 +18868,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19423,10 +19423,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19608,10 +19608,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -20533,7 +20533,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20903,7 +20903,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21088,7 +21088,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21461,7 +21461,7 @@
         <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
@@ -21643,7 +21643,7 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
         <v>145</v>
@@ -21828,7 +21828,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -22013,10 +22013,10 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="D111" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22568,10 +22568,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22604,7 +22604,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22938,7 +22938,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -23123,7 +23123,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23308,10 +23308,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23493,7 +23493,7 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D119" t="s">
         <v>146</v>
@@ -23678,7 +23678,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D120" t="s">
         <v>145</v>
@@ -23863,10 +23863,10 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="D121" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
@@ -24048,10 +24048,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24233,10 +24233,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24418,7 +24418,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D124" t="s">
         <v>145</v>
@@ -24454,7 +24454,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24603,10 +24603,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -25158,7 +25158,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
         <v>145</v>
@@ -25343,10 +25343,10 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -25528,7 +25528,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25713,7 +25713,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -26083,7 +26083,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D133" t="s">
         <v>145</v>
@@ -26268,7 +26268,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
         <v>145</v>
@@ -26453,7 +26453,7 @@
         <v>88</v>
       </c>
       <c r="C135" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D135" t="s">
         <v>145</v>
@@ -26638,7 +26638,7 @@
         <v>88</v>
       </c>
       <c r="C136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D136" t="s">
         <v>146</v>
@@ -26823,10 +26823,10 @@
         <v>88</v>
       </c>
       <c r="C137" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E137" t="s">
         <v>282</v>
@@ -27008,7 +27008,7 @@
         <v>88</v>
       </c>
       <c r="C138" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D138" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="417">
   <si>
     <t>Date</t>
   </si>
@@ -310,78 +310,78 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
+    <t>France National</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -394,13 +394,19 @@
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
@@ -412,18 +418,12 @@
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>France Ligue 1</t>
+    <t>Spain La Liga</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Brazil Serie C</t>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
+    <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,142 +484,151 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
+    <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
   </si>
   <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Chayka</t>
+    <t>Fakel</t>
   </si>
   <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
     <t>Lillestrøm W</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
   </si>
   <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
   </si>
   <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>PSV W</t>
   </si>
   <si>
     <t>Ajax W</t>
@@ -628,58 +637,64 @@
     <t>Utrecht W</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
   </si>
   <si>
     <t>Wil</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
     <t>Aarau</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
     <t>Virtus Entella</t>
   </si>
   <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Venezia</t>
+    <t>Frosinone</t>
   </si>
   <si>
     <t>Cesena</t>
@@ -688,19 +703,10 @@
     <t>Pescara</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
@@ -712,40 +718,40 @@
     <t>Athlone Town</t>
   </si>
   <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>Torino</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Wexford</t>
+    <t>Cork City</t>
   </si>
   <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Levante UD</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>ÍA</t>
   </si>
   <si>
     <t>Fram</t>
@@ -754,120 +760,102 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
     <t>Atlético Rafaela</t>
   </si>
   <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Domžale</t>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
   </si>
   <si>
     <t>Amazonas</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Posusje</t>
   </si>
   <si>
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
+    <t>Voždovac</t>
   </si>
   <si>
     <t>Jedinstvo Ub</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
     <t>Loznica</t>
   </si>
   <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -898,142 +886,151 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
+    <t>Arda</t>
   </si>
   <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Arda</t>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
   </si>
   <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
+    <t>SKA Khabarovsk</t>
   </si>
   <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
     <t>Haugesund W</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
   </si>
   <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
   </si>
   <si>
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>HB</t>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
   </si>
   <si>
     <t>AZ W</t>
@@ -1042,58 +1039,64 @@
     <t>Heerenveen W</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
     <t>Feyenoord W</t>
   </si>
   <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
     <t>Bellinzona</t>
   </si>
   <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
     <t>Carrarese</t>
   </si>
   <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Palermo</t>
+    <t>Mantova</t>
   </si>
   <si>
     <t>Calcio Padova</t>
@@ -1102,19 +1105,10 @@
     <t>Spezia</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
@@ -1126,40 +1120,40 @@
     <t>Treaty United</t>
   </si>
   <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>Sassuolo</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Longford Town</t>
+    <t>UCD</t>
   </si>
   <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>CA Osasuna</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
-    <t>Waterford</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
   </si>
   <si>
     <t>Valur</t>
@@ -1168,118 +1162,100 @@
     <t>FH</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Celje</t>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Almagro</t>
   </si>
   <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Velež</t>
   </si>
   <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Rangers</t>
+    <t>OFK Vršac</t>
   </si>
   <si>
     <t>Zemun</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
     <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -1652,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI139"/>
+  <dimension ref="A1:BI135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1857,7 +1833,7 @@
         <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1884,7 +1860,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2042,7 +2018,7 @@
         <v>148</v>
       </c>
       <c r="F3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2069,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2227,7 +2203,7 @@
         <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2254,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2412,7 +2388,7 @@
         <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2439,7 +2415,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2597,7 +2573,7 @@
         <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2624,7 +2600,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2782,7 +2758,7 @@
         <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2809,7 +2785,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2967,7 +2943,7 @@
         <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2994,7 +2970,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3152,7 +3128,7 @@
         <v>154</v>
       </c>
       <c r="F9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3179,7 +3155,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3337,7 +3313,7 @@
         <v>155</v>
       </c>
       <c r="F10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3364,7 +3340,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3522,7 +3498,7 @@
         <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3549,7 +3525,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3707,7 +3683,7 @@
         <v>157</v>
       </c>
       <c r="F12" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3734,7 +3710,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3886,13 +3862,13 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3919,7 +3895,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4071,13 +4047,13 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4104,7 +4080,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4262,7 +4238,7 @@
         <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -4289,7 +4265,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4447,7 +4423,7 @@
         <v>161</v>
       </c>
       <c r="F16" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4474,16 +4450,16 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4626,13 +4602,13 @@
         <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
       </c>
       <c r="F17" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4659,7 +4635,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4808,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4817,7 +4793,7 @@
         <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4844,7 +4820,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4996,13 +4972,13 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -5029,16 +5005,16 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5187,7 +5163,7 @@
         <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -5214,7 +5190,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5372,7 +5348,7 @@
         <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -5399,7 +5375,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5548,7 +5524,7 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -5557,7 +5533,7 @@
         <v>167</v>
       </c>
       <c r="F22" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5584,7 +5560,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5733,16 +5709,16 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
       </c>
       <c r="F23" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5769,16 +5745,16 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5817,10 +5793,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -5921,13 +5897,13 @@
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
       </c>
       <c r="F24" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5954,7 +5930,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -6103,7 +6079,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6112,7 +6088,7 @@
         <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -6139,7 +6115,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -6291,13 +6267,13 @@
         <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6324,16 +6300,16 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6372,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -6476,13 +6452,13 @@
         <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
       </c>
       <c r="F27" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6509,7 +6485,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6658,7 +6634,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6667,7 +6643,7 @@
         <v>173</v>
       </c>
       <c r="F28" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6694,7 +6670,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6843,16 +6819,16 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6879,7 +6855,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -7028,16 +7004,16 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7064,7 +7040,7 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -7216,13 +7192,13 @@
         <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
       </c>
       <c r="F31" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7249,16 +7225,16 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P31">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7297,10 +7273,10 @@
         <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -7398,7 +7374,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -7407,7 +7383,7 @@
         <v>177</v>
       </c>
       <c r="F32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7434,16 +7410,16 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P32">
-        <v>2.4</v>
+        <v>4.78</v>
       </c>
       <c r="Q32">
-        <v>3.5</v>
+        <v>4.14</v>
       </c>
       <c r="R32">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7482,10 +7458,10 @@
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -7583,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7592,7 +7568,7 @@
         <v>178</v>
       </c>
       <c r="F33" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7619,7 +7595,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7768,7 +7744,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7777,7 +7753,7 @@
         <v>179</v>
       </c>
       <c r="F34" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7804,7 +7780,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7956,13 +7932,13 @@
         <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7989,7 +7965,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -8138,7 +8114,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -8147,7 +8123,7 @@
         <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -8174,16 +8150,16 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P36">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8326,13 +8302,13 @@
         <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -8359,16 +8335,16 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P37">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8508,16 +8484,16 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
       </c>
       <c r="F38" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -8544,16 +8520,16 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8693,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8702,7 +8678,7 @@
         <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8729,7 +8705,7 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -8887,7 +8863,7 @@
         <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8914,7 +8890,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -9072,7 +9048,7 @@
         <v>186</v>
       </c>
       <c r="F41" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -9099,7 +9075,7 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -9257,7 +9233,7 @@
         <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -9284,16 +9260,16 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P42">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="Q42">
-        <v>3.61</v>
+        <v>3.76</v>
       </c>
       <c r="R42">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9442,7 +9418,7 @@
         <v>188</v>
       </c>
       <c r="F43" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -9469,16 +9445,16 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P43">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9627,7 +9603,7 @@
         <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -9654,7 +9630,7 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -9806,13 +9782,13 @@
         <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9839,16 +9815,16 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9988,7 +9964,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
         <v>145</v>
@@ -9997,7 +9973,7 @@
         <v>191</v>
       </c>
       <c r="F46" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -10024,7 +10000,7 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -10173,16 +10149,16 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -10209,16 +10185,16 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P47">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10358,7 +10334,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10367,7 +10343,7 @@
         <v>193</v>
       </c>
       <c r="F48" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -10394,7 +10370,7 @@
         <v>-1</v>
       </c>
       <c r="O48" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -10543,16 +10519,16 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
       </c>
       <c r="F49" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -10579,16 +10555,16 @@
         <v>-1</v>
       </c>
       <c r="O49" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10728,16 +10704,16 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
       </c>
       <c r="F50" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -10764,7 +10740,7 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -10913,7 +10889,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10922,7 +10898,7 @@
         <v>196</v>
       </c>
       <c r="F51" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -10949,7 +10925,7 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P51">
         <v>3.03</v>
@@ -11101,13 +11077,13 @@
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
       </c>
       <c r="F52" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -11134,7 +11110,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11283,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11292,7 +11268,7 @@
         <v>198</v>
       </c>
       <c r="F53" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -11319,7 +11295,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11471,13 +11447,13 @@
         <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
       </c>
       <c r="F54" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -11504,7 +11480,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11662,7 +11638,7 @@
         <v>200</v>
       </c>
       <c r="F55" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -11689,7 +11665,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11847,7 +11823,7 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -11874,7 +11850,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12032,7 +12008,7 @@
         <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -12059,7 +12035,7 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -12208,7 +12184,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12217,7 +12193,7 @@
         <v>203</v>
       </c>
       <c r="F58" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -12244,7 +12220,7 @@
         <v>-1</v>
       </c>
       <c r="O58" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -12402,7 +12378,7 @@
         <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12429,7 +12405,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12587,7 +12563,7 @@
         <v>205</v>
       </c>
       <c r="F60" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12614,7 +12590,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12763,7 +12739,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12772,7 +12748,7 @@
         <v>206</v>
       </c>
       <c r="F61" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12799,16 +12775,16 @@
         <v>-1</v>
       </c>
       <c r="O61" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P61">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -12948,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -12957,7 +12933,7 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12984,7 +12960,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -13142,7 +13118,7 @@
         <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -13169,7 +13145,7 @@
         <v>-1</v>
       </c>
       <c r="O63" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -13318,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13327,7 +13303,7 @@
         <v>209</v>
       </c>
       <c r="F64" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -13354,7 +13330,7 @@
         <v>-1</v>
       </c>
       <c r="O64" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -13503,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13512,7 +13488,7 @@
         <v>210</v>
       </c>
       <c r="F65" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13539,16 +13515,16 @@
         <v>-1</v>
       </c>
       <c r="O65" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13697,7 +13673,7 @@
         <v>211</v>
       </c>
       <c r="F66" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13724,7 +13700,7 @@
         <v>-1</v>
       </c>
       <c r="O66" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -13882,7 +13858,7 @@
         <v>212</v>
       </c>
       <c r="F67" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13909,7 +13885,7 @@
         <v>-1</v>
       </c>
       <c r="O67" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -14067,7 +14043,7 @@
         <v>213</v>
       </c>
       <c r="F68" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -14094,7 +14070,7 @@
         <v>-1</v>
       </c>
       <c r="O68" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -14252,7 +14228,7 @@
         <v>214</v>
       </c>
       <c r="F69" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14279,7 +14255,7 @@
         <v>-1</v>
       </c>
       <c r="O69" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P69">
         <v>1.33</v>
@@ -14437,7 +14413,7 @@
         <v>215</v>
       </c>
       <c r="F70" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14464,7 +14440,7 @@
         <v>-1</v>
       </c>
       <c r="O70" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P70">
         <v>0</v>
@@ -14622,7 +14598,7 @@
         <v>216</v>
       </c>
       <c r="F71" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -14649,16 +14625,16 @@
         <v>-1</v>
       </c>
       <c r="O71" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P71">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="Q71">
-        <v>3.18</v>
+        <v>5.03</v>
       </c>
       <c r="R71">
-        <v>4</v>
+        <v>5.63</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14697,16 +14673,16 @@
         <v>0</v>
       </c>
       <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
         <v>1.9</v>
       </c>
-      <c r="AF71">
-        <v>1.78</v>
-      </c>
-      <c r="AG71">
-        <v>0</v>
-      </c>
       <c r="AH71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14798,7 +14774,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14807,7 +14783,7 @@
         <v>217</v>
       </c>
       <c r="F72" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -14834,16 +14810,16 @@
         <v>-1</v>
       </c>
       <c r="O72" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P72">
-        <v>1.49</v>
+        <v>3.57</v>
       </c>
       <c r="Q72">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="R72">
-        <v>6.11</v>
+        <v>2.13</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14882,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14983,7 +14959,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -14992,7 +14968,7 @@
         <v>218</v>
       </c>
       <c r="F73" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -15019,16 +14995,16 @@
         <v>-1</v>
       </c>
       <c r="O73" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P73">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="Q73">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="R73">
-        <v>3.58</v>
+        <v>6.11</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15067,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF73">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15168,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15177,7 +15153,7 @@
         <v>219</v>
       </c>
       <c r="F74" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -15204,16 +15180,16 @@
         <v>-1</v>
       </c>
       <c r="O74" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P74">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="Q74">
-        <v>5.03</v>
+        <v>3.78</v>
       </c>
       <c r="R74">
-        <v>5.63</v>
+        <v>4.22</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15252,16 +15228,16 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG74">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH74">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -15362,7 +15338,7 @@
         <v>220</v>
       </c>
       <c r="F75" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -15389,16 +15365,16 @@
         <v>-1</v>
       </c>
       <c r="O75" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P75">
-        <v>3.57</v>
+        <v>2.3</v>
       </c>
       <c r="Q75">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="R75">
-        <v>2.13</v>
+        <v>3.16</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15437,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15538,7 +15514,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15547,7 +15523,7 @@
         <v>221</v>
       </c>
       <c r="F76" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -15574,16 +15550,16 @@
         <v>-1</v>
       </c>
       <c r="O76" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P76">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="Q76">
-        <v>3.84</v>
+        <v>3.38</v>
       </c>
       <c r="R76">
-        <v>4.08</v>
+        <v>3.58</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15622,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF76">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15723,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15732,7 +15708,7 @@
         <v>222</v>
       </c>
       <c r="F77" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -15759,16 +15735,16 @@
         <v>-1</v>
       </c>
       <c r="O77" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P77">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q77">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="R77">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15807,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF77">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15908,7 +15884,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15917,7 +15893,7 @@
         <v>223</v>
       </c>
       <c r="F78" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -15944,16 +15920,16 @@
         <v>-1</v>
       </c>
       <c r="O78" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P78">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="Q78">
-        <v>3.56</v>
+        <v>4.35</v>
       </c>
       <c r="R78">
-        <v>3.05</v>
+        <v>6.14</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15992,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF78">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16093,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16102,7 +16078,7 @@
         <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -16129,16 +16105,16 @@
         <v>-1</v>
       </c>
       <c r="O79" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P79">
-        <v>1.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q79">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="R79">
-        <v>6.14</v>
+        <v>2.16</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16177,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16278,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16287,7 +16263,7 @@
         <v>225</v>
       </c>
       <c r="F80" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -16314,16 +16290,16 @@
         <v>-1</v>
       </c>
       <c r="O80" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P80">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="Q80">
-        <v>3.78</v>
+        <v>3.18</v>
       </c>
       <c r="R80">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16362,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AF80">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16463,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16472,7 +16448,7 @@
         <v>226</v>
       </c>
       <c r="F81" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -16499,16 +16475,16 @@
         <v>-1</v>
       </c>
       <c r="O81" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P81">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="Q81">
-        <v>3.16</v>
+        <v>4.5</v>
       </c>
       <c r="R81">
-        <v>3.16</v>
+        <v>5</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16547,10 +16523,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16648,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16657,7 +16633,7 @@
         <v>227</v>
       </c>
       <c r="F82" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -16684,16 +16660,16 @@
         <v>-1</v>
       </c>
       <c r="O82" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P82">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="Q82">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R82">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16732,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16833,7 +16809,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16842,7 +16818,7 @@
         <v>228</v>
       </c>
       <c r="F83" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -16869,16 +16845,16 @@
         <v>-1</v>
       </c>
       <c r="O83" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P83">
-        <v>3.41</v>
+        <v>2.18</v>
       </c>
       <c r="Q83">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="R83">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16917,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
+        <v>1.61</v>
+      </c>
+      <c r="AF83">
         <v>2.15</v>
-      </c>
-      <c r="AF83">
-        <v>1.61</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17021,13 +16997,13 @@
         <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
       </c>
       <c r="F84" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -17054,16 +17030,16 @@
         <v>-1</v>
       </c>
       <c r="O84" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17206,13 +17182,13 @@
         <v>130</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
       </c>
       <c r="F85" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -17239,16 +17215,16 @@
         <v>-1</v>
       </c>
       <c r="O85" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P85">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17388,7 +17364,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17397,7 +17373,7 @@
         <v>231</v>
       </c>
       <c r="F86" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -17424,7 +17400,7 @@
         <v>-1</v>
       </c>
       <c r="O86" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -17573,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D87" t="s">
         <v>145</v>
@@ -17582,7 +17558,7 @@
         <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -17609,16 +17585,16 @@
         <v>-1</v>
       </c>
       <c r="O87" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P87">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q87">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="R87">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17657,10 +17633,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -17758,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17767,7 +17743,7 @@
         <v>233</v>
       </c>
       <c r="F88" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -17794,7 +17770,7 @@
         <v>-1</v>
       </c>
       <c r="O88" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P88">
         <v>0</v>
@@ -17943,16 +17919,16 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
       </c>
       <c r="F89" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -17979,16 +17955,16 @@
         <v>-1</v>
       </c>
       <c r="O89" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P89">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18128,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18137,7 +18113,7 @@
         <v>235</v>
       </c>
       <c r="F90" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -18164,7 +18140,7 @@
         <v>-1</v>
       </c>
       <c r="O90" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P90">
         <v>0</v>
@@ -18313,7 +18289,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18322,7 +18298,7 @@
         <v>236</v>
       </c>
       <c r="F91" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -18349,7 +18325,7 @@
         <v>-1</v>
       </c>
       <c r="O91" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P91">
         <v>0</v>
@@ -18498,16 +18474,16 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -18534,16 +18510,16 @@
         <v>-1</v>
       </c>
       <c r="O92" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18582,10 +18558,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -18683,7 +18659,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18692,7 +18668,7 @@
         <v>238</v>
       </c>
       <c r="F93" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -18719,7 +18695,7 @@
         <v>-1</v>
       </c>
       <c r="O93" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -18868,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -18877,7 +18853,7 @@
         <v>239</v>
       </c>
       <c r="F94" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -18904,7 +18880,7 @@
         <v>-1</v>
       </c>
       <c r="O94" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -19053,7 +19029,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
         <v>146</v>
@@ -19062,7 +19038,7 @@
         <v>240</v>
       </c>
       <c r="F95" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -19089,7 +19065,7 @@
         <v>-1</v>
       </c>
       <c r="O95" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -19238,16 +19214,16 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -19274,7 +19250,7 @@
         <v>-1</v>
       </c>
       <c r="O96" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -19423,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19432,7 +19408,7 @@
         <v>242</v>
       </c>
       <c r="F97" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -19459,7 +19435,7 @@
         <v>-1</v>
       </c>
       <c r="O97" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P97">
         <v>0</v>
@@ -19608,16 +19584,16 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
       </c>
       <c r="F98" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -19644,7 +19620,7 @@
         <v>-1</v>
       </c>
       <c r="O98" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -19793,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19802,7 +19778,7 @@
         <v>244</v>
       </c>
       <c r="F99" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -19829,7 +19805,7 @@
         <v>-1</v>
       </c>
       <c r="O99" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -19978,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -19987,7 +19963,7 @@
         <v>245</v>
       </c>
       <c r="F100" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -20014,7 +19990,7 @@
         <v>-1</v>
       </c>
       <c r="O100" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -20163,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20172,7 +20148,7 @@
         <v>246</v>
       </c>
       <c r="F101" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -20199,7 +20175,7 @@
         <v>-1</v>
       </c>
       <c r="O101" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -20348,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20357,7 +20333,7 @@
         <v>247</v>
       </c>
       <c r="F102" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -20384,7 +20360,7 @@
         <v>-1</v>
       </c>
       <c r="O102" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -20542,7 +20518,7 @@
         <v>248</v>
       </c>
       <c r="F103" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -20569,7 +20545,7 @@
         <v>-1</v>
       </c>
       <c r="O103" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -20727,7 +20703,7 @@
         <v>249</v>
       </c>
       <c r="F104" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -20754,7 +20730,7 @@
         <v>-1</v>
       </c>
       <c r="O104" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P104">
         <v>0</v>
@@ -20903,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -20912,7 +20888,7 @@
         <v>250</v>
       </c>
       <c r="F105" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -20939,7 +20915,7 @@
         <v>-1</v>
       </c>
       <c r="O105" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -21088,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21097,7 +21073,7 @@
         <v>251</v>
       </c>
       <c r="F106" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -21124,7 +21100,7 @@
         <v>-1</v>
       </c>
       <c r="O106" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -21282,7 +21258,7 @@
         <v>252</v>
       </c>
       <c r="F107" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -21309,7 +21285,7 @@
         <v>-1</v>
       </c>
       <c r="O107" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P107">
         <v>0</v>
@@ -21461,13 +21437,13 @@
         <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
       </c>
       <c r="F108" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -21494,7 +21470,7 @@
         <v>-1</v>
       </c>
       <c r="O108" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -21646,13 +21622,13 @@
         <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
       </c>
       <c r="F109" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -21679,7 +21655,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21828,7 +21804,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -21837,7 +21813,7 @@
         <v>255</v>
       </c>
       <c r="F110" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -21864,7 +21840,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -22013,16 +21989,16 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
       </c>
       <c r="F111" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -22049,7 +22025,7 @@
         <v>-1</v>
       </c>
       <c r="O111" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -22198,16 +22174,16 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
       </c>
       <c r="F112" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -22234,7 +22210,7 @@
         <v>-1</v>
       </c>
       <c r="O112" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -22383,7 +22359,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D113" t="s">
         <v>146</v>
@@ -22392,7 +22368,7 @@
         <v>258</v>
       </c>
       <c r="F113" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -22419,7 +22395,7 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -22568,16 +22544,16 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
       </c>
       <c r="F114" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -22604,7 +22580,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22753,16 +22729,16 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
       </c>
       <c r="F115" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -22789,7 +22765,7 @@
         <v>-1</v>
       </c>
       <c r="O115" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -22938,7 +22914,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -22947,7 +22923,7 @@
         <v>261</v>
       </c>
       <c r="F116" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -22974,7 +22950,7 @@
         <v>-1</v>
       </c>
       <c r="O116" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -23123,16 +23099,16 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
       </c>
       <c r="F117" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -23159,7 +23135,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23311,13 +23287,13 @@
         <v>140</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
       </c>
       <c r="F118" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -23344,7 +23320,7 @@
         <v>-1</v>
       </c>
       <c r="O118" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -23493,16 +23469,16 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
       </c>
       <c r="F119" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -23529,7 +23505,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23678,16 +23654,16 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
       </c>
       <c r="F120" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -23714,7 +23690,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23863,16 +23839,16 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
       </c>
       <c r="F121" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -23899,7 +23875,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24048,7 +24024,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D122" t="s">
         <v>146</v>
@@ -24057,7 +24033,7 @@
         <v>267</v>
       </c>
       <c r="F122" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -24084,7 +24060,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24233,7 +24209,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24242,7 +24218,7 @@
         <v>268</v>
       </c>
       <c r="F123" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -24269,7 +24245,7 @@
         <v>-1</v>
       </c>
       <c r="O123" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -24418,16 +24394,16 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
       </c>
       <c r="F124" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -24454,7 +24430,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24603,7 +24579,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24612,7 +24588,7 @@
         <v>270</v>
       </c>
       <c r="F125" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -24639,7 +24615,7 @@
         <v>-1</v>
       </c>
       <c r="O125" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P125">
         <v>0</v>
@@ -24788,7 +24764,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
         <v>146</v>
@@ -24797,7 +24773,7 @@
         <v>271</v>
       </c>
       <c r="F126" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -24824,7 +24800,7 @@
         <v>-1</v>
       </c>
       <c r="O126" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -24973,7 +24949,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D127" t="s">
         <v>146</v>
@@ -24982,7 +24958,7 @@
         <v>272</v>
       </c>
       <c r="F127" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -25009,7 +24985,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25158,16 +25134,16 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
       </c>
       <c r="F128" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -25194,7 +25170,7 @@
         <v>-1</v>
       </c>
       <c r="O128" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -25343,16 +25319,16 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
       </c>
       <c r="F129" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -25379,7 +25355,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -25531,13 +25507,13 @@
         <v>139</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130" t="s">
         <v>275</v>
       </c>
       <c r="F130" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -25564,7 +25540,7 @@
         <v>-1</v>
       </c>
       <c r="O130" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -25713,7 +25689,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -25722,7 +25698,7 @@
         <v>276</v>
       </c>
       <c r="F131" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -25749,7 +25725,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25898,43 +25874,43 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
       </c>
       <c r="F132" t="s">
+        <v>411</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>-1</v>
+      </c>
+      <c r="N132">
+        <v>-1</v>
+      </c>
+      <c r="O132" t="s">
         <v>415</v>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>-1</v>
-      </c>
-      <c r="N132">
-        <v>-1</v>
-      </c>
-      <c r="O132" t="s">
-        <v>423</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26083,7 +26059,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D133" t="s">
         <v>145</v>
@@ -26092,7 +26068,7 @@
         <v>278</v>
       </c>
       <c r="F133" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -26119,7 +26095,7 @@
         <v>-1</v>
       </c>
       <c r="O133" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -26268,7 +26244,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="D134" t="s">
         <v>145</v>
@@ -26277,7 +26253,7 @@
         <v>279</v>
       </c>
       <c r="F134" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -26304,7 +26280,7 @@
         <v>-1</v>
       </c>
       <c r="O134" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -26450,19 +26426,19 @@
         <v>46150</v>
       </c>
       <c r="B135" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C135" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E135" t="s">
         <v>280</v>
       </c>
       <c r="F135" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -26489,7 +26465,7 @@
         <v>-1</v>
       </c>
       <c r="O135" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -26627,746 +26603,6 @@
         <v>0</v>
       </c>
       <c r="BI135" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="136" spans="1:61">
-      <c r="A136" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B136" t="s">
-        <v>88</v>
-      </c>
-      <c r="C136" t="s">
-        <v>139</v>
-      </c>
-      <c r="D136" t="s">
-        <v>146</v>
-      </c>
-      <c r="E136" t="s">
-        <v>281</v>
-      </c>
-      <c r="F136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>-1</v>
-      </c>
-      <c r="N136">
-        <v>-1</v>
-      </c>
-      <c r="O136" t="s">
-        <v>423</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136">
-        <v>0</v>
-      </c>
-      <c r="AI136">
-        <v>0</v>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>0</v>
-      </c>
-      <c r="AN136">
-        <v>0</v>
-      </c>
-      <c r="AO136">
-        <v>0</v>
-      </c>
-      <c r="AP136">
-        <v>0</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136">
-        <v>0</v>
-      </c>
-      <c r="AV136">
-        <v>0</v>
-      </c>
-      <c r="AW136">
-        <v>0</v>
-      </c>
-      <c r="AX136">
-        <v>0</v>
-      </c>
-      <c r="AY136">
-        <v>0</v>
-      </c>
-      <c r="AZ136">
-        <v>0</v>
-      </c>
-      <c r="BA136">
-        <v>0</v>
-      </c>
-      <c r="BB136">
-        <v>0</v>
-      </c>
-      <c r="BC136">
-        <v>0</v>
-      </c>
-      <c r="BD136">
-        <v>0</v>
-      </c>
-      <c r="BE136">
-        <v>0</v>
-      </c>
-      <c r="BF136">
-        <v>0</v>
-      </c>
-      <c r="BG136">
-        <v>0</v>
-      </c>
-      <c r="BH136">
-        <v>0</v>
-      </c>
-      <c r="BI136" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="137" spans="1:61">
-      <c r="A137" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B137" t="s">
-        <v>88</v>
-      </c>
-      <c r="C137" t="s">
-        <v>100</v>
-      </c>
-      <c r="D137" t="s">
-        <v>145</v>
-      </c>
-      <c r="E137" t="s">
-        <v>282</v>
-      </c>
-      <c r="F137" t="s">
-        <v>420</v>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>-1</v>
-      </c>
-      <c r="N137">
-        <v>-1</v>
-      </c>
-      <c r="O137" t="s">
-        <v>423</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137">
-        <v>0</v>
-      </c>
-      <c r="AI137">
-        <v>0</v>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>0</v>
-      </c>
-      <c r="AN137">
-        <v>0</v>
-      </c>
-      <c r="AO137">
-        <v>0</v>
-      </c>
-      <c r="AP137">
-        <v>0</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137">
-        <v>0</v>
-      </c>
-      <c r="AV137">
-        <v>0</v>
-      </c>
-      <c r="AW137">
-        <v>0</v>
-      </c>
-      <c r="AX137">
-        <v>0</v>
-      </c>
-      <c r="AY137">
-        <v>0</v>
-      </c>
-      <c r="AZ137">
-        <v>0</v>
-      </c>
-      <c r="BA137">
-        <v>0</v>
-      </c>
-      <c r="BB137">
-        <v>0</v>
-      </c>
-      <c r="BC137">
-        <v>0</v>
-      </c>
-      <c r="BD137">
-        <v>0</v>
-      </c>
-      <c r="BE137">
-        <v>0</v>
-      </c>
-      <c r="BF137">
-        <v>0</v>
-      </c>
-      <c r="BG137">
-        <v>0</v>
-      </c>
-      <c r="BH137">
-        <v>0</v>
-      </c>
-      <c r="BI137" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="138" spans="1:61">
-      <c r="A138" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B138" t="s">
-        <v>88</v>
-      </c>
-      <c r="C138" t="s">
-        <v>141</v>
-      </c>
-      <c r="D138" t="s">
-        <v>146</v>
-      </c>
-      <c r="E138" t="s">
-        <v>283</v>
-      </c>
-      <c r="F138" t="s">
-        <v>421</v>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>-1</v>
-      </c>
-      <c r="N138">
-        <v>-1</v>
-      </c>
-      <c r="O138" t="s">
-        <v>423</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138">
-        <v>0</v>
-      </c>
-      <c r="AI138">
-        <v>0</v>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>0</v>
-      </c>
-      <c r="AN138">
-        <v>0</v>
-      </c>
-      <c r="AO138">
-        <v>0</v>
-      </c>
-      <c r="AP138">
-        <v>0</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138">
-        <v>0</v>
-      </c>
-      <c r="AV138">
-        <v>0</v>
-      </c>
-      <c r="AW138">
-        <v>0</v>
-      </c>
-      <c r="AX138">
-        <v>0</v>
-      </c>
-      <c r="AY138">
-        <v>0</v>
-      </c>
-      <c r="AZ138">
-        <v>0</v>
-      </c>
-      <c r="BA138">
-        <v>0</v>
-      </c>
-      <c r="BB138">
-        <v>0</v>
-      </c>
-      <c r="BC138">
-        <v>0</v>
-      </c>
-      <c r="BD138">
-        <v>0</v>
-      </c>
-      <c r="BE138">
-        <v>0</v>
-      </c>
-      <c r="BF138">
-        <v>0</v>
-      </c>
-      <c r="BG138">
-        <v>0</v>
-      </c>
-      <c r="BH138">
-        <v>0</v>
-      </c>
-      <c r="BI138" s="3">
-        <v>46150.875</v>
-      </c>
-    </row>
-    <row r="139" spans="1:61">
-      <c r="A139" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B139" t="s">
-        <v>89</v>
-      </c>
-      <c r="C139" t="s">
-        <v>138</v>
-      </c>
-      <c r="D139" t="s">
-        <v>146</v>
-      </c>
-      <c r="E139" t="s">
-        <v>284</v>
-      </c>
-      <c r="F139" t="s">
-        <v>422</v>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>-1</v>
-      </c>
-      <c r="N139">
-        <v>-1</v>
-      </c>
-      <c r="O139" t="s">
-        <v>423</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139">
-        <v>0</v>
-      </c>
-      <c r="AI139">
-        <v>0</v>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>0</v>
-      </c>
-      <c r="AN139">
-        <v>0</v>
-      </c>
-      <c r="AO139">
-        <v>0</v>
-      </c>
-      <c r="AP139">
-        <v>0</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139">
-        <v>0</v>
-      </c>
-      <c r="AV139">
-        <v>0</v>
-      </c>
-      <c r="AW139">
-        <v>0</v>
-      </c>
-      <c r="AX139">
-        <v>0</v>
-      </c>
-      <c r="AY139">
-        <v>0</v>
-      </c>
-      <c r="AZ139">
-        <v>0</v>
-      </c>
-      <c r="BA139">
-        <v>0</v>
-      </c>
-      <c r="BB139">
-        <v>0</v>
-      </c>
-      <c r="BC139">
-        <v>0</v>
-      </c>
-      <c r="BD139">
-        <v>0</v>
-      </c>
-      <c r="BE139">
-        <v>0</v>
-      </c>
-      <c r="BF139">
-        <v>0</v>
-      </c>
-      <c r="BG139">
-        <v>0</v>
-      </c>
-      <c r="BH139">
-        <v>0</v>
-      </c>
-      <c r="BI139" s="3">
         <v>46150.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,6 +316,9 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
@@ -325,30 +328,27 @@
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
@@ -358,6 +358,9 @@
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -367,54 +370,51 @@
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Italy Serie B</t>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
+    <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
+    <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -496,115 +496,124 @@
     <t>BFC Daugavpils</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
     <t>Ranheim</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Durban City</t>
@@ -613,82 +622,79 @@
     <t>Rodina Moskva</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
   </si>
   <si>
     <t>PEC Zwolle W</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>PSV W</t>
-  </si>
-  <si>
     <t>Ajax W</t>
   </si>
   <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
     <t>NAC Breda W</t>
   </si>
   <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
   </si>
   <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
+    <t>Cesena</t>
   </si>
   <si>
     <t>Virtus Entella</t>
@@ -697,55 +703,55 @@
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Pescara</t>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Lens</t>
   </si>
   <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Torino</t>
+    <t>Cork City</t>
   </si>
   <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Galway United</t>
+    <t>Levante UD</t>
+  </si>
+  <si>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
-    <t>Wisła Kraków</t>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>Stjarnan</t>
@@ -754,108 +760,102 @@
     <t>ÍA</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
     <t>Barra do Garcas</t>
   </si>
   <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -898,115 +898,124 @@
     <t>Riga</t>
   </si>
   <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
     <t>Liepāja</t>
   </si>
   <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Värnamo</t>
   </si>
   <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
-    <t>CSKA Sofia</t>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Stellenbosch</t>
@@ -1015,82 +1024,79 @@
     <t>Chelyabinsk</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>Thór</t>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
   </si>
   <si>
     <t>HERA</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
     <t>AZ W</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
     <t>Twente W</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
+    <t>Bellinzona</t>
   </si>
   <si>
     <t>Vaduz</t>
   </si>
   <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
   </si>
   <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
+    <t>Calcio Padova</t>
   </si>
   <si>
     <t>Carrarese</t>
@@ -1099,55 +1105,55 @@
     <t>Mantova</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Spezia</t>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Nantes</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
     <t>Bohemians</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
+    <t>UCD</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
-    <t>Chrobry Głogów</t>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>FH</t>
   </si>
   <si>
     <t>KR</t>
@@ -1156,106 +1162,100 @@
     <t>Keflavík</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
     <t>Sarajevo</t>
   </si>
   <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
     <t>Caxias</t>
   </si>
   <si>
     <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4232,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4453,13 +4453,13 @@
         <v>415</v>
       </c>
       <c r="P16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4638,13 +4638,13 @@
         <v>415</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4972,7 +4972,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5524,7 +5524,7 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -5709,7 +5709,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5748,13 +5748,13 @@
         <v>415</v>
       </c>
       <c r="P23">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R23">
-        <v>2.65</v>
+        <v>4.18</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5793,10 +5793,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -5894,7 +5894,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -6082,7 +6082,7 @@
         <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6303,14 +6303,14 @@
         <v>415</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q26">
+        <v>3.33</v>
+      </c>
+      <c r="R26">
         <v>3.78</v>
       </c>
-      <c r="R26">
-        <v>1.97</v>
-      </c>
       <c r="S26">
         <v>0</v>
       </c>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AF26">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6634,7 +6634,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -7004,7 +7004,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -7192,7 +7192,7 @@
         <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7228,13 +7228,13 @@
         <v>415</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -7413,13 +7413,13 @@
         <v>415</v>
       </c>
       <c r="P32">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7559,10 +7559,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>178</v>
@@ -7744,7 +7744,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7929,7 +7929,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -8114,10 +8114,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8299,7 +8299,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
         <v>146</v>
@@ -8484,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
         <v>145</v>
@@ -8523,13 +8523,13 @@
         <v>415</v>
       </c>
       <c r="P38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -8893,13 +8893,13 @@
         <v>415</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>415</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9594,10 +9594,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9779,10 +9779,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>1.77</v>
+        <v>2.94</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>3.96</v>
+        <v>2.32</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10149,7 +10149,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
         <v>146</v>
@@ -10334,7 +10334,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10519,10 +10519,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>2.94</v>
+        <v>1.77</v>
       </c>
       <c r="Q49">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="R49">
-        <v>2.32</v>
+        <v>3.96</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10704,7 +10704,7 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -10889,7 +10889,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10928,13 +10928,13 @@
         <v>415</v>
       </c>
       <c r="P51">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11077,7 +11077,7 @@
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
@@ -11259,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11295,7 +11295,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
         <v>146</v>
@@ -11629,7 +11629,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
         <v>145</v>
@@ -11665,7 +11665,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11814,10 +11814,10 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11853,13 +11853,13 @@
         <v>415</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12038,13 +12038,13 @@
         <v>415</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12184,7 +12184,7 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
         <v>145</v>
@@ -12369,7 +12369,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12554,7 +12554,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12739,7 +12739,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12924,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13518,13 +13518,13 @@
         <v>415</v>
       </c>
       <c r="P65">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>1.57</v>
+        <v>3.57</v>
       </c>
       <c r="Q71">
-        <v>5.03</v>
+        <v>3.42</v>
       </c>
       <c r="R71">
-        <v>5.63</v>
+        <v>2.13</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14679,10 +14679,10 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH71">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>3.57</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="R72">
-        <v>2.13</v>
+        <v>4.08</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14959,7 +14959,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -15144,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15329,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q75">
-        <v>3.16</v>
+        <v>3.56</v>
       </c>
       <c r="R75">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AF75">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>2.03</v>
+        <v>3.41</v>
       </c>
       <c r="Q76">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="R76">
-        <v>3.58</v>
+        <v>2.16</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF76">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15699,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q77">
-        <v>3.84</v>
+        <v>4.35</v>
       </c>
       <c r="R77">
-        <v>4.08</v>
+        <v>6.14</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>4.35</v>
+        <v>3.16</v>
       </c>
       <c r="R78">
-        <v>6.14</v>
+        <v>3.16</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="Q79">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R79">
-        <v>2.16</v>
+        <v>3.58</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF79">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="Q80">
-        <v>3.18</v>
+        <v>5.03</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>5.63</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,16 +16338,16 @@
         <v>0</v>
       </c>
       <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
         <v>1.9</v>
       </c>
-      <c r="AF80">
-        <v>1.78</v>
-      </c>
-      <c r="AG80">
-        <v>0</v>
-      </c>
       <c r="AH80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI80">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="Q81">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R81">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,10 +16523,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="Q82">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="R82">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF82">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="Q83">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="R83">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -16997,7 +16997,7 @@
         <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
@@ -17033,13 +17033,13 @@
         <v>415</v>
       </c>
       <c r="P84">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17182,7 +17182,7 @@
         <v>130</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17218,13 +17218,13 @@
         <v>415</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17367,7 +17367,7 @@
         <v>131</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>231</v>
@@ -17403,13 +17403,13 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17549,10 +17549,10 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17588,13 +17588,13 @@
         <v>415</v>
       </c>
       <c r="P87">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17734,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17919,7 +17919,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18104,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18289,7 +18289,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18659,7 +18659,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19029,7 +19029,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D95" t="s">
         <v>146</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19399,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19584,10 +19584,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20509,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21437,7 +21437,7 @@
         <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E108" t="s">
         <v>253</v>
@@ -21804,10 +21804,10 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -21989,7 +21989,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22174,7 +22174,7 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D112" t="s">
         <v>146</v>
@@ -22359,10 +22359,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22544,7 +22544,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22729,7 +22729,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D115" t="s">
         <v>145</v>
@@ -22765,7 +22765,7 @@
         <v>-1</v>
       </c>
       <c r="O115" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -22914,7 +22914,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23284,7 +23284,7 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D118" t="s">
         <v>146</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23654,10 +23654,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23839,10 +23839,10 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D121" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
@@ -24024,10 +24024,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24209,7 +24209,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24248,13 +24248,13 @@
         <v>415</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -24394,7 +24394,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -24579,7 +24579,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24764,7 +24764,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D126" t="s">
         <v>146</v>
@@ -24949,7 +24949,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
         <v>146</v>
@@ -25134,7 +25134,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D128" t="s">
         <v>146</v>
@@ -25319,10 +25319,10 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D130" t="s">
         <v>145</v>
@@ -25689,10 +25689,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25725,7 +25725,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25874,7 +25874,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -26059,10 +26059,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26244,10 +26244,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>
@@ -26468,13 +26468,13 @@
         <v>415</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S135">
         <v>0</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,114 +310,114 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
+    <t>Netherlands Eredivisie Women</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Netherlands Eredivisie Women</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
-    <t>Germany Bundesliga</t>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>France Ligue 1</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
+    <t>Italy Serie A</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -436,21 +436,21 @@
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,16 +484,25 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
+    <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>BFC Daugavpils</t>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
   </si>
   <si>
     <t>Toronto II</t>
@@ -502,124 +511,133 @@
     <t>Fakel</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
     <t>Brann W</t>
   </si>
   <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
     <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
   </si>
   <si>
     <t>CFR Cluj</t>
@@ -631,112 +649,97 @@
     <t>PSV W</t>
   </si>
   <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Wil</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
   </si>
   <si>
     <t>Cádiz</t>
   </si>
   <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
     <t>Venezia</t>
   </si>
   <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Cesena</t>
   </si>
   <si>
     <t>Pescara</t>
   </si>
   <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Cork City</t>
   </si>
   <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Lens</t>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Torino</t>
   </si>
   <si>
     <t>Standard Liège</t>
   </si>
   <si>
-    <t>Dundalk</t>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Levante UD</t>
@@ -745,117 +748,114 @@
     <t>Wisła Kraków</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>ÍA</t>
   </si>
   <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
     <t>Itabaiana</t>
   </si>
   <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
     <t>Atlético Rafaela</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
   </si>
   <si>
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -886,16 +886,25 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
+    <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Riga</t>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>New York RB II</t>
@@ -904,124 +913,133 @@
     <t>SKA Khabarovsk</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>CS U Craiova</t>
@@ -1033,112 +1051,97 @@
     <t>ADO Den Haag W</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Twente W</t>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
   </si>
   <si>
     <t>Deportivo La Coruña</t>
   </si>
   <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
     <t>Palermo</t>
   </si>
   <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
   </si>
   <si>
     <t>Spezia</t>
   </si>
   <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Mantova</t>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>UCD</t>
   </si>
   <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Nantes</t>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
   </si>
   <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Bohemians</t>
+    <t>Longford Town</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Derry City</t>
+    <t>Waterford</t>
   </si>
   <si>
     <t>CA Osasuna</t>
@@ -1147,115 +1150,112 @@
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>Waterford</t>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
   </si>
   <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Floresta</t>
   </si>
   <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
   </si>
   <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
     <t>Almagro</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3862,7 +3862,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -4047,7 +4047,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4232,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4453,13 +4453,13 @@
         <v>415</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4638,13 +4638,13 @@
         <v>415</v>
       </c>
       <c r="P17">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4784,10 +4784,10 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -4969,7 +4969,7 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -5527,7 +5527,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5712,7 +5712,7 @@
         <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5748,13 +5748,13 @@
         <v>415</v>
       </c>
       <c r="P23">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5894,10 +5894,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6079,7 +6079,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
@@ -6449,10 +6449,10 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
@@ -6634,10 +6634,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,10 +6819,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7007,7 +7007,7 @@
         <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7228,13 +7228,13 @@
         <v>415</v>
       </c>
       <c r="P31">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7744,7 +7744,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7932,7 +7932,7 @@
         <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -7968,13 +7968,13 @@
         <v>415</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8013,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8117,7 +8117,7 @@
         <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8299,10 +8299,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
         <v>145</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R39">
-        <v>2.65</v>
+        <v>4.18</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
@@ -9263,13 +9263,13 @@
         <v>415</v>
       </c>
       <c r="P42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9412,7 +9412,7 @@
         <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9448,13 +9448,13 @@
         <v>415</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9594,10 +9594,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9779,10 +9779,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10003,13 +10003,13 @@
         <v>415</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -10188,13 +10188,13 @@
         <v>415</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10334,10 +10334,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10519,10 +10519,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>1.77</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R49">
-        <v>3.96</v>
+        <v>2.04</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10704,10 +10704,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -11077,7 +11077,7 @@
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
@@ -11259,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11295,16 +11295,16 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11444,10 +11444,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11480,7 +11480,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11629,10 +11629,10 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11814,10 +11814,10 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11853,13 +11853,13 @@
         <v>415</v>
       </c>
       <c r="P56">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12038,13 +12038,13 @@
         <v>415</v>
       </c>
       <c r="P57">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12369,7 +12369,7 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>145</v>
@@ -12554,7 +12554,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12739,7 +12739,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13148,13 +13148,13 @@
         <v>415</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -14073,13 +14073,13 @@
         <v>415</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI68">
         <v>0</v>
@@ -14258,13 +14258,13 @@
         <v>415</v>
       </c>
       <c r="P69">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14309,10 +14309,10 @@
         <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH69">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI69">
         <v>0</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>3.57</v>
+        <v>1.57</v>
       </c>
       <c r="Q71">
-        <v>3.42</v>
+        <v>5.03</v>
       </c>
       <c r="R71">
-        <v>2.13</v>
+        <v>5.63</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14679,10 +14679,10 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14813,55 +14813,55 @@
         <v>415</v>
       </c>
       <c r="P72">
+        <v>1.99</v>
+      </c>
+      <c r="Q72">
+        <v>3.18</v>
+      </c>
+      <c r="R72">
+        <v>4</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>1.9</v>
+      </c>
+      <c r="AF72">
         <v>1.78</v>
-      </c>
-      <c r="Q72">
-        <v>3.84</v>
-      </c>
-      <c r="R72">
-        <v>4.08</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>0</v>
-      </c>
-      <c r="AE72">
-        <v>1.65</v>
-      </c>
-      <c r="AF72">
-        <v>2.1</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="Q74">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="R74">
-        <v>4.22</v>
+        <v>3.58</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF74">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="Q75">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="R75">
-        <v>3.05</v>
+        <v>4.22</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,7 +15413,7 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF75">
         <v>2.15</v>
@@ -15514,7 +15514,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>3.41</v>
+        <v>3.57</v>
       </c>
       <c r="Q76">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R76">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15699,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>1.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q77">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="R77">
-        <v>6.14</v>
+        <v>2.16</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="Q78">
-        <v>3.16</v>
+        <v>4.5</v>
       </c>
       <c r="R78">
-        <v>3.16</v>
+        <v>5</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF78">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="Q79">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R79">
-        <v>3.58</v>
+        <v>4.08</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AF79">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16254,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Q80">
-        <v>5.03</v>
+        <v>4.35</v>
       </c>
       <c r="R80">
-        <v>5.63</v>
+        <v>6.14</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16344,10 +16344,10 @@
         <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH80">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI80">
         <v>0</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q81">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="R81">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,10 +16523,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF81">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="Q82">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF82">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q83">
-        <v>4.5</v>
+        <v>3.56</v>
       </c>
       <c r="R83">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17179,10 +17179,10 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17218,13 +17218,13 @@
         <v>415</v>
       </c>
       <c r="P85">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17364,7 +17364,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
         <v>145</v>
@@ -17403,13 +17403,13 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q86">
-        <v>3.51</v>
+        <v>6.09</v>
       </c>
       <c r="R86">
-        <v>3.15</v>
+        <v>10.6</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17549,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17734,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17919,7 +17919,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18104,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18289,7 +18289,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18474,7 +18474,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
         <v>145</v>
@@ -18659,10 +18659,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18698,13 +18698,13 @@
         <v>415</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19399,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19584,10 +19584,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20509,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21622,7 +21622,7 @@
         <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21840,7 +21840,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -21992,7 +21992,7 @@
         <v>140</v>
       </c>
       <c r="D111" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22359,10 +22359,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22729,7 +22729,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D115" t="s">
         <v>145</v>
@@ -23099,7 +23099,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23284,7 +23284,7 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D118" t="s">
         <v>146</v>
@@ -23323,13 +23323,13 @@
         <v>415</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23654,10 +23654,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23839,7 +23839,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D121" t="s">
         <v>145</v>
@@ -24024,7 +24024,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D122" t="s">
         <v>145</v>
@@ -24209,7 +24209,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24248,13 +24248,13 @@
         <v>415</v>
       </c>
       <c r="P123">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -24394,10 +24394,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24579,7 +24579,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24949,7 +24949,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
         <v>146</v>
@@ -25319,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25504,10 +25504,10 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130" t="s">
         <v>275</v>
@@ -25692,7 +25692,7 @@
         <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25725,7 +25725,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25874,7 +25874,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D132" t="s">
         <v>145</v>
@@ -26059,7 +26059,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26244,7 +26244,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D134" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -319,22 +319,28 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
@@ -343,31 +349,28 @@
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
+    <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
@@ -379,9 +382,6 @@
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -394,36 +394,36 @@
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -439,18 +439,18 @@
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,142 +484,145 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>Brann W</t>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
   </si>
   <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
     <t>Molde W</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
   </si>
   <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
   </si>
   <si>
     <t>Durban City</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
     <t>Villefranche</t>
   </si>
   <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>Víkingur Reykjavík</t>
+    <t>PSV W</t>
   </si>
   <si>
     <t>PEC Zwolle W</t>
@@ -634,228 +637,225 @@
     <t>Utrecht W</t>
   </si>
   <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
     <t>NAC Breda W</t>
   </si>
   <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>PSV W</t>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Wil</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Cesena</t>
   </si>
   <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
-    <t>Virtus Entella</t>
+    <t>Pescara</t>
   </si>
   <si>
     <t>Monza</t>
   </si>
   <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Pescara</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
   </si>
   <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
   </si>
   <si>
     <t>Lens</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Athlone Town</t>
   </si>
   <si>
+    <t>Wisła Kraków</t>
+  </si>
+  <si>
+    <t>Levante UD</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
-    <t>Wisła Kraków</t>
+    <t>ÍA</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>Stjarnan</t>
   </si>
   <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -886,142 +886,145 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
     <t>Csikszereda</t>
   </si>
   <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
     <t>First Vienna</t>
   </si>
   <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>Stabæk Women</t>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
   </si>
   <si>
     <t>Liepāja</t>
   </si>
   <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
     <t>Røa Women</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
     <t>Lyn W</t>
   </si>
   <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
     <t>Admira</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Pharco</t>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
     <t>Ajaccio</t>
   </si>
   <si>
     <t>HB</t>
   </si>
   <si>
-    <t>Thór</t>
+    <t>ADO Den Haag W</t>
   </si>
   <si>
     <t>HERA</t>
@@ -1036,226 +1039,223 @@
     <t>Heerenveen W</t>
   </si>
   <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
     <t>Twente W</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
   </si>
   <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
-    <t>Carrarese</t>
+    <t>Spezia</t>
   </si>
   <si>
     <t>Empoli</t>
   </si>
   <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Spezia</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Derry City</t>
   </si>
   <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
   </si>
   <si>
     <t>Nantes</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Longford Town</t>
   </si>
   <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
     <t>Treaty United</t>
   </si>
   <si>
+    <t>Chrobry Głogów</t>
+  </si>
+  <si>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
-    <t>Chrobry Głogów</t>
+    <t>Keflavík</t>
+  </si>
+  <si>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>KR</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
     <t>Anápolis</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Almagro</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4414,7 +4414,7 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>145</v>
@@ -4453,13 +4453,13 @@
         <v>415</v>
       </c>
       <c r="P16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4599,10 +4599,10 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -4784,10 +4784,10 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -4823,13 +4823,13 @@
         <v>415</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -5563,13 +5563,13 @@
         <v>415</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5894,10 +5894,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6079,10 +6079,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6264,10 +6264,10 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -6303,13 +6303,13 @@
         <v>415</v>
       </c>
       <c r="P26">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -6634,10 +6634,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6819,7 +6819,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -7004,7 +7004,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>4.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q30">
-        <v>4.14</v>
+        <v>3.5</v>
       </c>
       <c r="R30">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7598,13 +7598,13 @@
         <v>415</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7744,10 +7744,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7783,13 +7783,13 @@
         <v>415</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -7929,10 +7929,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -7968,13 +7968,13 @@
         <v>415</v>
       </c>
       <c r="P35">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8013,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8114,7 +8114,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -8299,10 +8299,10 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -8484,10 +8484,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="Q39">
         <v>3.78</v>
       </c>
       <c r="R39">
-        <v>4.18</v>
+        <v>1.97</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -8893,13 +8893,13 @@
         <v>415</v>
       </c>
       <c r="P40">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>415</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
@@ -9409,10 +9409,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9448,13 +9448,13 @@
         <v>415</v>
       </c>
       <c r="P43">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9594,7 +9594,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
         <v>146</v>
@@ -9633,13 +9633,13 @@
         <v>415</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
         <v>145</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -10188,13 +10188,13 @@
         <v>415</v>
       </c>
       <c r="P47">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10519,10 +10519,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10704,10 +10704,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -10889,7 +10889,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -11077,7 +11077,7 @@
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
@@ -11480,7 +11480,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11632,7 +11632,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11665,7 +11665,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13148,13 +13148,13 @@
         <v>415</v>
       </c>
       <c r="P63">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13518,13 +13518,13 @@
         <v>415</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14073,13 +14073,13 @@
         <v>415</v>
       </c>
       <c r="P68">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH68">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI68">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14494,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14589,7 +14589,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Q71">
-        <v>5.03</v>
+        <v>4.35</v>
       </c>
       <c r="R71">
-        <v>5.63</v>
+        <v>6.14</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14679,10 +14679,10 @@
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH71">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI71">
         <v>0</v>
@@ -14774,7 +14774,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>3.18</v>
+        <v>3.84</v>
       </c>
       <c r="R72">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AF72">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14959,7 +14959,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q73">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R73">
-        <v>6.11</v>
+        <v>5</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>2.03</v>
+        <v>3.41</v>
       </c>
       <c r="Q74">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="R74">
-        <v>3.58</v>
+        <v>2.16</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF74">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="Q75">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="R75">
-        <v>4.22</v>
+        <v>3.58</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF75">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>3.57</v>
+        <v>1.77</v>
       </c>
       <c r="Q76">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="R76">
-        <v>2.13</v>
+        <v>4.22</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15699,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>3.41</v>
+        <v>1.99</v>
       </c>
       <c r="Q77">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R77">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AF77">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>1.55</v>
+        <v>3.57</v>
       </c>
       <c r="Q78">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="R78">
-        <v>5</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q79">
-        <v>3.84</v>
+        <v>3.16</v>
       </c>
       <c r="R79">
-        <v>4.08</v>
+        <v>3.16</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF79">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16254,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="Q80">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="R80">
-        <v>6.14</v>
+        <v>4.3</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Q81">
-        <v>3.16</v>
+        <v>5.03</v>
       </c>
       <c r="R81">
-        <v>3.16</v>
+        <v>5.63</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,16 +16523,16 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI81">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="Q82">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="R82">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AF82">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="Q83">
-        <v>3.56</v>
+        <v>4.3</v>
       </c>
       <c r="R83">
-        <v>3.05</v>
+        <v>6.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF83">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17367,7 +17367,7 @@
         <v>130</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E86" t="s">
         <v>231</v>
@@ -17403,13 +17403,13 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17549,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17919,7 +17919,7 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
         <v>146</v>
@@ -18107,7 +18107,7 @@
         <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18143,13 +18143,13 @@
         <v>415</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -18289,10 +18289,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18328,13 +18328,13 @@
         <v>415</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18474,7 +18474,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
         <v>145</v>
@@ -18513,13 +18513,13 @@
         <v>415</v>
       </c>
       <c r="P92">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="Q92">
-        <v>3.2</v>
+        <v>6.09</v>
       </c>
       <c r="R92">
-        <v>3.56</v>
+        <v>10.6</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18558,10 +18558,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -18659,10 +18659,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18698,13 +18698,13 @@
         <v>415</v>
       </c>
       <c r="P93">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19399,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19584,10 +19584,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21619,10 +21619,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21804,7 +21804,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
         <v>145</v>
@@ -21840,7 +21840,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -21989,10 +21989,10 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22174,7 +22174,7 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D112" t="s">
         <v>146</v>
@@ -22359,7 +22359,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D113" t="s">
         <v>146</v>
@@ -22729,10 +22729,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -22914,10 +22914,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="D116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23284,10 +23284,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23323,13 +23323,13 @@
         <v>415</v>
       </c>
       <c r="P118">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23654,10 +23654,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -24024,7 +24024,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D122" t="s">
         <v>145</v>
@@ -24060,7 +24060,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24209,7 +24209,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24394,10 +24394,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24579,7 +24579,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24949,7 +24949,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
         <v>146</v>
@@ -25134,10 +25134,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25319,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,7 +25689,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -25728,13 +25728,13 @@
         <v>415</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -26059,7 +26059,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26244,10 +26244,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,108 +316,108 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -475,151 +475,154 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>Terengganu</t>
+  </si>
+  <si>
     <t>PDRM</t>
   </si>
   <si>
-    <t>Terengganu</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
     <t>Fakel</t>
   </si>
   <si>
-    <t>Chayka</t>
+    <t>UTA Arad</t>
   </si>
   <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Brann W</t>
-  </si>
-  <si>
     <t>Amstetten</t>
   </si>
   <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
+    <t>Excelsior Barendrecht W</t>
   </si>
   <si>
     <t>PSV W</t>
@@ -628,78 +631,75 @@
     <t>PEC Zwolle W</t>
   </si>
   <si>
-    <t>Excelsior Barendrecht W</t>
+    <t>Utrecht W</t>
   </si>
   <si>
     <t>Ajax W</t>
   </si>
   <si>
-    <t>Utrecht W</t>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
   </si>
   <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Wil</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Aarau</t>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
     <t>Venezia</t>
   </si>
   <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
     <t>Monza</t>
   </si>
   <si>
@@ -709,34 +709,37 @@
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Drogheda United</t>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Galway United</t>
   </si>
   <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
@@ -745,7 +748,10 @@
     <t>Levante UD</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>ÍA</t>
@@ -754,12 +760,6 @@
     <t>Fram</t>
   </si>
   <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -775,46 +775,76 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
     <t>Maringá</t>
   </si>
   <si>
-    <t>Volta Redonda</t>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
   </si>
   <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Posusje</t>
   </si>
   <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Posusje</t>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
   </si>
   <si>
     <t>Domžale</t>
@@ -823,39 +853,9 @@
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
     <t>Atlético Rafaela</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -877,151 +877,154 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Imigresen</t>
+  </si>
+  <si>
     <t>Pulau Pinang</t>
   </si>
   <si>
-    <t>Imigresen</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
+    <t>Csikszereda</t>
   </si>
   <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
     <t>Austria Klagenfurt</t>
   </si>
   <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
     <t>Thór</t>
   </si>
   <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>HB</t>
+    <t>Feyenoord W</t>
   </si>
   <si>
     <t>ADO Den Haag W</t>
@@ -1030,78 +1033,75 @@
     <t>HERA</t>
   </si>
   <si>
-    <t>Feyenoord W</t>
+    <t>Heerenveen W</t>
   </si>
   <si>
     <t>AZ W</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
   </si>
   <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Stade Nyonnais</t>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
   </si>
   <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
     <t>Palermo</t>
   </si>
   <si>
     <t>Mantova</t>
   </si>
   <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
     <t>Empoli</t>
   </si>
   <si>
@@ -1111,34 +1111,37 @@
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Derry City</t>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
+    <t>Waterford</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
@@ -1147,7 +1150,10 @@
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Waterford</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>FH</t>
   </si>
   <si>
     <t>Keflavík</t>
@@ -1156,12 +1162,6 @@
     <t>Valur</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1177,46 +1177,76 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Ferroviária</t>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
   </si>
   <si>
     <t>Sarajevo</t>
   </si>
   <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Floresta</t>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Velež</t>
   </si>
   <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Velež</t>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Celje</t>
@@ -1225,37 +1255,7 @@
     <t>Defensores de Belgrano</t>
   </si>
   <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
     <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4414,7 +4414,7 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>145</v>
@@ -4602,7 +4602,7 @@
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -4972,7 +4972,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5527,7 +5527,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5563,13 +5563,13 @@
         <v>415</v>
       </c>
       <c r="P22">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5894,10 +5894,10 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -6079,7 +6079,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6118,13 +6118,13 @@
         <v>415</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6163,10 +6163,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -6449,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -6634,7 +6634,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>145</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,10 +6819,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -7004,10 +7004,10 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7228,13 +7228,13 @@
         <v>415</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7744,10 +7744,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7783,13 +7783,13 @@
         <v>415</v>
       </c>
       <c r="P34">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -7929,10 +7929,10 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -8302,7 +8302,7 @@
         <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>182</v>
@@ -8487,7 +8487,7 @@
         <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -8523,13 +8523,13 @@
         <v>415</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8568,10 +8568,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -9263,13 +9263,13 @@
         <v>415</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9409,10 +9409,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9594,10 +9594,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9633,13 +9633,13 @@
         <v>415</v>
       </c>
       <c r="P44">
+        <v>3.03</v>
+      </c>
+      <c r="Q44">
         <v>3.15</v>
       </c>
-      <c r="Q44">
-        <v>3.76</v>
-      </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9782,7 +9782,7 @@
         <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
         <v>145</v>
@@ -10003,13 +10003,13 @@
         <v>415</v>
       </c>
       <c r="P46">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -10149,10 +10149,10 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -10334,10 +10334,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>2.94</v>
+        <v>1.77</v>
       </c>
       <c r="Q48">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="R48">
-        <v>2.32</v>
+        <v>3.96</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10519,10 +10519,10 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10704,10 +10704,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -10889,10 +10889,10 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -11259,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11295,16 +11295,16 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P53">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11444,10 +11444,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11629,7 +11629,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
         <v>145</v>
@@ -11665,7 +11665,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11814,10 +11814,10 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11853,13 +11853,13 @@
         <v>415</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -12924,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13148,13 +13148,13 @@
         <v>415</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13518,13 +13518,13 @@
         <v>415</v>
       </c>
       <c r="P65">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13888,13 +13888,13 @@
         <v>415</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13939,10 +13939,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14494,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14589,7 +14589,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>1.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q71">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="R71">
-        <v>6.14</v>
+        <v>2.16</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14673,10 +14673,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="Q72">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="R72">
-        <v>4.08</v>
+        <v>3.05</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF72">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q73">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="R73">
-        <v>5</v>
+        <v>3.16</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>3.41</v>
+        <v>1.57</v>
       </c>
       <c r="Q74">
-        <v>3.22</v>
+        <v>5.03</v>
       </c>
       <c r="R74">
-        <v>2.16</v>
+        <v>5.63</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,16 +15228,16 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF74">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="Q75">
-        <v>3.38</v>
+        <v>4.35</v>
       </c>
       <c r="R75">
-        <v>3.58</v>
+        <v>6.14</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="Q76">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="R76">
-        <v>4.22</v>
+        <v>3.58</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF76">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>3.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q78">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>4.3</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>2.3</v>
+        <v>3.57</v>
       </c>
       <c r="Q79">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="R79">
-        <v>3.16</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q80">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="R80">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF80">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="Q81">
-        <v>5.03</v>
+        <v>3.84</v>
       </c>
       <c r="R81">
-        <v>5.63</v>
+        <v>4.08</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,16 +16523,16 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH81">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI81">
         <v>0</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="Q82">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="R82">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17364,7 +17364,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17552,7 +17552,7 @@
         <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17588,13 +17588,13 @@
         <v>415</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17734,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17919,10 +17919,10 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
@@ -17958,13 +17958,13 @@
         <v>415</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D90" t="s">
         <v>145</v>
@@ -18289,10 +18289,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18328,13 +18328,13 @@
         <v>415</v>
       </c>
       <c r="P91">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18474,10 +18474,10 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
@@ -18513,13 +18513,13 @@
         <v>415</v>
       </c>
       <c r="P92">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18659,7 +18659,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19399,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19584,10 +19584,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -20509,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21619,10 +21619,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21807,7 +21807,7 @@
         <v>140</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
         <v>255</v>
@@ -21989,7 +21989,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22174,7 +22174,7 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D112" t="s">
         <v>146</v>
@@ -22359,7 +22359,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D113" t="s">
         <v>146</v>
@@ -22544,10 +22544,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22729,7 +22729,7 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D115" t="s">
         <v>146</v>
@@ -22914,10 +22914,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -22953,13 +22953,13 @@
         <v>415</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23284,10 +23284,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23657,7 +23657,7 @@
         <v>140</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23842,7 +23842,7 @@
         <v>140</v>
       </c>
       <c r="D121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s">
         <v>266</v>
@@ -24024,10 +24024,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24060,7 +24060,7 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -24209,7 +24209,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24579,10 +24579,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24764,10 +24764,10 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24949,10 +24949,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25137,7 +25137,7 @@
         <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25319,10 +25319,10 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,10 +25689,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25728,13 +25728,13 @@
         <v>415</v>
       </c>
       <c r="P131">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -25910,7 +25910,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26059,7 +26059,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26244,10 +26244,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,25 +316,31 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
@@ -343,64 +349,61 @@
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
+    <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
     <t>Republic of Ireland First Division</t>
@@ -409,15 +412,12 @@
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
+    <t>Italy Serie A</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -475,54 +475,69 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
     <t>Molde W</t>
   </si>
   <si>
     <t>Trondheims-Ørn</t>
   </si>
   <si>
+    <t>Brann W</t>
+  </si>
+  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
@@ -532,49 +547,43 @@
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
     <t>Tammeka</t>
   </si>
   <si>
     <t>Anorthosis</t>
   </si>
   <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
   </si>
   <si>
     <t>HamKam</t>
@@ -583,70 +592,70 @@
     <t>Erzgebirge Aue</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
   </si>
   <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
     <t>PSV W</t>
   </si>
   <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>Rijeka</t>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Wil</t>
   </si>
   <si>
     <t>Rapperswil-Jona</t>
@@ -655,108 +664,99 @@
     <t>Aarau</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>Étoile Carouge</t>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
     <t>Südtirol</t>
   </si>
   <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Monza</t>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Torino</t>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
     <t>Levante UD</t>
   </si>
   <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>ÍA</t>
+  </si>
+  <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Fram</t>
   </si>
   <si>
@@ -766,96 +766,96 @@
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
+    <t>Itabaiana</t>
   </si>
   <si>
     <t>Maranhão</t>
   </si>
   <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
   </si>
   <si>
     <t>Orlando Pride</t>
   </si>
   <si>
-    <t>Itabaiana</t>
+    <t>Željezničar</t>
   </si>
   <si>
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -877,54 +877,69 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
     <t>Røa Women</t>
   </si>
   <si>
     <t>Bodø / Glimt W</t>
   </si>
   <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
     <t>Lyn W</t>
   </si>
   <si>
@@ -934,49 +949,43 @@
     <t>Liepāja</t>
   </si>
   <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>Kuressaare</t>
   </si>
   <si>
     <t>Digenis Ypsonas</t>
   </si>
   <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
   </si>
   <si>
     <t>Vålerenga</t>
@@ -985,70 +994,70 @@
     <t>MSV Duisburg</t>
   </si>
   <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Brage</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>HERA</t>
   </si>
   <si>
     <t>Feyenoord W</t>
   </si>
   <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
@@ -1057,108 +1066,99 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
     <t>Juve Stabia</t>
   </si>
   <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Empoli</t>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
+    <t>Kerry</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Kerry</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
     <t>CA Osasuna</t>
   </si>
   <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
+  </si>
+  <si>
     <t>KR</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -1168,94 +1168,94 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Caxias</t>
+    <t>Floresta</t>
   </si>
   <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>North Carolina Courage</t>
   </si>
   <si>
-    <t>Floresta</t>
+    <t>Sloga Doboj</t>
   </si>
   <si>
     <t>Magallanes</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3898,13 +3898,13 @@
         <v>415</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4083,13 +4083,13 @@
         <v>415</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -4268,13 +4268,13 @@
         <v>415</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4313,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -4599,7 +4599,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>145</v>
@@ -4784,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4823,13 +4823,13 @@
         <v>415</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>2.77</v>
       </c>
       <c r="Q18">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="R18">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5008,13 +5008,13 @@
         <v>415</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5563,13 +5563,13 @@
         <v>415</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5608,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5897,7 +5897,7 @@
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -5933,13 +5933,13 @@
         <v>415</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6118,13 +6118,13 @@
         <v>415</v>
       </c>
       <c r="P25">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q25">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="R25">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6163,10 +6163,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -6449,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -6634,10 +6634,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -7007,7 +7007,7 @@
         <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7228,13 +7228,13 @@
         <v>415</v>
       </c>
       <c r="P31">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7377,7 +7377,7 @@
         <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7598,13 +7598,13 @@
         <v>415</v>
       </c>
       <c r="P33">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7783,13 +7783,13 @@
         <v>415</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7929,7 +7929,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
         <v>145</v>
@@ -7968,13 +7968,13 @@
         <v>415</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8114,7 +8114,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
         <v>145</v>
@@ -8153,13 +8153,13 @@
         <v>415</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8484,10 +8484,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -8523,13 +8523,13 @@
         <v>415</v>
       </c>
       <c r="P38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8568,10 +8568,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -8893,13 +8893,13 @@
         <v>415</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q40">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>415</v>
       </c>
       <c r="P41">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9263,13 +9263,13 @@
         <v>415</v>
       </c>
       <c r="P42">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="Q42">
-        <v>3.61</v>
+        <v>3.76</v>
       </c>
       <c r="R42">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
         <v>145</v>
@@ -9594,7 +9594,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -9633,13 +9633,13 @@
         <v>415</v>
       </c>
       <c r="P44">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
         <v>145</v>
@@ -10149,7 +10149,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10188,13 +10188,13 @@
         <v>415</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10334,10 +10334,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10889,10 +10889,10 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -10928,13 +10928,13 @@
         <v>415</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11077,7 +11077,7 @@
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
         <v>197</v>
@@ -11259,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11295,16 +11295,16 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11444,10 +11444,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11480,7 +11480,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11629,10 +11629,10 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11814,10 +11814,10 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11853,13 +11853,13 @@
         <v>415</v>
       </c>
       <c r="P56">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12038,13 +12038,13 @@
         <v>415</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12739,7 +12739,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13148,13 +13148,13 @@
         <v>415</v>
       </c>
       <c r="P63">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13703,13 +13703,13 @@
         <v>415</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13888,13 +13888,13 @@
         <v>415</v>
       </c>
       <c r="P67">
-        <v>1.33</v>
+        <v>3.16</v>
       </c>
       <c r="Q67">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="R67">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13939,10 +13939,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14073,13 +14073,13 @@
         <v>415</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14258,13 +14258,13 @@
         <v>415</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14494,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>3.41</v>
+        <v>1.49</v>
       </c>
       <c r="Q71">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="R71">
-        <v>2.16</v>
+        <v>6.11</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14673,10 +14673,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AF71">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="Q72">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="R72">
-        <v>3.05</v>
+        <v>4.22</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF72">
         <v>2.15</v>
@@ -14959,7 +14959,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>2.3</v>
+        <v>3.57</v>
       </c>
       <c r="Q73">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="R73">
-        <v>3.16</v>
+        <v>2.13</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="Q74">
-        <v>5.03</v>
+        <v>3.16</v>
       </c>
       <c r="R74">
-        <v>5.63</v>
+        <v>3.16</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,16 +15228,16 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG74">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH74">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q75">
-        <v>4.35</v>
+        <v>5.03</v>
       </c>
       <c r="R75">
-        <v>6.14</v>
+        <v>5.63</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15419,10 +15419,10 @@
         <v>0</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="Q76">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="R76">
-        <v>3.58</v>
+        <v>5</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="Q77">
-        <v>3.18</v>
+        <v>3.84</v>
       </c>
       <c r="R77">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AF77">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="Q78">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="R78">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>3.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q79">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>4.3</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="Q80">
-        <v>3.78</v>
+        <v>3.18</v>
       </c>
       <c r="R80">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AF80">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q81">
-        <v>3.84</v>
+        <v>4.35</v>
       </c>
       <c r="R81">
-        <v>4.08</v>
+        <v>6.14</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,10 +16523,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>1.55</v>
+        <v>3.41</v>
       </c>
       <c r="Q82">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="R82">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>1.49</v>
+        <v>2.03</v>
       </c>
       <c r="Q83">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="R83">
-        <v>6.11</v>
+        <v>3.58</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF83">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17033,13 +17033,13 @@
         <v>415</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17179,7 +17179,7 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D85" t="s">
         <v>146</v>
@@ -17364,7 +17364,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17549,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>145</v>
@@ -17734,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17773,13 +17773,13 @@
         <v>415</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17818,10 +17818,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -17958,13 +17958,13 @@
         <v>415</v>
       </c>
       <c r="P89">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="R89">
-        <v>3.15</v>
+        <v>3.56</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18003,10 +18003,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18104,10 +18104,10 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
         <v>235</v>
@@ -18143,13 +18143,13 @@
         <v>415</v>
       </c>
       <c r="P90">
-        <v>2.37</v>
+        <v>3.88</v>
       </c>
       <c r="Q90">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R90">
-        <v>3.56</v>
+        <v>1.96</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -18289,10 +18289,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18328,13 +18328,13 @@
         <v>415</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18474,7 +18474,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18513,13 +18513,13 @@
         <v>415</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18659,7 +18659,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -19029,7 +19029,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
         <v>146</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19399,10 +19399,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19438,13 +19438,13 @@
         <v>415</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20509,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21619,10 +21619,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -22174,10 +22174,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22359,10 +22359,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22544,7 +22544,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D114" t="s">
         <v>145</v>
@@ -22729,10 +22729,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -22914,7 +22914,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -22953,13 +22953,13 @@
         <v>415</v>
       </c>
       <c r="P116">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23469,7 +23469,7 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="D119" t="s">
         <v>145</v>
@@ -23839,7 +23839,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24024,7 +24024,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D122" t="s">
         <v>146</v>
@@ -24209,7 +24209,7 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
         <v>146</v>
@@ -24394,7 +24394,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -24579,10 +24579,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24767,7 +24767,7 @@
         <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24949,10 +24949,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25134,7 +25134,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D128" t="s">
         <v>146</v>
@@ -25319,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -25355,7 +25355,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,7 +25689,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D131" t="s">
         <v>145</v>
@@ -25874,10 +25874,10 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -25910,16 +25910,16 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26059,10 +26059,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26244,7 +26244,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,72 +316,72 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
+    <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -394,24 +394,24 @@
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
@@ -436,6 +436,9 @@
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -448,9 +451,6 @@
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>Terengganu</t>
+  </si>
+  <si>
     <t>PDRM</t>
   </si>
   <si>
-    <t>Terengganu</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
@@ -496,366 +496,366 @@
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
     <t>Fakel</t>
   </si>
   <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
     <t>Austria Salzburg</t>
   </si>
   <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
     <t>Kapfenberger SV</t>
   </si>
   <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
   </si>
   <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>Villefranche</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
     <t>NAC Breda W</t>
   </si>
   <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>Utrecht W</t>
+    <t>Olympique Dcheïra</t>
   </si>
   <si>
     <t>PSV W</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Aarau</t>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Cesena</t>
   </si>
   <si>
     <t>Monza</t>
   </si>
   <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
     <t>Cádiz</t>
   </si>
   <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
     <t>Venezia</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Cesena</t>
+    <t>Südtirol</t>
   </si>
   <si>
     <t>Virtus Entella</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>Drogheda United</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
+    <t>Dundalk</t>
   </si>
   <si>
     <t>Torino</t>
   </si>
   <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
+    <t>Levante UD</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>ÍA</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
     <t>Barra do Garcas</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
+    <t>Puerto Montt</t>
   </si>
   <si>
     <t>Loznica</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -877,12 +877,12 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Imigresen</t>
+  </si>
+  <si>
     <t>Pulau Pinang</t>
   </si>
   <si>
-    <t>Imigresen</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -898,364 +898,364 @@
     <t>Arda</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
     <t>Austria Lustenau</t>
   </si>
   <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
     <t>Austria Wien II</t>
   </si>
   <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
     <t>St. Pölten</t>
   </si>
   <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Ajaccio</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
     <t>Twente W</t>
   </si>
   <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>Heerenveen W</t>
+    <t>Yacoub El Mansour</t>
   </si>
   <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
   </si>
   <si>
     <t>Empoli</t>
   </si>
   <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
     <t>Deportivo La Coruña</t>
   </si>
   <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
     <t>Palermo</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
+    <t>Juve Stabia</t>
   </si>
   <si>
     <t>Carrarese</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Kerry</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
+    <t>Bohemians</t>
   </si>
   <si>
     <t>Sassuolo</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
     <t>Keflavík</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
     <t>Caxias</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
+    <t>Magallanes</t>
   </si>
   <si>
     <t>Mačva Šabac</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>Floresta</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4268,13 +4268,13 @@
         <v>415</v>
       </c>
       <c r="P15">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="Q15">
-        <v>4.86</v>
+        <v>3.44</v>
       </c>
       <c r="R15">
-        <v>9.25</v>
+        <v>3.75</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4313,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>161</v>
@@ -4638,13 +4638,13 @@
         <v>415</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4823,13 +4823,13 @@
         <v>415</v>
       </c>
       <c r="P18">
-        <v>2.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q18">
-        <v>3.36</v>
+        <v>4.86</v>
       </c>
       <c r="R18">
-        <v>2.42</v>
+        <v>9.25</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -4868,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5008,13 +5008,13 @@
         <v>415</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5563,13 +5563,13 @@
         <v>415</v>
       </c>
       <c r="P22">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5608,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5897,7 +5897,7 @@
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -5933,13 +5933,13 @@
         <v>415</v>
       </c>
       <c r="P24">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6118,13 +6118,13 @@
         <v>415</v>
       </c>
       <c r="P25">
-        <v>2.63</v>
+        <v>4.04</v>
       </c>
       <c r="Q25">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -6303,13 +6303,13 @@
         <v>415</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -6637,7 +6637,7 @@
         <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -7004,7 +7004,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q30">
         <v>3.78</v>
       </c>
       <c r="R30">
-        <v>1.97</v>
+        <v>4.18</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7374,7 +7374,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7598,13 +7598,13 @@
         <v>415</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7643,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -7744,10 +7744,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7783,13 +7783,13 @@
         <v>415</v>
       </c>
       <c r="P34">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7929,7 +7929,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
         <v>145</v>
@@ -7968,13 +7968,13 @@
         <v>415</v>
       </c>
       <c r="P35">
-        <v>4.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q35">
-        <v>4.14</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8013,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8153,13 +8153,13 @@
         <v>415</v>
       </c>
       <c r="P36">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R36">
-        <v>4.19</v>
+        <v>6.17</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>1.76</v>
+        <v>3.57</v>
       </c>
       <c r="Q37">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="R37">
-        <v>4.18</v>
+        <v>1.99</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -8484,10 +8484,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -8523,13 +8523,13 @@
         <v>415</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>1.87</v>
+        <v>4.78</v>
       </c>
       <c r="Q39">
-        <v>3.33</v>
+        <v>4.14</v>
       </c>
       <c r="R39">
-        <v>3.78</v>
+        <v>1.57</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -8893,13 +8893,13 @@
         <v>415</v>
       </c>
       <c r="P40">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>415</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
@@ -9263,13 +9263,13 @@
         <v>415</v>
       </c>
       <c r="P42">
-        <v>3.15</v>
+        <v>1.77</v>
       </c>
       <c r="Q42">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>3.96</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9409,10 +9409,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9779,7 +9779,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
         <v>145</v>
@@ -10149,7 +10149,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D47" t="s">
         <v>145</v>
@@ -10188,13 +10188,13 @@
         <v>415</v>
       </c>
       <c r="P47">
-        <v>1.77</v>
+        <v>3.03</v>
       </c>
       <c r="Q47">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R47">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10334,10 +10334,10 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>193</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10743,13 +10743,13 @@
         <v>415</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10889,10 +10889,10 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -10928,13 +10928,13 @@
         <v>415</v>
       </c>
       <c r="P51">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11259,7 +11259,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
         <v>145</v>
@@ -11447,7 +11447,7 @@
         <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>199</v>
@@ -11480,7 +11480,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11817,7 +11817,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -11850,7 +11850,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12739,7 +12739,7 @@
         <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -12924,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13703,13 +13703,13 @@
         <v>415</v>
       </c>
       <c r="P66">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="Q66">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="R66">
-        <v>5.11</v>
+        <v>6.5</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13754,10 +13754,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -13888,13 +13888,13 @@
         <v>415</v>
       </c>
       <c r="P67">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="Q67">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14073,13 +14073,13 @@
         <v>415</v>
       </c>
       <c r="P68">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="R68">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14258,13 +14258,13 @@
         <v>415</v>
       </c>
       <c r="P69">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="Q69">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="R69">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Q70">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="R70">
-        <v>6.5</v>
+        <v>5.11</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14494,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14589,7 +14589,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q71">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="R71">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14673,10 +14673,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="Q72">
-        <v>3.78</v>
+        <v>5.03</v>
       </c>
       <c r="R72">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,16 +14858,16 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH72">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI72">
         <v>0</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>3.57</v>
+        <v>2.18</v>
       </c>
       <c r="Q73">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="R73">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>2.3</v>
+        <v>3.41</v>
       </c>
       <c r="Q74">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="R74">
-        <v>3.16</v>
+        <v>2.16</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF74">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="Q75">
-        <v>5.03</v>
+        <v>3.78</v>
       </c>
       <c r="R75">
-        <v>5.63</v>
+        <v>4.22</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,16 +15413,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG75">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15699,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q77">
-        <v>3.84</v>
+        <v>3.16</v>
       </c>
       <c r="R77">
-        <v>4.08</v>
+        <v>3.16</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF77">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="Q78">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="R78">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF78">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="Q79">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R79">
-        <v>4.3</v>
+        <v>6.11</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16254,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>1.99</v>
+        <v>3.57</v>
       </c>
       <c r="Q80">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="R80">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q81">
-        <v>4.35</v>
+        <v>3.84</v>
       </c>
       <c r="R81">
-        <v>6.14</v>
+        <v>4.08</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,10 +16523,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="Q82">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="R82">
-        <v>2.16</v>
+        <v>3.58</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF82">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="Q83">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="R83">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF83">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -16997,7 +16997,7 @@
         <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
@@ -17033,13 +17033,13 @@
         <v>415</v>
       </c>
       <c r="P84">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="Q84">
-        <v>3.18</v>
+        <v>6.09</v>
       </c>
       <c r="R84">
-        <v>2.35</v>
+        <v>10.6</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17364,7 +17364,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17403,13 +17403,13 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17549,10 +17549,10 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
         <v>232</v>
@@ -17588,13 +17588,13 @@
         <v>415</v>
       </c>
       <c r="P87">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17734,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>146</v>
@@ -17919,10 +17919,10 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
@@ -17958,13 +17958,13 @@
         <v>415</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18003,10 +18003,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18143,13 +18143,13 @@
         <v>415</v>
       </c>
       <c r="P90">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18289,10 +18289,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18328,13 +18328,13 @@
         <v>415</v>
       </c>
       <c r="P91">
-        <v>2.25</v>
+        <v>3.11</v>
       </c>
       <c r="Q91">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="R91">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18474,10 +18474,10 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
@@ -18513,13 +18513,13 @@
         <v>415</v>
       </c>
       <c r="P92">
-        <v>3.11</v>
+        <v>2.37</v>
       </c>
       <c r="Q92">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R92">
-        <v>2.24</v>
+        <v>3.56</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18558,10 +18558,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -18659,10 +18659,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18698,13 +18698,13 @@
         <v>415</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -18883,13 +18883,13 @@
         <v>415</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19253,13 +19253,13 @@
         <v>415</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -19399,10 +19399,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19438,13 +19438,13 @@
         <v>415</v>
       </c>
       <c r="P97">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19584,10 +19584,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -19623,13 +19623,13 @@
         <v>415</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21619,10 +21619,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21655,7 +21655,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -21989,7 +21989,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22174,10 +22174,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22359,10 +22359,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22398,13 +22398,13 @@
         <v>415</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -22544,10 +22544,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22729,10 +22729,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -22914,7 +22914,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D116" t="s">
         <v>146</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23654,10 +23654,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23839,7 +23839,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24024,10 +24024,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24209,10 +24209,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24394,10 +24394,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24579,10 +24579,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24803,13 +24803,13 @@
         <v>415</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -24949,10 +24949,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25134,7 +25134,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D128" t="s">
         <v>146</v>
@@ -25319,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -25355,7 +25355,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,10 +25689,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25874,7 +25874,7 @@
         <v>88</v>
       </c>
       <c r="C132" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
         <v>146</v>
@@ -25913,13 +25913,13 @@
         <v>415</v>
       </c>
       <c r="P132">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26059,7 +26059,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="D133" t="s">
         <v>145</v>
@@ -26244,7 +26244,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D134" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -316,69 +316,69 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>France National</t>
   </si>
   <si>
@@ -403,21 +403,21 @@
     <t>Spain Segunda División</t>
   </si>
   <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -475,39 +475,39 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Toronto II</t>
   </si>
   <si>
@@ -517,190 +517,220 @@
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
     <t>Brann W</t>
   </si>
   <si>
     <t>Hønefoss Women</t>
   </si>
   <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
   </si>
   <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
     <t>Viborg</t>
   </si>
   <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Varberg</t>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Durban City</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
     <t>Villefranche</t>
   </si>
   <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>PSV W</t>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
     <t>Pescara</t>
   </si>
   <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
   </si>
   <si>
     <t>Lens</t>
@@ -709,34 +739,7 @@
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Cork City</t>
+    <t>St Patrick's Athl.</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
@@ -745,117 +748,114 @@
     <t>Levante UD</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>ÍA</t>
+  </si>
+  <si>
+    <t>Fram</t>
   </si>
   <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>Domžale</t>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
   </si>
   <si>
     <t>Volta Redonda</t>
   </si>
   <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -877,39 +877,39 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
     <t>New York RB II</t>
   </si>
   <si>
@@ -919,190 +919,220 @@
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
     <t>Lyn W</t>
   </si>
   <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
     <t>Vålerenga Women</t>
   </si>
   <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
   </si>
   <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
     <t>Pharco</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>HB</t>
-  </si>
-  <si>
     <t>Ajaccio</t>
   </si>
   <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>ADO Den Haag W</t>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
     <t>Spezia</t>
   </si>
   <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
   </si>
   <si>
     <t>Nantes</t>
@@ -1111,34 +1141,7 @@
     <t>Kerry</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>UCD</t>
+    <t>Waterford</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
@@ -1147,115 +1150,112 @@
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Waterford</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
+  </si>
+  <si>
+    <t>Valur</t>
   </si>
   <si>
     <t>FH</t>
   </si>
   <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
     <t>Confiança</t>
   </si>
   <si>
-    <t>Celje</t>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Caxias</t>
   </si>
   <si>
     <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Floresta</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4268,13 +4268,13 @@
         <v>415</v>
       </c>
       <c r="P15">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="Q15">
-        <v>3.44</v>
+        <v>4.86</v>
       </c>
       <c r="R15">
-        <v>3.75</v>
+        <v>9.25</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4313,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -4638,13 +4638,13 @@
         <v>415</v>
       </c>
       <c r="P17">
-        <v>2.77</v>
+        <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="R17">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4823,13 +4823,13 @@
         <v>415</v>
       </c>
       <c r="P18">
-        <v>1.36</v>
+        <v>2.77</v>
       </c>
       <c r="Q18">
-        <v>4.86</v>
+        <v>3.36</v>
       </c>
       <c r="R18">
-        <v>9.25</v>
+        <v>2.42</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -4868,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG18">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>167</v>
@@ -5563,13 +5563,13 @@
         <v>415</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5608,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5897,7 +5897,7 @@
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
         <v>169</v>
@@ -5933,13 +5933,13 @@
         <v>415</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6264,10 +6264,10 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -6303,13 +6303,13 @@
         <v>415</v>
       </c>
       <c r="P26">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R26">
-        <v>4.19</v>
+        <v>6.17</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
@@ -6488,13 +6488,13 @@
         <v>415</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -7004,7 +7004,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q30">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R30">
-        <v>4.18</v>
+        <v>2.65</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -7377,7 +7377,7 @@
         <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7413,13 +7413,13 @@
         <v>415</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7598,13 +7598,13 @@
         <v>415</v>
       </c>
       <c r="P33">
-        <v>1.87</v>
+        <v>4.78</v>
       </c>
       <c r="Q33">
-        <v>3.33</v>
+        <v>4.14</v>
       </c>
       <c r="R33">
-        <v>3.78</v>
+        <v>1.57</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7643,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -7744,7 +7744,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -7932,7 +7932,7 @@
         <v>106</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
         <v>180</v>
@@ -7968,13 +7968,13 @@
         <v>415</v>
       </c>
       <c r="P35">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8013,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8114,7 +8114,7 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -8153,13 +8153,13 @@
         <v>415</v>
       </c>
       <c r="P36">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>3.57</v>
+        <v>1.87</v>
       </c>
       <c r="Q37">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="R37">
-        <v>1.99</v>
+        <v>3.78</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AF37">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -8484,10 +8484,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
         <v>183</v>
@@ -8523,13 +8523,13 @@
         <v>415</v>
       </c>
       <c r="P38">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>4.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q39">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R39">
-        <v>1.57</v>
+        <v>4.18</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8893,13 +8893,13 @@
         <v>415</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q40">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>415</v>
       </c>
       <c r="P41">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9594,10 +9594,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9633,13 +9633,13 @@
         <v>415</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -9964,7 +9964,7 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
         <v>145</v>
@@ -10149,10 +10149,10 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
         <v>192</v>
@@ -10188,13 +10188,13 @@
         <v>415</v>
       </c>
       <c r="P47">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="Q47">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10707,7 +10707,7 @@
         <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -10743,13 +10743,13 @@
         <v>415</v>
       </c>
       <c r="P50">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10889,10 +10889,10 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>196</v>
@@ -11074,7 +11074,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11113,13 +11113,13 @@
         <v>415</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -11259,10 +11259,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11298,13 +11298,13 @@
         <v>415</v>
       </c>
       <c r="P53">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="Q53">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="R53">
-        <v>5.46</v>
+        <v>10.6</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11632,7 +11632,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11999,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
         <v>145</v>
@@ -12038,13 +12038,13 @@
         <v>415</v>
       </c>
       <c r="P57">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12924,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13518,13 +13518,13 @@
         <v>415</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13703,13 +13703,13 @@
         <v>415</v>
       </c>
       <c r="P66">
-        <v>1.33</v>
+        <v>2.96</v>
       </c>
       <c r="Q66">
-        <v>4.75</v>
+        <v>3.28</v>
       </c>
       <c r="R66">
-        <v>6.5</v>
+        <v>2.19</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13754,10 +13754,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH66">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -13888,13 +13888,13 @@
         <v>415</v>
       </c>
       <c r="P67">
-        <v>2.96</v>
+        <v>1.49</v>
       </c>
       <c r="Q67">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
       <c r="R67">
-        <v>2.19</v>
+        <v>5.11</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="Q70">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="R70">
-        <v>5.11</v>
+        <v>6.5</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14494,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14589,7 +14589,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="Q73">
-        <v>3.56</v>
+        <v>3.18</v>
       </c>
       <c r="R73">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF73">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>3.41</v>
+        <v>1.49</v>
       </c>
       <c r="Q74">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="R74">
-        <v>2.16</v>
+        <v>6.11</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AF74">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="Q75">
-        <v>3.78</v>
+        <v>3.16</v>
       </c>
       <c r="R75">
-        <v>4.22</v>
+        <v>3.16</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF75">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q76">
-        <v>4.5</v>
+        <v>3.56</v>
       </c>
       <c r="R76">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q77">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="R77">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF77">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q78">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="R78">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q79">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R79">
-        <v>6.11</v>
+        <v>5</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16254,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>3.57</v>
+        <v>2.03</v>
       </c>
       <c r="Q80">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R80">
-        <v>2.13</v>
+        <v>3.58</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q81">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="R81">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,10 +16523,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF81">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>2.03</v>
+        <v>3.57</v>
       </c>
       <c r="Q82">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R82">
-        <v>3.58</v>
+        <v>2.13</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>1.99</v>
+        <v>3.41</v>
       </c>
       <c r="Q83">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="R83">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AF83">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -16997,7 +16997,7 @@
         <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
@@ -17033,13 +17033,13 @@
         <v>415</v>
       </c>
       <c r="P84">
-        <v>1.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q84">
-        <v>6.09</v>
+        <v>3.15</v>
       </c>
       <c r="R84">
-        <v>10.6</v>
+        <v>2.7</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17218,13 +17218,13 @@
         <v>415</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17364,7 +17364,7 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>146</v>
@@ -17403,13 +17403,13 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="Q86">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R86">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17549,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17588,13 +17588,13 @@
         <v>415</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17737,7 +17737,7 @@
         <v>131</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -17773,13 +17773,13 @@
         <v>415</v>
       </c>
       <c r="P88">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q88">
-        <v>4.15</v>
+        <v>3.51</v>
       </c>
       <c r="R88">
-        <v>6.26</v>
+        <v>3.15</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17818,10 +17818,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -17919,10 +17919,10 @@
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E89" t="s">
         <v>234</v>
@@ -17958,13 +17958,13 @@
         <v>415</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18003,10 +18003,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18143,13 +18143,13 @@
         <v>415</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18289,7 +18289,7 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
         <v>146</v>
@@ -18474,10 +18474,10 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E92" t="s">
         <v>237</v>
@@ -18513,13 +18513,13 @@
         <v>415</v>
       </c>
       <c r="P92">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="Q92">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R92">
-        <v>3.56</v>
+        <v>6.78</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18558,10 +18558,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -18659,10 +18659,10 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
         <v>238</v>
@@ -18698,13 +18698,13 @@
         <v>415</v>
       </c>
       <c r="P93">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q93">
-        <v>3.51</v>
+        <v>4.15</v>
       </c>
       <c r="R93">
-        <v>3.15</v>
+        <v>6.26</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -18844,10 +18844,10 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
         <v>239</v>
@@ -18883,13 +18883,13 @@
         <v>415</v>
       </c>
       <c r="P94">
-        <v>3.88</v>
+        <v>1.32</v>
       </c>
       <c r="Q94">
-        <v>3.34</v>
+        <v>6.09</v>
       </c>
       <c r="R94">
-        <v>1.96</v>
+        <v>10.6</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19029,7 +19029,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D95" t="s">
         <v>146</v>
@@ -19068,13 +19068,13 @@
         <v>415</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19253,13 +19253,13 @@
         <v>415</v>
       </c>
       <c r="P96">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Q96">
-        <v>4.5</v>
+        <v>5.95</v>
       </c>
       <c r="R96">
-        <v>7.06</v>
+        <v>11.5</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -19399,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
         <v>145</v>
@@ -19438,13 +19438,13 @@
         <v>415</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19584,10 +19584,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -19623,13 +19623,13 @@
         <v>415</v>
       </c>
       <c r="P98">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19808,13 +19808,13 @@
         <v>415</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -19993,13 +19993,13 @@
         <v>415</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20178,13 +20178,13 @@
         <v>415</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI101">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20363,13 +20363,13 @@
         <v>415</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -20414,10 +20414,10 @@
         <v>0</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH102">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI102">
         <v>0</v>
@@ -20733,13 +20733,13 @@
         <v>415</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -20778,10 +20778,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21655,7 +21655,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -22174,7 +22174,7 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D112" t="s">
         <v>146</v>
@@ -22359,10 +22359,10 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
         <v>258</v>
@@ -22395,16 +22395,16 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P113">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R113">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -22544,7 +22544,7 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D114" t="s">
         <v>146</v>
@@ -22583,13 +22583,13 @@
         <v>415</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -22914,10 +22914,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23099,7 +23099,7 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s">
         <v>146</v>
@@ -23284,10 +23284,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23654,10 +23654,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23839,7 +23839,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24024,7 +24024,7 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="D122" t="s">
         <v>145</v>
@@ -24209,10 +24209,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24394,10 +24394,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24579,10 +24579,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24803,13 +24803,13 @@
         <v>415</v>
       </c>
       <c r="P126">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R126">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -24949,7 +24949,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D127" t="s">
         <v>145</v>
@@ -25134,10 +25134,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25319,10 +25319,10 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,10 +25689,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25913,13 +25913,13 @@
         <v>415</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26059,10 +26059,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26244,7 +26244,7 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
         <v>146</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,24 +310,24 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
@@ -337,93 +337,93 @@
     <t>Norway Toppserien</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Italy Serie B</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie B</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>France Ligue 1</t>
+    <t>Spain La Liga</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,24 +433,24 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Ecuador Primera Categoría Serie A</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>Ecuador Primera Categoría Serie A</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -490,27 +490,27 @@
     <t>Petrojet</t>
   </si>
   <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
+    <t>Chayka</t>
   </si>
   <si>
     <t>Fakel</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -520,187 +520,193 @@
     <t>Austria Salzburg</t>
   </si>
   <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>Liefering</t>
   </si>
   <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
     <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
+    <t>Villefranche</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
-    <t>Villefranche</t>
-  </si>
-  <si>
     <t>PSV W</t>
   </si>
   <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
     <t>Utrecht W</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
   </si>
   <si>
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
-  </si>
-  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Aarau</t>
   </si>
   <si>
     <t>Wil</t>
   </si>
   <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Aarau</t>
+    <t>Reggiana</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
     <t>Virtus Entella</t>
   </si>
   <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
     <t>Pescara</t>
   </si>
   <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Torino</t>
   </si>
   <si>
     <t>Athlone Town</t>
@@ -712,51 +718,45 @@
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
+    <t>Levante UD</t>
+  </si>
+  <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
-    <t>Levante UD</t>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>ÍA</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -766,96 +766,96 @@
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
   </si>
   <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
     <t>Voždovac</t>
   </si>
   <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -892,27 +892,27 @@
     <t>Wadi Degla</t>
   </si>
   <si>
+    <t>Arda</t>
+  </si>
+  <si>
     <t>Riga</t>
   </si>
   <si>
-    <t>Arda</t>
+    <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
     <t>Trajal Krusevac</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
@@ -922,187 +922,193 @@
     <t>Austria Lustenau</t>
   </si>
   <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Lyn W</t>
   </si>
   <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
     <t>Admira</t>
   </si>
   <si>
     <t>First Vienna</t>
   </si>
   <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
     <t>Liepāja</t>
   </si>
   <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
-  </si>
-  <si>
-    <t>Pharco</t>
+    <t>Ajaccio</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
+    <t>HB</t>
+  </si>
+  <si>
     <t>Thór</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Ajaccio</t>
-  </si>
-  <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
     <t>Heerenveen W</t>
   </si>
   <si>
-    <t>Twente W</t>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>HERA</t>
   </si>
   <si>
     <t>Feyenoord W</t>
   </si>
   <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>AZ W</t>
-  </si>
-  <si>
     <t>HNK Vukovar 1991</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
+    <t>Stade Nyonnais</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
+    <t>Sampdoria</t>
   </si>
   <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
     <t>Eintracht Frankfurt</t>
   </si>
   <si>
     <t>Carrarese</t>
   </si>
   <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
     <t>Spezia</t>
   </si>
   <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
   </si>
   <si>
     <t>Treaty United</t>
@@ -1114,51 +1120,45 @@
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Longford Town</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
     <t>Waterford</t>
   </si>
   <si>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
@@ -1168,94 +1168,94 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
   </si>
   <si>
     <t>Almagro</t>
   </si>
   <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
     <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3862,7 +3862,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -3898,13 +3898,13 @@
         <v>415</v>
       </c>
       <c r="P13">
-        <v>8.75</v>
+        <v>2.47</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>1.29</v>
+        <v>3.11</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4083,13 +4083,13 @@
         <v>415</v>
       </c>
       <c r="P14">
-        <v>2.47</v>
+        <v>8.75</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>3.11</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -4268,13 +4268,13 @@
         <v>415</v>
       </c>
       <c r="P15">
-        <v>1.36</v>
+        <v>2.77</v>
       </c>
       <c r="Q15">
-        <v>4.86</v>
+        <v>3.36</v>
       </c>
       <c r="R15">
-        <v>9.25</v>
+        <v>2.42</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4313,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>145</v>
@@ -4453,13 +4453,13 @@
         <v>415</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4498,10 +4498,10 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
         <v>0</v>
@@ -4599,10 +4599,10 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -4638,13 +4638,13 @@
         <v>415</v>
       </c>
       <c r="P17">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4823,13 +4823,13 @@
         <v>415</v>
       </c>
       <c r="P18">
-        <v>2.77</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="R18">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
@@ -5709,10 +5709,10 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>168</v>
@@ -5748,13 +5748,13 @@
         <v>415</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5793,10 +5793,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -5933,13 +5933,13 @@
         <v>415</v>
       </c>
       <c r="P24">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q24">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="R24">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6079,10 +6079,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6118,13 +6118,13 @@
         <v>415</v>
       </c>
       <c r="P25">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -6303,13 +6303,13 @@
         <v>415</v>
       </c>
       <c r="P26">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>145</v>
@@ -6488,55 +6488,55 @@
         <v>415</v>
       </c>
       <c r="P27">
+        <v>1.87</v>
+      </c>
+      <c r="Q27">
+        <v>3.33</v>
+      </c>
+      <c r="R27">
+        <v>3.78</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>1.92</v>
+      </c>
+      <c r="AF27">
         <v>1.76</v>
-      </c>
-      <c r="Q27">
-        <v>3.75</v>
-      </c>
-      <c r="R27">
-        <v>4.19</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -6819,10 +6819,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -6858,13 +6858,13 @@
         <v>415</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>2.4</v>
+        <v>4.78</v>
       </c>
       <c r="Q30">
-        <v>3.5</v>
+        <v>4.14</v>
       </c>
       <c r="R30">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7374,10 +7374,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7413,13 +7413,13 @@
         <v>415</v>
       </c>
       <c r="P32">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7598,13 +7598,13 @@
         <v>415</v>
       </c>
       <c r="P33">
-        <v>4.78</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R33">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7643,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -7744,10 +7744,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7783,13 +7783,13 @@
         <v>415</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8299,7 +8299,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="Q37">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="R37">
-        <v>3.78</v>
+        <v>4.19</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -8669,10 +8669,10 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
         <v>184</v>
@@ -8708,13 +8708,13 @@
         <v>415</v>
       </c>
       <c r="P39">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="Q39">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="R39">
-        <v>4.18</v>
+        <v>6.17</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -9263,13 +9263,13 @@
         <v>415</v>
       </c>
       <c r="P42">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9409,10 +9409,10 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>188</v>
@@ -9448,13 +9448,13 @@
         <v>415</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9594,10 +9594,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9633,13 +9633,13 @@
         <v>415</v>
       </c>
       <c r="P44">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10003,13 +10003,13 @@
         <v>415</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -10188,13 +10188,13 @@
         <v>415</v>
       </c>
       <c r="P47">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10704,10 +10704,10 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>195</v>
@@ -10889,7 +10889,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10928,13 +10928,13 @@
         <v>415</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11074,7 +11074,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
         <v>145</v>
@@ -11110,16 +11110,16 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P52">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -11259,10 +11259,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11298,13 +11298,13 @@
         <v>415</v>
       </c>
       <c r="P53">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Q53">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R53">
-        <v>10.6</v>
+        <v>5.46</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11632,7 +11632,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11668,13 +11668,13 @@
         <v>415</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -11850,7 +11850,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12554,7 +12554,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12924,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -12963,13 +12963,13 @@
         <v>415</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13479,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
         <v>145</v>
@@ -13518,13 +13518,13 @@
         <v>415</v>
       </c>
       <c r="P65">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13703,13 +13703,13 @@
         <v>415</v>
       </c>
       <c r="P66">
-        <v>2.96</v>
+        <v>1.33</v>
       </c>
       <c r="Q66">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="R66">
-        <v>2.19</v>
+        <v>6.5</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13754,10 +13754,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -13888,13 +13888,13 @@
         <v>415</v>
       </c>
       <c r="P67">
-        <v>1.49</v>
+        <v>2.96</v>
       </c>
       <c r="Q67">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R67">
-        <v>5.11</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Q70">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="R70">
-        <v>6.5</v>
+        <v>5.11</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14494,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI70">
         <v>0</v>
@@ -14589,7 +14589,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>145</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>1.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q71">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="R71">
-        <v>6.14</v>
+        <v>2.16</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14673,10 +14673,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14774,7 +14774,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Q72">
-        <v>5.03</v>
+        <v>4.35</v>
       </c>
       <c r="R72">
-        <v>5.63</v>
+        <v>6.14</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14864,10 +14864,10 @@
         <v>0</v>
       </c>
       <c r="AG72">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH72">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI72">
         <v>0</v>
@@ -14959,7 +14959,7 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
         <v>145</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>1.99</v>
+        <v>1.49</v>
       </c>
       <c r="Q73">
-        <v>3.18</v>
+        <v>4.3</v>
       </c>
       <c r="R73">
-        <v>4</v>
+        <v>6.11</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF73">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
         <v>145</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="Q74">
+        <v>3.75</v>
+      </c>
+      <c r="R74">
         <v>4.3</v>
-      </c>
-      <c r="R74">
-        <v>6.11</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>2.3</v>
+        <v>3.57</v>
       </c>
       <c r="Q75">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="R75">
-        <v>3.16</v>
+        <v>2.13</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,10 +15413,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
         <v>145</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="Q76">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="R76">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15699,7 +15699,7 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
         <v>145</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q77">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="R77">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF77">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
         <v>145</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="Q78">
-        <v>3.84</v>
+        <v>3.38</v>
       </c>
       <c r="R78">
-        <v>4.08</v>
+        <v>3.58</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF78">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16069,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
         <v>145</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q79">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="R79">
-        <v>5</v>
+        <v>4.08</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16254,7 +16254,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
         <v>145</v>
@@ -16293,13 +16293,13 @@
         <v>415</v>
       </c>
       <c r="P80">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="Q80">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="R80">
-        <v>3.58</v>
+        <v>4.22</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16338,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AF80">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="Q81">
-        <v>3.78</v>
+        <v>5.03</v>
       </c>
       <c r="R81">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,16 +16523,16 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI81">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>3.57</v>
+        <v>1.99</v>
       </c>
       <c r="Q82">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="R82">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>3.41</v>
+        <v>2.18</v>
       </c>
       <c r="Q83">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="R83">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
+        <v>1.61</v>
+      </c>
+      <c r="AF83">
         <v>2.15</v>
-      </c>
-      <c r="AF83">
-        <v>1.61</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17033,13 +17033,13 @@
         <v>415</v>
       </c>
       <c r="P84">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q84">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R84">
-        <v>2.7</v>
+        <v>6.78</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17182,7 +17182,7 @@
         <v>130</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17218,13 +17218,13 @@
         <v>415</v>
       </c>
       <c r="P85">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="Q85">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R85">
-        <v>1.96</v>
+        <v>3.56</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17263,10 +17263,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -17403,10 +17403,10 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="Q86">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R86">
         <v>2.7</v>
@@ -17549,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17588,13 +17588,13 @@
         <v>415</v>
       </c>
       <c r="P87">
-        <v>1.85</v>
+        <v>3.88</v>
       </c>
       <c r="Q87">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="R87">
-        <v>3.79</v>
+        <v>1.96</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17734,10 +17734,10 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -17773,13 +17773,13 @@
         <v>415</v>
       </c>
       <c r="P88">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q88">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="R88">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17958,13 +17958,13 @@
         <v>415</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="Q89">
-        <v>3.2</v>
+        <v>6.09</v>
       </c>
       <c r="R89">
-        <v>3.56</v>
+        <v>10.6</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18003,10 +18003,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18143,13 +18143,13 @@
         <v>415</v>
       </c>
       <c r="P90">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="Q90">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="R90">
-        <v>2.35</v>
+        <v>6.26</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -18289,10 +18289,10 @@
         <v>81</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18328,13 +18328,13 @@
         <v>415</v>
       </c>
       <c r="P91">
-        <v>3.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q91">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="R91">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18474,7 +18474,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18513,13 +18513,13 @@
         <v>415</v>
       </c>
       <c r="P92">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="Q92">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="R92">
-        <v>6.78</v>
+        <v>2.35</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18659,7 +18659,7 @@
         <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
         <v>146</v>
@@ -18698,13 +18698,13 @@
         <v>415</v>
       </c>
       <c r="P93">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="Q93">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="R93">
-        <v>6.26</v>
+        <v>2.99</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -18844,10 +18844,10 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
         <v>239</v>
@@ -18883,13 +18883,13 @@
         <v>415</v>
       </c>
       <c r="P94">
-        <v>1.32</v>
+        <v>3.11</v>
       </c>
       <c r="Q94">
-        <v>6.09</v>
+        <v>3.34</v>
       </c>
       <c r="R94">
-        <v>10.6</v>
+        <v>2.24</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19068,13 +19068,13 @@
         <v>415</v>
       </c>
       <c r="P95">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="Q95">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R95">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19214,7 +19214,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
         <v>146</v>
@@ -19438,13 +19438,13 @@
         <v>415</v>
       </c>
       <c r="P97">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19623,13 +19623,13 @@
         <v>415</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -19769,7 +19769,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
         <v>146</v>
@@ -19808,13 +19808,13 @@
         <v>415</v>
       </c>
       <c r="P99">
-        <v>3.13</v>
+        <v>1.98</v>
       </c>
       <c r="Q99">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="R99">
-        <v>1.94</v>
+        <v>3.11</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -19859,10 +19859,10 @@
         <v>0</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH99">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI99">
         <v>0</v>
@@ -19954,7 +19954,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D100" t="s">
         <v>146</v>
@@ -20139,7 +20139,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D101" t="s">
         <v>146</v>
@@ -20178,13 +20178,13 @@
         <v>415</v>
       </c>
       <c r="P101">
-        <v>1.98</v>
+        <v>3.13</v>
       </c>
       <c r="Q101">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="R101">
-        <v>3.11</v>
+        <v>1.94</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="AG101">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH101">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI101">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D102" t="s">
         <v>146</v>
@@ -20509,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21619,10 +21619,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21804,7 +21804,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -21989,7 +21989,7 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>146</v>
@@ -22028,13 +22028,13 @@
         <v>415</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>141</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22359,7 +22359,7 @@
         <v>88</v>
       </c>
       <c r="C113" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D113" t="s">
         <v>145</v>
@@ -22395,7 +22395,7 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -22544,10 +22544,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22583,13 +22583,13 @@
         <v>415</v>
       </c>
       <c r="P114">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -22729,10 +22729,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -22914,7 +22914,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D116" t="s">
         <v>145</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23135,7 +23135,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23284,10 +23284,10 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
         <v>263</v>
@@ -23323,13 +23323,13 @@
         <v>415</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -23469,10 +23469,10 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>264</v>
@@ -23654,10 +23654,10 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
         <v>265</v>
@@ -23839,7 +23839,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24024,10 +24024,10 @@
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>267</v>
@@ -24209,10 +24209,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24394,7 +24394,7 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -24579,7 +24579,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D125" t="s">
         <v>146</v>
@@ -24764,7 +24764,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D126" t="s">
         <v>146</v>
@@ -24949,10 +24949,10 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -25134,10 +25134,10 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E128" t="s">
         <v>273</v>
@@ -25319,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,10 +25689,10 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131" t="s">
         <v>276</v>
@@ -25913,13 +25913,13 @@
         <v>415</v>
       </c>
       <c r="P132">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26059,7 +26059,7 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
         <v>146</v>
@@ -26244,10 +26244,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -310,52 +310,58 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
+    <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
@@ -364,66 +370,60 @@
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Italy Serie B</t>
   </si>
   <si>
+    <t>Germany Bundesliga</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany Bundesliga</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>France Ligue 1</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>France Ligue 1</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -436,21 +436,21 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -484,169 +484,172 @@
     <t>Sur</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Petrojet</t>
+    <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>BFC Daugavpils</t>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Fakel</t>
   </si>
   <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
+    <t>Kabel Novi Sad</t>
   </si>
   <si>
     <t>UTA Arad</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
     <t>Austria Salzburg</t>
   </si>
   <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
     <t>Brann W</t>
   </si>
   <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
     <t>Rīgas FS</t>
   </si>
   <si>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
+    <t>Ranheim</t>
   </si>
   <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Viborg</t>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
   </si>
   <si>
     <t>Villefranche</t>
   </si>
   <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>Durban City</t>
+    <t>Utrecht W</t>
+  </si>
+  <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>Excelsior Barendrecht W</t>
   </si>
   <si>
     <t>PSV W</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
   </si>
   <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
+    <t>Rapperswil-Jona</t>
   </si>
   <si>
     <t>Aarau</t>
@@ -655,88 +658,88 @@
     <t>Wil</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
+    <t>Venezia</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
   </si>
   <si>
     <t>Reggiana</t>
   </si>
   <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Cesena</t>
+    <t>Borussia Dortmund</t>
   </si>
   <si>
     <t>Cádiz</t>
   </si>
   <si>
-    <t>Frosinone</t>
-  </si>
-  <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Venezia</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Virtus Entella</t>
-  </si>
-  <si>
-    <t>Pescara</t>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Standard Liège</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>Lens</t>
+  </si>
+  <si>
     <t>Torino</t>
   </si>
   <si>
     <t>Athlone Town</t>
   </si>
   <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Standard Liège</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Wexford</t>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>St Patrick's Athl.</t>
@@ -745,117 +748,114 @@
     <t>Levante UD</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>ÍA</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
     <t>Nacional Potosí</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
     <t>San Telmo</t>
   </si>
   <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
     <t>Atlético Rafaela</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
+    <t>Maranhão</t>
   </si>
   <si>
     <t>Domžale</t>
   </si>
   <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
     <t>Loznica</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
     <t>Inter de Limeira</t>
   </si>
   <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -886,169 +886,172 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
+    <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
-    <t>Riga</t>
+    <t>New York RB II</t>
+  </si>
+  <si>
+    <t>SKA Khabarovsk</t>
   </si>
   <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>New York RB II</t>
+    <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
     <t>Austria Lustenau</t>
   </si>
   <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
     <t>Austria Wien II</t>
   </si>
   <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
     <t>Stabæk Women</t>
   </si>
   <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
     <t>Liepāja</t>
   </si>
   <si>
+    <t>Arminia Bielefeld</t>
+  </si>
+  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
+    <t>Kongsvinger</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
   </si>
   <si>
     <t>Ajaccio</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>Feyenoord W</t>
   </si>
   <si>
     <t>ADO Den Haag W</t>
   </si>
   <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
+    <t>Neuchâtel Xamax</t>
   </si>
   <si>
     <t>Stade Nyonnais</t>
@@ -1057,88 +1060,88 @@
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
+    <t>Bellinzona</t>
   </si>
   <si>
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Bellinzona</t>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Mantova</t>
   </si>
   <si>
     <t>Sampdoria</t>
   </si>
   <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
+    <t>Eintracht Frankfurt</t>
   </si>
   <si>
     <t>Deportivo La Coruña</t>
   </si>
   <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Carrarese</t>
-  </si>
-  <si>
-    <t>Spezia</t>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>OH Leuven</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
+    <t>Nantes</t>
+  </si>
+  <si>
     <t>Sassuolo</t>
   </si>
   <si>
     <t>Treaty United</t>
   </si>
   <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Nantes</t>
-  </si>
-  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>OH Leuven</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Waterford</t>
@@ -1147,115 +1150,112 @@
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Keflavík</t>
+  </si>
+  <si>
+    <t>FH</t>
   </si>
   <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
+    <t>Botafogo PB</t>
   </si>
   <si>
     <t>Celje</t>
   </si>
   <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>Mačva Šabac</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -3862,7 +3862,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -3898,13 +3898,13 @@
         <v>415</v>
       </c>
       <c r="P13">
-        <v>2.47</v>
+        <v>8.75</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>3.11</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>159</v>
@@ -4083,13 +4083,13 @@
         <v>415</v>
       </c>
       <c r="P14">
-        <v>8.75</v>
+        <v>2.47</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>3.11</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -4232,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -4268,13 +4268,13 @@
         <v>415</v>
       </c>
       <c r="P15">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>145</v>
@@ -4602,7 +4602,7 @@
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
         <v>162</v>
@@ -4638,13 +4638,13 @@
         <v>415</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4823,13 +4823,13 @@
         <v>415</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -5008,13 +5008,13 @@
         <v>415</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>415</v>
       </c>
       <c r="P22">
-        <v>3.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q22">
-        <v>3.44</v>
+        <v>3.78</v>
       </c>
       <c r="R22">
-        <v>1.99</v>
+        <v>4.18</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5608,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5748,13 +5748,13 @@
         <v>415</v>
       </c>
       <c r="P23">
-        <v>2.4</v>
+        <v>3.57</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R23">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5793,10 +5793,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -5894,7 +5894,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -5933,13 +5933,13 @@
         <v>415</v>
       </c>
       <c r="P24">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q24">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6079,10 +6079,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
         <v>170</v>
@@ -6118,13 +6118,13 @@
         <v>415</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6163,10 +6163,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -6303,13 +6303,13 @@
         <v>415</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6449,10 +6449,10 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
         <v>172</v>
@@ -6488,13 +6488,13 @@
         <v>415</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6533,10 +6533,10 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
         <v>173</v>
@@ -6673,13 +6673,13 @@
         <v>415</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6819,10 +6819,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
@@ -6858,13 +6858,13 @@
         <v>415</v>
       </c>
       <c r="P29">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -7043,13 +7043,13 @@
         <v>415</v>
       </c>
       <c r="P30">
-        <v>4.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q30">
-        <v>4.14</v>
+        <v>3.5</v>
       </c>
       <c r="R30">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
         <v>176</v>
@@ -7228,13 +7228,13 @@
         <v>415</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
         <v>177</v>
@@ -7413,13 +7413,13 @@
         <v>415</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7559,7 +7559,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -7598,13 +7598,13 @@
         <v>415</v>
       </c>
       <c r="P33">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7643,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -7744,10 +7744,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -7783,13 +7783,13 @@
         <v>415</v>
       </c>
       <c r="P34">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7929,7 +7929,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -8114,10 +8114,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
         <v>181</v>
@@ -8299,7 +8299,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
         <v>145</v>
@@ -8338,13 +8338,13 @@
         <v>415</v>
       </c>
       <c r="P37">
-        <v>1.76</v>
+        <v>4.78</v>
       </c>
       <c r="Q37">
-        <v>3.75</v>
+        <v>4.14</v>
       </c>
       <c r="R37">
-        <v>4.19</v>
+        <v>1.57</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -8669,7 +8669,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
         <v>146</v>
@@ -8893,13 +8893,13 @@
         <v>415</v>
       </c>
       <c r="P40">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>415</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
@@ -9263,13 +9263,13 @@
         <v>415</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>145</v>
@@ -9448,13 +9448,13 @@
         <v>415</v>
       </c>
       <c r="P43">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9594,10 +9594,10 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>189</v>
@@ -9633,13 +9633,13 @@
         <v>415</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9779,10 +9779,10 @@
         <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -9818,13 +9818,13 @@
         <v>415</v>
       </c>
       <c r="P45">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>191</v>
@@ -10003,13 +10003,13 @@
         <v>415</v>
       </c>
       <c r="P46">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
         <v>146</v>
@@ -10334,7 +10334,7 @@
         <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
         <v>145</v>
@@ -10373,13 +10373,13 @@
         <v>415</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10558,13 +10558,13 @@
         <v>415</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10704,7 +10704,7 @@
         <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
         <v>146</v>
@@ -10743,13 +10743,13 @@
         <v>415</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10889,7 +10889,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D51" t="s">
         <v>145</v>
@@ -10928,13 +10928,13 @@
         <v>415</v>
       </c>
       <c r="P51">
-        <v>1.77</v>
+        <v>3.03</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R51">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11110,7 +11110,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -11259,10 +11259,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>198</v>
@@ -11298,13 +11298,13 @@
         <v>415</v>
       </c>
       <c r="P53">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
         <v>146</v>
@@ -11483,13 +11483,13 @@
         <v>415</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -11629,10 +11629,10 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
         <v>200</v>
@@ -11668,13 +11668,13 @@
         <v>415</v>
       </c>
       <c r="P55">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Q55">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R55">
-        <v>10.6</v>
+        <v>5.46</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -11850,7 +11850,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12554,7 +12554,7 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -12924,7 +12924,7 @@
         <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>145</v>
@@ -12963,13 +12963,13 @@
         <v>415</v>
       </c>
       <c r="P62">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>145</v>
@@ -13148,13 +13148,13 @@
         <v>415</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>145</v>
@@ -13703,13 +13703,13 @@
         <v>415</v>
       </c>
       <c r="P66">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R66">
-        <v>6.5</v>
+        <v>2.25</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13754,10 +13754,10 @@
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH66">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66">
         <v>0</v>
@@ -13888,13 +13888,13 @@
         <v>415</v>
       </c>
       <c r="P67">
-        <v>2.96</v>
+        <v>1.33</v>
       </c>
       <c r="Q67">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="R67">
-        <v>2.19</v>
+        <v>6.5</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13939,10 +13939,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14073,13 +14073,13 @@
         <v>415</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="Q68">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14258,13 +14258,13 @@
         <v>415</v>
       </c>
       <c r="P69">
-        <v>3.16</v>
+        <v>1.49</v>
       </c>
       <c r="Q69">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>5.11</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14443,13 +14443,13 @@
         <v>415</v>
       </c>
       <c r="P70">
-        <v>1.49</v>
+        <v>3.16</v>
       </c>
       <c r="Q70">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="R70">
-        <v>5.11</v>
+        <v>2</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14628,13 +14628,13 @@
         <v>415</v>
       </c>
       <c r="P71">
-        <v>3.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="R71">
-        <v>2.16</v>
+        <v>3.16</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14673,10 +14673,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF71">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14774,7 +14774,7 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>145</v>
@@ -14813,13 +14813,13 @@
         <v>415</v>
       </c>
       <c r="P72">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="Q72">
-        <v>4.35</v>
+        <v>3.18</v>
       </c>
       <c r="R72">
-        <v>6.14</v>
+        <v>4</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -14998,13 +14998,13 @@
         <v>415</v>
       </c>
       <c r="P73">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="Q73">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="R73">
-        <v>6.11</v>
+        <v>4.08</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15043,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF73">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15183,13 +15183,13 @@
         <v>415</v>
       </c>
       <c r="P74">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q74">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R74">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>145</v>
@@ -15368,13 +15368,13 @@
         <v>415</v>
       </c>
       <c r="P75">
-        <v>3.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q75">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="R75">
-        <v>2.13</v>
+        <v>5</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15553,13 +15553,13 @@
         <v>415</v>
       </c>
       <c r="P76">
-        <v>1.55</v>
+        <v>3.41</v>
       </c>
       <c r="Q76">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="R76">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15738,13 +15738,13 @@
         <v>415</v>
       </c>
       <c r="P77">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q77">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="R77">
-        <v>3.16</v>
+        <v>6.11</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF77">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15923,13 +15923,13 @@
         <v>415</v>
       </c>
       <c r="P78">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q78">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="R78">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15968,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF78">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16108,13 +16108,13 @@
         <v>415</v>
       </c>
       <c r="P79">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="Q79">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="R79">
-        <v>4.08</v>
+        <v>3.05</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16153,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF79">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D81" t="s">
         <v>145</v>
@@ -16478,13 +16478,13 @@
         <v>415</v>
       </c>
       <c r="P81">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Q81">
-        <v>5.03</v>
+        <v>4.35</v>
       </c>
       <c r="R81">
-        <v>5.63</v>
+        <v>6.14</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16529,10 +16529,10 @@
         <v>0</v>
       </c>
       <c r="AG81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH81">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI81">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D82" t="s">
         <v>145</v>
@@ -16663,13 +16663,13 @@
         <v>415</v>
       </c>
       <c r="P82">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="Q82">
-        <v>3.18</v>
+        <v>5.03</v>
       </c>
       <c r="R82">
-        <v>4</v>
+        <v>5.63</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16708,16 +16708,16 @@
         <v>0</v>
       </c>
       <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
         <v>1.9</v>
       </c>
-      <c r="AF82">
-        <v>1.78</v>
-      </c>
-      <c r="AG82">
-        <v>0</v>
-      </c>
       <c r="AH82">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI82">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D83" t="s">
         <v>145</v>
@@ -16848,13 +16848,13 @@
         <v>415</v>
       </c>
       <c r="P83">
-        <v>2.18</v>
+        <v>3.57</v>
       </c>
       <c r="Q83">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="R83">
-        <v>3.05</v>
+        <v>2.13</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16893,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17033,13 +17033,13 @@
         <v>415</v>
       </c>
       <c r="P84">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="Q84">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R84">
-        <v>6.78</v>
+        <v>3.79</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17179,10 +17179,10 @@
         <v>81</v>
       </c>
       <c r="C85" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
         <v>230</v>
@@ -17218,13 +17218,13 @@
         <v>415</v>
       </c>
       <c r="P85">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q85">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R85">
-        <v>3.56</v>
+        <v>2.7</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17263,10 +17263,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>231</v>
@@ -17403,13 +17403,13 @@
         <v>415</v>
       </c>
       <c r="P86">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="Q86">
+        <v>3.51</v>
+      </c>
+      <c r="R86">
         <v>3.15</v>
-      </c>
-      <c r="R86">
-        <v>2.7</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17549,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
         <v>146</v>
@@ -17588,13 +17588,13 @@
         <v>415</v>
       </c>
       <c r="P87">
-        <v>3.88</v>
+        <v>1.43</v>
       </c>
       <c r="Q87">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="R87">
-        <v>1.96</v>
+        <v>6.78</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17734,10 +17734,10 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -17773,13 +17773,13 @@
         <v>415</v>
       </c>
       <c r="P88">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q88">
-        <v>3.3</v>
+        <v>6.09</v>
       </c>
       <c r="R88">
-        <v>2.7</v>
+        <v>10.6</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17958,13 +17958,13 @@
         <v>415</v>
       </c>
       <c r="P89">
-        <v>1.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>6.09</v>
+        <v>3.2</v>
       </c>
       <c r="R89">
-        <v>10.6</v>
+        <v>3.56</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18003,10 +18003,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
         <v>146</v>
@@ -18143,13 +18143,13 @@
         <v>415</v>
       </c>
       <c r="P90">
-        <v>1.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q90">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="R90">
-        <v>6.26</v>
+        <v>2.7</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -18292,7 +18292,7 @@
         <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E91" t="s">
         <v>236</v>
@@ -18328,13 +18328,13 @@
         <v>415</v>
       </c>
       <c r="P91">
-        <v>2.25</v>
+        <v>3.11</v>
       </c>
       <c r="Q91">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="R91">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18474,7 +18474,7 @@
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
         <v>146</v>
@@ -18844,7 +18844,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
         <v>146</v>
@@ -18883,13 +18883,13 @@
         <v>415</v>
       </c>
       <c r="P94">
-        <v>3.11</v>
+        <v>3.88</v>
       </c>
       <c r="Q94">
         <v>3.34</v>
       </c>
       <c r="R94">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19029,7 +19029,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
         <v>146</v>
@@ -19068,13 +19068,13 @@
         <v>415</v>
       </c>
       <c r="P95">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Q95">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="R95">
-        <v>3.79</v>
+        <v>6.26</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19113,10 +19113,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -19214,10 +19214,10 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
         <v>241</v>
@@ -19253,13 +19253,13 @@
         <v>415</v>
       </c>
       <c r="P96">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Q96">
-        <v>5.95</v>
+        <v>4.5</v>
       </c>
       <c r="R96">
-        <v>11.5</v>
+        <v>7.06</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -19399,10 +19399,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
         <v>242</v>
@@ -19438,13 +19438,13 @@
         <v>415</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19623,13 +19623,13 @@
         <v>415</v>
       </c>
       <c r="P98">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -19808,13 +19808,13 @@
         <v>415</v>
       </c>
       <c r="P99">
-        <v>1.98</v>
+        <v>3.13</v>
       </c>
       <c r="Q99">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="R99">
-        <v>3.11</v>
+        <v>1.94</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -19859,10 +19859,10 @@
         <v>0</v>
       </c>
       <c r="AG99">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH99">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI99">
         <v>0</v>
@@ -20178,13 +20178,13 @@
         <v>415</v>
       </c>
       <c r="P101">
-        <v>3.13</v>
+        <v>1.57</v>
       </c>
       <c r="Q101">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R101">
-        <v>1.94</v>
+        <v>4.59</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH101">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI101">
         <v>0</v>
@@ -20363,13 +20363,13 @@
         <v>415</v>
       </c>
       <c r="P102">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="Q102">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="R102">
-        <v>4.59</v>
+        <v>3.11</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -20414,10 +20414,10 @@
         <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH102">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AI102">
         <v>0</v>
@@ -20509,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D103" t="s">
         <v>145</v>
@@ -20879,7 +20879,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D105" t="s">
         <v>146</v>
@@ -21064,7 +21064,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -21288,13 +21288,13 @@
         <v>415</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -21619,10 +21619,10 @@
         <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
         <v>254</v>
@@ -21804,7 +21804,7 @@
         <v>88</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
         <v>146</v>
@@ -21989,10 +21989,10 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E111" t="s">
         <v>256</v>
@@ -22028,13 +22028,13 @@
         <v>415</v>
       </c>
       <c r="P111">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22174,10 +22174,10 @@
         <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
         <v>257</v>
@@ -22544,10 +22544,10 @@
         <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
         <v>259</v>
@@ -22729,10 +22729,10 @@
         <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>260</v>
@@ -22914,10 +22914,10 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116" t="s">
         <v>261</v>
@@ -23099,10 +23099,10 @@
         <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
         <v>262</v>
@@ -23135,7 +23135,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23284,7 +23284,7 @@
         <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D118" t="s">
         <v>146</v>
@@ -23323,13 +23323,13 @@
         <v>415</v>
       </c>
       <c r="P118">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -23469,7 +23469,7 @@
         <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D119" t="s">
         <v>146</v>
@@ -23654,7 +23654,7 @@
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="D120" t="s">
         <v>145</v>
@@ -23839,7 +23839,7 @@
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D121" t="s">
         <v>146</v>
@@ -24063,13 +24063,13 @@
         <v>415</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24209,10 +24209,10 @@
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>268</v>
@@ -24394,10 +24394,10 @@
         <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E124" t="s">
         <v>269</v>
@@ -24579,10 +24579,10 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125" t="s">
         <v>270</v>
@@ -24764,10 +24764,10 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E126" t="s">
         <v>271</v>
@@ -24949,7 +24949,7 @@
         <v>88</v>
       </c>
       <c r="C127" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
         <v>146</v>
@@ -25134,7 +25134,7 @@
         <v>88</v>
       </c>
       <c r="C128" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D128" t="s">
         <v>146</v>
@@ -25319,7 +25319,7 @@
         <v>88</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D129" t="s">
         <v>146</v>
@@ -25358,13 +25358,13 @@
         <v>415</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -25504,7 +25504,7 @@
         <v>88</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
         <v>146</v>
@@ -25689,7 +25689,7 @@
         <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D131" t="s">
         <v>146</v>
@@ -25877,7 +25877,7 @@
         <v>144</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E132" t="s">
         <v>277</v>
@@ -25910,7 +25910,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26059,10 +26059,10 @@
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E133" t="s">
         <v>278</v>
@@ -26244,10 +26244,10 @@
         <v>88</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>279</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="427">
   <si>
     <t>Date</t>
   </si>
@@ -244,6 +244,9 @@
     <t>13:30</t>
   </si>
   <si>
+    <t>13:45</t>
+  </si>
+  <si>
     <t>14:00</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -331,45 +337,45 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Norway Toppserien</t>
-  </si>
-  <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -385,24 +391,24 @@
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Italy Serie B</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
@@ -412,18 +418,18 @@
     <t>France Ligue 1</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
+    <t>Spain La Liga</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,15 +439,15 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -475,12 +481,12 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>Terengganu</t>
+  </si>
+  <si>
     <t>PDRM</t>
   </si>
   <si>
-    <t>Terengganu</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
@@ -502,79 +508,112 @@
     <t>Fakel</t>
   </si>
   <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Liefering</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Liefering</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
     <t>Fortuna Ålesund</t>
   </si>
   <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
+    <t>Paderborn</t>
   </si>
   <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Paderborn</t>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Örebro</t>
   </si>
   <si>
     <t>Ranheim</t>
@@ -583,30 +622,6 @@
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
@@ -622,13 +637,22 @@
     <t>Villefranche</t>
   </si>
   <si>
+    <t>NAC Breda W</t>
+  </si>
+  <si>
+    <t>Olympique Dcheïra</t>
+  </si>
+  <si>
+    <t>PSV W</t>
+  </si>
+  <si>
+    <t>Ajax W</t>
+  </si>
+  <si>
     <t>Utrecht W</t>
   </si>
   <si>
-    <t>NAC Breda W</t>
-  </si>
-  <si>
-    <t>Ajax W</t>
+    <t>Rijeka</t>
   </si>
   <si>
     <t>PEC Zwolle W</t>
@@ -637,126 +661,120 @@
     <t>Excelsior Barendrecht W</t>
   </si>
   <si>
-    <t>PSV W</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Olympique Dcheïra</t>
+    <t>Wil</t>
   </si>
   <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
+    <t>Cádiz</t>
+  </si>
+  <si>
+    <t>Virtus Entella</t>
+  </si>
+  <si>
     <t>Avellino</t>
   </si>
   <si>
-    <t>Virtus Entella</t>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Cesena</t>
   </si>
   <si>
     <t>Venezia</t>
   </si>
   <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
     <t>Frosinone</t>
   </si>
   <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
     <t>Reggiana</t>
   </si>
   <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
-    <t>Pescara</t>
-  </si>
-  <si>
     <t>Catanzaro</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
-    <t>Cádiz</t>
-  </si>
-  <si>
     <t>Wexford</t>
   </si>
   <si>
+    <t>Standard Liège</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Standard Liège</t>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
+    <t>Levante UD</t>
   </si>
   <si>
     <t>Wisła Kraków</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Levante UD</t>
+    <t>ÍA</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Fram</t>
   </si>
   <si>
@@ -766,96 +784,96 @@
     <t>Racing Louisville</t>
   </si>
   <si>
+    <t>Nacional Potosí</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Nacional Potosí</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Brusque</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
     <t>Jedinstvo Ub</t>
   </si>
   <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Posusje</t>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
   </si>
   <si>
     <t>Barra do Garcas</t>
   </si>
   <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -877,12 +895,12 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Imigresen</t>
+  </si>
+  <si>
     <t>Pulau Pinang</t>
   </si>
   <si>
-    <t>Imigresen</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -904,79 +922,112 @@
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Admira</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
     <t>Korona Kielce</t>
   </si>
   <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Admira</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
     <t>Lyn W</t>
   </si>
   <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Brage</t>
   </si>
   <si>
     <t>Kongsvinger</t>
@@ -985,30 +1036,6 @@
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
@@ -1024,13 +1051,22 @@
     <t>Ajaccio</t>
   </si>
   <si>
+    <t>Twente W</t>
+  </si>
+  <si>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>ADO Den Haag W</t>
+  </si>
+  <si>
+    <t>AZ W</t>
+  </si>
+  <si>
     <t>Heerenveen W</t>
   </si>
   <si>
-    <t>Twente W</t>
-  </si>
-  <si>
-    <t>AZ W</t>
+    <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>HERA</t>
@@ -1039,126 +1075,120 @@
     <t>Feyenoord W</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>Yacoub El Mansour</t>
+    <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
     <t>Vaduz</t>
   </si>
   <si>
+    <t>Deportivo La Coruña</t>
+  </si>
+  <si>
+    <t>Carrarese</t>
+  </si>
+  <si>
     <t>Modena</t>
   </si>
   <si>
-    <t>Carrarese</t>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Juve Stabia</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
   </si>
   <si>
     <t>Palermo</t>
   </si>
   <si>
-    <t>Juve Stabia</t>
-  </si>
-  <si>
     <t>Mantova</t>
   </si>
   <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
     <t>Sampdoria</t>
   </si>
   <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
     <t>Bari 1908</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
-    <t>Deportivo La Coruña</t>
-  </si>
-  <si>
     <t>Longford Town</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>OH Leuven</t>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Kerry</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Nantes</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
+    <t>CA Osasuna</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>CA Osasuna</t>
+    <t>Keflavík</t>
+  </si>
+  <si>
+    <t>FH</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Keflavík</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -1168,94 +1198,94 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Aurora</t>
-  </si>
-  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>Zemun</t>
   </si>
   <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Velež</t>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
   </si>
   <si>
     <t>Caxias</t>
   </si>
   <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
     <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -1628,7 +1658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI135"/>
+  <dimension ref="A1:BI139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1824,16 +1854,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1860,7 +1890,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2009,16 +2039,16 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2045,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2194,16 +2224,16 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2230,7 +2260,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2379,16 +2409,16 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2415,7 +2445,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2564,16 +2594,16 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2600,7 +2630,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2749,16 +2779,16 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F7" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2785,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2934,16 +2964,16 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F8" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2970,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3119,16 +3149,16 @@
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3155,7 +3185,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3304,16 +3334,16 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F10" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3340,7 +3370,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3489,16 +3519,16 @@
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3525,7 +3555,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3674,16 +3704,16 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F12" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3710,7 +3740,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3859,16 +3889,16 @@
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3895,7 +3925,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P13">
         <v>8.75</v>
@@ -4044,16 +4074,16 @@
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F14" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4080,7 +4110,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P14">
         <v>2.47</v>
@@ -4229,16 +4259,16 @@
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F15" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -4265,7 +4295,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4414,16 +4444,16 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4450,7 +4480,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P16">
         <v>1.36</v>
@@ -4599,16 +4629,16 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4635,16 +4665,16 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P17">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4784,16 +4814,16 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4820,7 +4850,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4969,16 +4999,16 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F19" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -5005,7 +5035,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P19">
         <v>1.94</v>
@@ -5151,19 +5181,19 @@
         <v>46150</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -5190,7 +5220,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5328,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3">
-        <v>46150.52083333334</v>
+        <v>46150.5</v>
       </c>
     </row>
     <row r="21" spans="1:61">
@@ -5336,19 +5366,19 @@
         <v>46150</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F21" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -5375,16 +5405,16 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -5513,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3">
-        <v>46150.53125</v>
+        <v>46150.5</v>
       </c>
     </row>
     <row r="22" spans="1:61">
@@ -5521,19 +5551,19 @@
         <v>46150</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F22" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5560,16 +5590,16 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P22">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5698,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3">
-        <v>46150.54166666666</v>
+        <v>46150.52083333334</v>
       </c>
     </row>
     <row r="23" spans="1:61">
@@ -5706,19 +5736,19 @@
         <v>46150</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
         <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F23" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5745,16 +5775,16 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P23">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5793,10 +5823,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -5883,7 +5913,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3">
-        <v>46150.54166666666</v>
+        <v>46150.53125</v>
       </c>
     </row>
     <row r="24" spans="1:61">
@@ -5894,16 +5924,16 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F24" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5930,7 +5960,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P24">
         <v>3.25</v>
@@ -6079,16 +6109,16 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F25" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -6115,16 +6145,16 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P25">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6163,10 +6193,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -6264,16 +6294,16 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -6300,16 +6330,16 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P26">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="Q26">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="R26">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6449,16 +6479,16 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F27" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -6485,16 +6515,16 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6634,16 +6664,16 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6670,58 +6700,58 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P28">
+        <v>1.87</v>
+      </c>
+      <c r="Q28">
+        <v>3.33</v>
+      </c>
+      <c r="R28">
+        <v>3.78</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>1.92</v>
+      </c>
+      <c r="AF28">
         <v>1.76</v>
-      </c>
-      <c r="Q28">
-        <v>3.75</v>
-      </c>
-      <c r="R28">
-        <v>4.19</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6819,16 +6849,16 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F29" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6855,16 +6885,16 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7004,16 +7034,16 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F30" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7040,16 +7070,16 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P30">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7088,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -7189,16 +7219,16 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F31" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7225,16 +7255,16 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P31">
-        <v>2.63</v>
+        <v>4.78</v>
       </c>
       <c r="Q31">
-        <v>3.58</v>
+        <v>4.14</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7374,16 +7404,16 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F32" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7410,16 +7440,16 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P32">
-        <v>4.04</v>
+        <v>1.43</v>
       </c>
       <c r="Q32">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R32">
-        <v>1.79</v>
+        <v>6.17</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7559,16 +7589,16 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F33" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7595,7 +7625,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7744,16 +7774,16 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E34" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F34" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7780,16 +7810,16 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7828,10 +7858,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -7929,16 +7959,16 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F35" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7965,7 +7995,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -8114,16 +8144,16 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E36" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F36" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -8150,16 +8180,16 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8198,10 +8228,10 @@
         <v>0</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -8299,16 +8329,16 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F37" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -8335,16 +8365,16 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P37">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8484,16 +8514,16 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -8520,16 +8550,16 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8669,16 +8699,16 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F39" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8705,16 +8735,16 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P39">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8851,19 +8881,19 @@
         <v>46150</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E40" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F40" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8890,16 +8920,16 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q40">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>4.18</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9028,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3">
-        <v>46150.5625</v>
+        <v>46150.54166666666</v>
       </c>
     </row>
     <row r="41" spans="1:61">
@@ -9036,19 +9066,19 @@
         <v>46150</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F41" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -9075,16 +9105,16 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P41">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9213,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3">
-        <v>46150.5625</v>
+        <v>46150.54166666666</v>
       </c>
     </row>
     <row r="42" spans="1:61">
@@ -9221,19 +9251,19 @@
         <v>46150</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E42" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F42" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -9260,16 +9290,16 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P42">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="Q42">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>5.73</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9398,7 +9428,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3">
-        <v>46150.58333333334</v>
+        <v>46150.5625</v>
       </c>
     </row>
     <row r="43" spans="1:61">
@@ -9406,19 +9436,19 @@
         <v>46150</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C43" t="s">
         <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F43" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -9445,16 +9475,16 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9583,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3">
-        <v>46150.58333333334</v>
+        <v>46150.5625</v>
       </c>
     </row>
     <row r="44" spans="1:61">
@@ -9594,16 +9624,16 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F44" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -9630,16 +9660,16 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P44">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9768,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3">
-        <v>46150.58333333334</v>
+        <v>46150.57291666666</v>
       </c>
     </row>
     <row r="45" spans="1:61">
@@ -9776,19 +9806,19 @@
         <v>46150</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F45" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9815,16 +9845,16 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9961,19 +9991,19 @@
         <v>46150</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F46" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -10000,7 +10030,7 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -10146,19 +10176,19 @@
         <v>46150</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E47" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F47" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -10185,16 +10215,16 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10331,19 +10361,19 @@
         <v>46150</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F48" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -10370,16 +10400,16 @@
         <v>-1</v>
       </c>
       <c r="O48" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P48">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10516,19 +10546,19 @@
         <v>46150</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F49" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -10555,16 +10585,16 @@
         <v>-1</v>
       </c>
       <c r="O49" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P49">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="Q49">
-        <v>3.61</v>
+        <v>3.15</v>
       </c>
       <c r="R49">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10701,19 +10731,19 @@
         <v>46150</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F50" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -10740,16 +10770,16 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P50">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10886,19 +10916,19 @@
         <v>46150</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F51" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -10925,16 +10955,16 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P51">
-        <v>3.03</v>
+        <v>1.77</v>
       </c>
       <c r="Q51">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11074,16 +11104,16 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F52" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -11110,16 +11140,16 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -11248,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3">
-        <v>46150.60416666666</v>
+        <v>46150.58333333334</v>
       </c>
     </row>
     <row r="53" spans="1:61">
@@ -11259,16 +11289,16 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F53" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -11295,16 +11325,16 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11433,7 +11463,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3">
-        <v>46150.60416666666</v>
+        <v>46150.58333333334</v>
       </c>
     </row>
     <row r="54" spans="1:61">
@@ -11444,16 +11474,16 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F54" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -11480,16 +11510,16 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P54">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -11618,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3">
-        <v>46150.60416666666</v>
+        <v>46150.58333333334</v>
       </c>
     </row>
     <row r="55" spans="1:61">
@@ -11626,19 +11656,19 @@
         <v>46150</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -11665,16 +11695,16 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P55">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -11811,19 +11841,19 @@
         <v>46150</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F56" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -11850,7 +11880,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12002,13 +12032,13 @@
         <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E57" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F57" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -12035,16 +12065,16 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12173,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3">
-        <v>46150.625</v>
+        <v>46150.60416666666</v>
       </c>
     </row>
     <row r="58" spans="1:61">
@@ -12184,16 +12214,16 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F58" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -12220,16 +12250,16 @@
         <v>-1</v>
       </c>
       <c r="O58" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -12358,7 +12388,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3">
-        <v>46150.625</v>
+        <v>46150.60416666666</v>
       </c>
     </row>
     <row r="59" spans="1:61">
@@ -12369,16 +12399,16 @@
         <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E59" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F59" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12405,7 +12435,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12543,7 +12573,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3">
-        <v>46150.625</v>
+        <v>46150.60416666666</v>
       </c>
     </row>
     <row r="60" spans="1:61">
@@ -12551,19 +12581,19 @@
         <v>46150</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F60" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12590,7 +12620,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12736,19 +12766,19 @@
         <v>46150</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F61" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12775,7 +12805,7 @@
         <v>-1</v>
       </c>
       <c r="O61" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -12921,19 +12951,19 @@
         <v>46150</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E62" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F62" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12960,7 +12990,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -13106,19 +13136,19 @@
         <v>46150</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E63" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F63" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -13145,16 +13175,16 @@
         <v>-1</v>
       </c>
       <c r="O63" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P63">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13291,19 +13321,19 @@
         <v>46150</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F64" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -13330,7 +13360,7 @@
         <v>-1</v>
       </c>
       <c r="O64" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -13476,19 +13506,19 @@
         <v>46150</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D65" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F65" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13515,7 +13545,7 @@
         <v>-1</v>
       </c>
       <c r="O65" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -13664,16 +13694,16 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E66" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F66" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13700,16 +13730,16 @@
         <v>-1</v>
       </c>
       <c r="O66" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P66">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -13838,7 +13868,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3">
-        <v>46150.63541666666</v>
+        <v>46150.625</v>
       </c>
     </row>
     <row r="67" spans="1:61">
@@ -13849,16 +13879,16 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E67" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F67" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13885,16 +13915,16 @@
         <v>-1</v>
       </c>
       <c r="O67" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -13939,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -14023,7 +14053,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3">
-        <v>46150.63541666666</v>
+        <v>46150.625</v>
       </c>
     </row>
     <row r="68" spans="1:61">
@@ -14034,16 +14064,16 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E68" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F68" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -14070,16 +14100,16 @@
         <v>-1</v>
       </c>
       <c r="O68" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P68">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="Q68">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="R68">
-        <v>2.19</v>
+        <v>2.68</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14208,7 +14238,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3">
-        <v>46150.63541666666</v>
+        <v>46150.625</v>
       </c>
     </row>
     <row r="69" spans="1:61">
@@ -14216,19 +14246,19 @@
         <v>46150</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F69" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14255,16 +14285,16 @@
         <v>-1</v>
       </c>
       <c r="O69" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P69">
-        <v>1.49</v>
+        <v>2.96</v>
       </c>
       <c r="Q69">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R69">
-        <v>5.11</v>
+        <v>2.19</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14401,19 +14431,19 @@
         <v>46150</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E70" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F70" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14440,16 +14470,16 @@
         <v>-1</v>
       </c>
       <c r="O70" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P70">
-        <v>3.16</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="R70">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14589,16 +14619,16 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E71" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F71" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -14625,16 +14655,16 @@
         <v>-1</v>
       </c>
       <c r="O71" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P71">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q71">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="R71">
-        <v>3.16</v>
+        <v>5.11</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -14673,10 +14703,10 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -14763,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3">
-        <v>46150.64583333334</v>
+        <v>46150.63541666666</v>
       </c>
     </row>
     <row r="72" spans="1:61">
@@ -14774,16 +14804,16 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E72" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F72" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -14810,16 +14840,16 @@
         <v>-1</v>
       </c>
       <c r="O72" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P72">
-        <v>1.99</v>
+        <v>1.33</v>
       </c>
       <c r="Q72">
-        <v>3.18</v>
+        <v>4.75</v>
       </c>
       <c r="R72">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14858,16 +14888,16 @@
         <v>0</v>
       </c>
       <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
         <v>1.9</v>
       </c>
-      <c r="AF72">
-        <v>1.78</v>
-      </c>
-      <c r="AG72">
-        <v>0</v>
-      </c>
       <c r="AH72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI72">
         <v>0</v>
@@ -14948,7 +14978,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3">
-        <v>46150.64583333334</v>
+        <v>46150.63541666666</v>
       </c>
     </row>
     <row r="73" spans="1:61">
@@ -14959,16 +14989,16 @@
         <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F73" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -14995,16 +15025,16 @@
         <v>-1</v>
       </c>
       <c r="O73" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P73">
-        <v>1.78</v>
+        <v>3.16</v>
       </c>
       <c r="Q73">
-        <v>3.84</v>
+        <v>3.54</v>
       </c>
       <c r="R73">
-        <v>4.08</v>
+        <v>2</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15043,10 +15073,10 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -15133,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3">
-        <v>46150.64583333334</v>
+        <v>46150.63541666666</v>
       </c>
     </row>
     <row r="74" spans="1:61">
@@ -15141,19 +15171,19 @@
         <v>46150</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F74" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -15180,16 +15210,16 @@
         <v>-1</v>
       </c>
       <c r="O74" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P74">
-        <v>2.03</v>
+        <v>3.57</v>
       </c>
       <c r="Q74">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R74">
-        <v>3.58</v>
+        <v>2.13</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -15228,10 +15258,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF74">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15326,19 +15356,19 @@
         <v>46150</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E75" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F75" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -15365,16 +15395,16 @@
         <v>-1</v>
       </c>
       <c r="O75" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P75">
-        <v>1.55</v>
+        <v>1.99</v>
       </c>
       <c r="Q75">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="R75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15413,10 +15443,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15511,19 +15541,19 @@
         <v>46150</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D76" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F76" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -15550,16 +15580,16 @@
         <v>-1</v>
       </c>
       <c r="O76" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P76">
-        <v>3.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q76">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="R76">
-        <v>2.16</v>
+        <v>3.16</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15598,10 +15628,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF76">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15696,19 +15726,19 @@
         <v>46150</v>
       </c>
       <c r="B77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E77" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F77" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -15735,16 +15765,16 @@
         <v>-1</v>
       </c>
       <c r="O77" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P77">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="Q77">
-        <v>4.3</v>
+        <v>5.03</v>
       </c>
       <c r="R77">
-        <v>6.11</v>
+        <v>5.63</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15783,16 +15813,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -15881,19 +15911,19 @@
         <v>46150</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D78" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F78" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -15920,16 +15950,16 @@
         <v>-1</v>
       </c>
       <c r="O78" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P78">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q78">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R78">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15968,10 +15998,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16066,19 +16096,19 @@
         <v>46150</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D79" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E79" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F79" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -16105,16 +16135,16 @@
         <v>-1</v>
       </c>
       <c r="O79" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P79">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="Q79">
-        <v>3.56</v>
+        <v>4.3</v>
       </c>
       <c r="R79">
-        <v>3.05</v>
+        <v>6.11</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16153,10 +16183,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF79">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16251,19 +16281,19 @@
         <v>46150</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D80" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F80" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -16290,16 +16320,16 @@
         <v>-1</v>
       </c>
       <c r="O80" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P80">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q80">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="R80">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16338,10 +16368,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF80">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16436,19 +16466,19 @@
         <v>46150</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D81" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E81" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F81" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -16475,16 +16505,16 @@
         <v>-1</v>
       </c>
       <c r="O81" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P81">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q81">
-        <v>4.35</v>
+        <v>3.84</v>
       </c>
       <c r="R81">
-        <v>6.14</v>
+        <v>4.08</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16523,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16621,19 +16651,19 @@
         <v>46150</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D82" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E82" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F82" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -16660,16 +16690,16 @@
         <v>-1</v>
       </c>
       <c r="O82" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P82">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q82">
-        <v>5.03</v>
+        <v>4.5</v>
       </c>
       <c r="R82">
-        <v>5.63</v>
+        <v>5</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16714,10 +16744,10 @@
         <v>0</v>
       </c>
       <c r="AG82">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH82">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI82">
         <v>0</v>
@@ -16806,19 +16836,19 @@
         <v>46150</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F83" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -16845,16 +16875,16 @@
         <v>-1</v>
       </c>
       <c r="O83" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P83">
-        <v>3.57</v>
+        <v>2.18</v>
       </c>
       <c r="Q83">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="R83">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16893,10 +16923,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -16994,16 +17024,16 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E84" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F84" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -17030,16 +17060,16 @@
         <v>-1</v>
       </c>
       <c r="O84" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P84">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="Q84">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="R84">
-        <v>3.79</v>
+        <v>6.14</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17168,7 +17198,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3">
-        <v>46150.65625</v>
+        <v>46150.64583333334</v>
       </c>
     </row>
     <row r="85" spans="1:61">
@@ -17182,13 +17212,13 @@
         <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E85" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F85" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -17215,16 +17245,16 @@
         <v>-1</v>
       </c>
       <c r="O85" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P85">
-        <v>2.33</v>
+        <v>3.41</v>
       </c>
       <c r="Q85">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="R85">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17263,10 +17293,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -17353,7 +17383,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3">
-        <v>46150.65625</v>
+        <v>46150.64583333334</v>
       </c>
     </row>
     <row r="86" spans="1:61">
@@ -17364,16 +17394,16 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E86" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F86" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -17400,16 +17430,16 @@
         <v>-1</v>
       </c>
       <c r="O86" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P86">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q86">
-        <v>3.51</v>
+        <v>3.78</v>
       </c>
       <c r="R86">
-        <v>3.15</v>
+        <v>4.22</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17448,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -17538,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3">
-        <v>46150.65625</v>
+        <v>46150.64583333334</v>
       </c>
     </row>
     <row r="87" spans="1:61">
@@ -17546,19 +17576,19 @@
         <v>46150</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E87" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F87" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -17585,16 +17615,16 @@
         <v>-1</v>
       </c>
       <c r="O87" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P87">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="Q87">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R87">
-        <v>6.78</v>
+        <v>3.79</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17731,19 +17761,19 @@
         <v>46150</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E88" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F88" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -17770,16 +17800,16 @@
         <v>-1</v>
       </c>
       <c r="O88" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P88">
-        <v>1.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q88">
-        <v>6.09</v>
+        <v>3.51</v>
       </c>
       <c r="R88">
-        <v>10.6</v>
+        <v>3.15</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17916,19 +17946,19 @@
         <v>46150</v>
       </c>
       <c r="B89" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E89" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -17955,16 +17985,16 @@
         <v>-1</v>
       </c>
       <c r="O89" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q89">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R89">
-        <v>3.56</v>
+        <v>2.7</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18003,10 +18033,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18101,19 +18131,19 @@
         <v>46150</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E90" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -18140,7 +18170,7 @@
         <v>-1</v>
       </c>
       <c r="O90" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P90">
         <v>2.42</v>
@@ -18286,19 +18316,19 @@
         <v>46150</v>
       </c>
       <c r="B91" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
         <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F91" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -18325,16 +18355,16 @@
         <v>-1</v>
       </c>
       <c r="O91" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P91">
-        <v>3.11</v>
+        <v>1.32</v>
       </c>
       <c r="Q91">
-        <v>3.34</v>
+        <v>6.09</v>
       </c>
       <c r="R91">
-        <v>2.24</v>
+        <v>10.6</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18471,19 +18501,19 @@
         <v>46150</v>
       </c>
       <c r="B92" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E92" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F92" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -18510,16 +18540,16 @@
         <v>-1</v>
       </c>
       <c r="O92" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P92">
-        <v>3.05</v>
+        <v>3.88</v>
       </c>
       <c r="Q92">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="R92">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18656,19 +18686,19 @@
         <v>46150</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E93" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F93" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -18695,16 +18725,16 @@
         <v>-1</v>
       </c>
       <c r="O93" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P93">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="Q93">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="R93">
-        <v>2.99</v>
+        <v>6.26</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18743,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -18841,19 +18871,19 @@
         <v>46150</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E94" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F94" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -18880,16 +18910,16 @@
         <v>-1</v>
       </c>
       <c r="O94" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P94">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="Q94">
         <v>3.34</v>
       </c>
       <c r="R94">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19026,19 +19056,19 @@
         <v>46150</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F95" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -19065,16 +19095,16 @@
         <v>-1</v>
       </c>
       <c r="O95" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P95">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q95">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="R95">
-        <v>6.26</v>
+        <v>3.56</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19113,10 +19143,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AF95">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -19214,16 +19244,16 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E96" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F96" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -19250,16 +19280,16 @@
         <v>-1</v>
       </c>
       <c r="O96" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P96">
-        <v>1.36</v>
+        <v>2.29</v>
       </c>
       <c r="Q96">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="R96">
-        <v>7.06</v>
+        <v>2.99</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -19388,7 +19418,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3">
-        <v>46150.66666666666</v>
+        <v>46150.65625</v>
       </c>
     </row>
     <row r="97" spans="1:61">
@@ -19399,16 +19429,16 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E97" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F97" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -19435,16 +19465,16 @@
         <v>-1</v>
       </c>
       <c r="O97" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P97">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="Q97">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="R97">
-        <v>11.5</v>
+        <v>6.78</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19573,7 +19603,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3">
-        <v>46150.66666666666</v>
+        <v>46150.65625</v>
       </c>
     </row>
     <row r="98" spans="1:61">
@@ -19584,16 +19614,16 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E98" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F98" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -19620,16 +19650,16 @@
         <v>-1</v>
       </c>
       <c r="O98" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -19758,7 +19788,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3">
-        <v>46150.66666666666</v>
+        <v>46150.65625</v>
       </c>
     </row>
     <row r="99" spans="1:61">
@@ -19769,16 +19799,16 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E99" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F99" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -19805,16 +19835,16 @@
         <v>-1</v>
       </c>
       <c r="O99" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P99">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -19943,7 +19973,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3">
-        <v>46150.67708333334</v>
+        <v>46150.66666666666</v>
       </c>
     </row>
     <row r="100" spans="1:61">
@@ -19954,16 +19984,16 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D100" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E100" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F100" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -19990,16 +20020,16 @@
         <v>-1</v>
       </c>
       <c r="O100" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P100">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="Q100">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="R100">
-        <v>4.23</v>
+        <v>7.06</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20128,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3">
-        <v>46150.67708333334</v>
+        <v>46150.66666666666</v>
       </c>
     </row>
     <row r="101" spans="1:61">
@@ -20139,16 +20169,16 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F101" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -20175,16 +20205,16 @@
         <v>-1</v>
       </c>
       <c r="O101" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P101">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -20229,10 +20259,10 @@
         <v>0</v>
       </c>
       <c r="AG101">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH101">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI101">
         <v>0</v>
@@ -20313,7 +20343,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3">
-        <v>46150.67708333334</v>
+        <v>46150.66666666666</v>
       </c>
     </row>
     <row r="102" spans="1:61">
@@ -20324,16 +20354,16 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D102" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E102" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F102" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -20360,16 +20390,16 @@
         <v>-1</v>
       </c>
       <c r="O102" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P102">
-        <v>1.98</v>
+        <v>1.23</v>
       </c>
       <c r="Q102">
-        <v>4.05</v>
+        <v>5.95</v>
       </c>
       <c r="R102">
-        <v>3.11</v>
+        <v>11.5</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -20414,10 +20444,10 @@
         <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH102">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI102">
         <v>0</v>
@@ -20498,7 +20528,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3">
-        <v>46150.67708333334</v>
+        <v>46150.66666666666</v>
       </c>
     </row>
     <row r="103" spans="1:61">
@@ -20509,16 +20539,16 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D103" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E103" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F103" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -20545,16 +20575,16 @@
         <v>-1</v>
       </c>
       <c r="O103" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -20683,7 +20713,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3">
-        <v>46150.70833333334</v>
+        <v>46150.67708333334</v>
       </c>
     </row>
     <row r="104" spans="1:61">
@@ -20691,19 +20721,19 @@
         <v>46150</v>
       </c>
       <c r="B104" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="D104" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E104" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F104" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -20730,16 +20760,16 @@
         <v>-1</v>
       </c>
       <c r="O104" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P104">
-        <v>2.86</v>
+        <v>1.57</v>
       </c>
       <c r="Q104">
-        <v>3.21</v>
+        <v>4.6</v>
       </c>
       <c r="R104">
-        <v>2.23</v>
+        <v>4.59</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -20778,16 +20808,16 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI104">
         <v>0</v>
@@ -20868,7 +20898,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3">
-        <v>46150.8125</v>
+        <v>46150.67708333334</v>
       </c>
     </row>
     <row r="105" spans="1:61">
@@ -20876,19 +20906,19 @@
         <v>46150</v>
       </c>
       <c r="B105" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D105" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E105" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F105" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -20915,16 +20945,16 @@
         <v>-1</v>
       </c>
       <c r="O105" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21053,7 +21083,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3">
-        <v>46150.83333333334</v>
+        <v>46150.67708333334</v>
       </c>
     </row>
     <row r="106" spans="1:61">
@@ -21061,19 +21091,19 @@
         <v>46150</v>
       </c>
       <c r="B106" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D106" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E106" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F106" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -21100,16 +21130,16 @@
         <v>-1</v>
       </c>
       <c r="O106" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -21154,10 +21184,10 @@
         <v>0</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH106">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI106">
         <v>0</v>
@@ -21238,7 +21268,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3">
-        <v>46150.83333333334</v>
+        <v>46150.67708333334</v>
       </c>
     </row>
     <row r="107" spans="1:61">
@@ -21246,19 +21276,19 @@
         <v>46150</v>
       </c>
       <c r="B107" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E107" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F107" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -21285,16 +21315,16 @@
         <v>-1</v>
       </c>
       <c r="O107" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P107">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -21423,7 +21453,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3">
-        <v>46150.85416666666</v>
+        <v>46150.70833333334</v>
       </c>
     </row>
     <row r="108" spans="1:61">
@@ -21431,19 +21461,19 @@
         <v>46150</v>
       </c>
       <c r="B108" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E108" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F108" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -21470,16 +21500,16 @@
         <v>-1</v>
       </c>
       <c r="O108" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -21518,10 +21548,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -21608,7 +21638,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3">
-        <v>46150.875</v>
+        <v>46150.8125</v>
       </c>
     </row>
     <row r="109" spans="1:61">
@@ -21616,19 +21646,19 @@
         <v>46150</v>
       </c>
       <c r="B109" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C109" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E109" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F109" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -21655,7 +21685,7 @@
         <v>-1</v>
       </c>
       <c r="O109" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P109">
         <v>0</v>
@@ -21793,7 +21823,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3">
-        <v>46150.875</v>
+        <v>46150.83333333334</v>
       </c>
     </row>
     <row r="110" spans="1:61">
@@ -21801,19 +21831,19 @@
         <v>46150</v>
       </c>
       <c r="B110" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E110" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -21840,7 +21870,7 @@
         <v>-1</v>
       </c>
       <c r="O110" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -21978,7 +22008,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3">
-        <v>46150.875</v>
+        <v>46150.83333333334</v>
       </c>
     </row>
     <row r="111" spans="1:61">
@@ -21989,16 +22019,16 @@
         <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E111" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F111" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -22025,16 +22055,16 @@
         <v>-1</v>
       </c>
       <c r="O111" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22163,7 +22193,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3">
-        <v>46150.875</v>
+        <v>46150.85416666666</v>
       </c>
     </row>
     <row r="112" spans="1:61">
@@ -22171,19 +22201,19 @@
         <v>46150</v>
       </c>
       <c r="B112" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C112" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E112" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F112" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -22210,7 +22240,7 @@
         <v>-1</v>
       </c>
       <c r="O112" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -22356,19 +22386,19 @@
         <v>46150</v>
       </c>
       <c r="B113" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E113" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F113" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -22395,7 +22425,7 @@
         <v>-1</v>
       </c>
       <c r="O113" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -22541,19 +22571,19 @@
         <v>46150</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C114" t="s">
         <v>142</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E114" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F114" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -22580,7 +22610,7 @@
         <v>-1</v>
       </c>
       <c r="O114" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -22726,19 +22756,19 @@
         <v>46150</v>
       </c>
       <c r="B115" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C115" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E115" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F115" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -22765,7 +22795,7 @@
         <v>-1</v>
       </c>
       <c r="O115" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -22911,19 +22941,19 @@
         <v>46150</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C116" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D116" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E116" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F116" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -22950,7 +22980,7 @@
         <v>-1</v>
       </c>
       <c r="O116" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -23096,19 +23126,19 @@
         <v>46150</v>
       </c>
       <c r="B117" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C117" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F117" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -23135,7 +23165,7 @@
         <v>-1</v>
       </c>
       <c r="O117" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -23281,19 +23311,19 @@
         <v>46150</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C118" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E118" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F118" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -23320,7 +23350,7 @@
         <v>-1</v>
       </c>
       <c r="O118" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -23466,19 +23496,19 @@
         <v>46150</v>
       </c>
       <c r="B119" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C119" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E119" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F119" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -23505,7 +23535,7 @@
         <v>-1</v>
       </c>
       <c r="O119" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -23651,19 +23681,19 @@
         <v>46150</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E120" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F120" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -23690,7 +23720,7 @@
         <v>-1</v>
       </c>
       <c r="O120" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -23836,19 +23866,19 @@
         <v>46150</v>
       </c>
       <c r="B121" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C121" t="s">
         <v>142</v>
       </c>
       <c r="D121" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F121" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -23875,7 +23905,7 @@
         <v>-1</v>
       </c>
       <c r="O121" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -24021,19 +24051,19 @@
         <v>46150</v>
       </c>
       <c r="B122" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E122" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F122" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -24060,16 +24090,16 @@
         <v>-1</v>
       </c>
       <c r="O122" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P122">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -24206,19 +24236,19 @@
         <v>46150</v>
       </c>
       <c r="B123" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F123" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -24245,7 +24275,7 @@
         <v>-1</v>
       </c>
       <c r="O123" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -24391,19 +24421,19 @@
         <v>46150</v>
       </c>
       <c r="B124" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E124" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F124" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -24430,7 +24460,7 @@
         <v>-1</v>
       </c>
       <c r="O124" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -24576,19 +24606,19 @@
         <v>46150</v>
       </c>
       <c r="B125" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E125" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F125" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -24615,16 +24645,16 @@
         <v>-1</v>
       </c>
       <c r="O125" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -24761,19 +24791,19 @@
         <v>46150</v>
       </c>
       <c r="B126" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E126" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F126" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -24800,7 +24830,7 @@
         <v>-1</v>
       </c>
       <c r="O126" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -24946,19 +24976,19 @@
         <v>46150</v>
       </c>
       <c r="B127" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F127" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -24985,7 +25015,7 @@
         <v>-1</v>
       </c>
       <c r="O127" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -25131,19 +25161,19 @@
         <v>46150</v>
       </c>
       <c r="B128" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E128" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F128" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -25170,7 +25200,7 @@
         <v>-1</v>
       </c>
       <c r="O128" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -25316,19 +25346,19 @@
         <v>46150</v>
       </c>
       <c r="B129" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E129" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F129" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -25355,7 +25385,7 @@
         <v>-1</v>
       </c>
       <c r="O129" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P129">
         <v>2.22</v>
@@ -25501,19 +25531,19 @@
         <v>46150</v>
       </c>
       <c r="B130" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E130" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F130" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -25540,7 +25570,7 @@
         <v>-1</v>
       </c>
       <c r="O130" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -25686,19 +25716,19 @@
         <v>46150</v>
       </c>
       <c r="B131" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E131" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F131" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -25725,7 +25755,7 @@
         <v>-1</v>
       </c>
       <c r="O131" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -25871,19 +25901,19 @@
         <v>46150</v>
       </c>
       <c r="B132" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F132" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -25910,7 +25940,7 @@
         <v>-1</v>
       </c>
       <c r="O132" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -26056,19 +26086,19 @@
         <v>46150</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C133" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E133" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F133" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -26095,7 +26125,7 @@
         <v>-1</v>
       </c>
       <c r="O133" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -26241,19 +26271,19 @@
         <v>46150</v>
       </c>
       <c r="B134" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E134" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F134" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -26280,7 +26310,7 @@
         <v>-1</v>
       </c>
       <c r="O134" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -26429,16 +26459,16 @@
         <v>89</v>
       </c>
       <c r="C135" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D135" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E135" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F135" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -26465,144 +26495,884 @@
         <v>-1</v>
       </c>
       <c r="O135" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
+      <c r="AG135">
+        <v>0</v>
+      </c>
+      <c r="AH135">
+        <v>0</v>
+      </c>
+      <c r="AI135">
+        <v>0</v>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+      <c r="AK135">
+        <v>0</v>
+      </c>
+      <c r="AL135">
+        <v>0</v>
+      </c>
+      <c r="AM135">
+        <v>0</v>
+      </c>
+      <c r="AN135">
+        <v>0</v>
+      </c>
+      <c r="AO135">
+        <v>0</v>
+      </c>
+      <c r="AP135">
+        <v>0</v>
+      </c>
+      <c r="AQ135">
+        <v>0</v>
+      </c>
+      <c r="AR135">
+        <v>0</v>
+      </c>
+      <c r="AS135">
+        <v>0</v>
+      </c>
+      <c r="AT135">
+        <v>0</v>
+      </c>
+      <c r="AU135">
+        <v>0</v>
+      </c>
+      <c r="AV135">
+        <v>0</v>
+      </c>
+      <c r="AW135">
+        <v>0</v>
+      </c>
+      <c r="AX135">
+        <v>0</v>
+      </c>
+      <c r="AY135">
+        <v>0</v>
+      </c>
+      <c r="AZ135">
+        <v>0</v>
+      </c>
+      <c r="BA135">
+        <v>0</v>
+      </c>
+      <c r="BB135">
+        <v>0</v>
+      </c>
+      <c r="BC135">
+        <v>0</v>
+      </c>
+      <c r="BD135">
+        <v>0</v>
+      </c>
+      <c r="BE135">
+        <v>0</v>
+      </c>
+      <c r="BF135">
+        <v>0</v>
+      </c>
+      <c r="BG135">
+        <v>0</v>
+      </c>
+      <c r="BH135">
+        <v>0</v>
+      </c>
+      <c r="BI135" s="3">
+        <v>46150.875</v>
+      </c>
+    </row>
+    <row r="136" spans="1:61">
+      <c r="A136" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B136" t="s">
+        <v>89</v>
+      </c>
+      <c r="C136" t="s">
+        <v>142</v>
+      </c>
+      <c r="D136" t="s">
+        <v>148</v>
+      </c>
+      <c r="E136" t="s">
+        <v>283</v>
+      </c>
+      <c r="F136" t="s">
+        <v>421</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>-1</v>
+      </c>
+      <c r="N136">
+        <v>-1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>425</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+      <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136">
+        <v>0</v>
+      </c>
+      <c r="Z136">
+        <v>0</v>
+      </c>
+      <c r="AA136">
+        <v>0</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>0</v>
+      </c>
+      <c r="AF136">
+        <v>0</v>
+      </c>
+      <c r="AG136">
+        <v>0</v>
+      </c>
+      <c r="AH136">
+        <v>0</v>
+      </c>
+      <c r="AI136">
+        <v>0</v>
+      </c>
+      <c r="AJ136">
+        <v>0</v>
+      </c>
+      <c r="AK136">
+        <v>0</v>
+      </c>
+      <c r="AL136">
+        <v>0</v>
+      </c>
+      <c r="AM136">
+        <v>0</v>
+      </c>
+      <c r="AN136">
+        <v>0</v>
+      </c>
+      <c r="AO136">
+        <v>0</v>
+      </c>
+      <c r="AP136">
+        <v>0</v>
+      </c>
+      <c r="AQ136">
+        <v>0</v>
+      </c>
+      <c r="AR136">
+        <v>0</v>
+      </c>
+      <c r="AS136">
+        <v>0</v>
+      </c>
+      <c r="AT136">
+        <v>0</v>
+      </c>
+      <c r="AU136">
+        <v>0</v>
+      </c>
+      <c r="AV136">
+        <v>0</v>
+      </c>
+      <c r="AW136">
+        <v>0</v>
+      </c>
+      <c r="AX136">
+        <v>0</v>
+      </c>
+      <c r="AY136">
+        <v>0</v>
+      </c>
+      <c r="AZ136">
+        <v>0</v>
+      </c>
+      <c r="BA136">
+        <v>0</v>
+      </c>
+      <c r="BB136">
+        <v>0</v>
+      </c>
+      <c r="BC136">
+        <v>0</v>
+      </c>
+      <c r="BD136">
+        <v>0</v>
+      </c>
+      <c r="BE136">
+        <v>0</v>
+      </c>
+      <c r="BF136">
+        <v>0</v>
+      </c>
+      <c r="BG136">
+        <v>0</v>
+      </c>
+      <c r="BH136">
+        <v>0</v>
+      </c>
+      <c r="BI136" s="3">
+        <v>46150.875</v>
+      </c>
+    </row>
+    <row r="137" spans="1:61">
+      <c r="A137" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B137" t="s">
+        <v>89</v>
+      </c>
+      <c r="C137" t="s">
+        <v>142</v>
+      </c>
+      <c r="D137" t="s">
+        <v>148</v>
+      </c>
+      <c r="E137" t="s">
+        <v>284</v>
+      </c>
+      <c r="F137" t="s">
+        <v>422</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>-1</v>
+      </c>
+      <c r="N137">
+        <v>-1</v>
+      </c>
+      <c r="O137" t="s">
+        <v>425</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137">
+        <v>0</v>
+      </c>
+      <c r="AI137">
+        <v>0</v>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>0</v>
+      </c>
+      <c r="AN137">
+        <v>0</v>
+      </c>
+      <c r="AO137">
+        <v>0</v>
+      </c>
+      <c r="AP137">
+        <v>0</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>0</v>
+      </c>
+      <c r="AS137">
+        <v>0</v>
+      </c>
+      <c r="AT137">
+        <v>0</v>
+      </c>
+      <c r="AU137">
+        <v>0</v>
+      </c>
+      <c r="AV137">
+        <v>0</v>
+      </c>
+      <c r="AW137">
+        <v>0</v>
+      </c>
+      <c r="AX137">
+        <v>0</v>
+      </c>
+      <c r="AY137">
+        <v>0</v>
+      </c>
+      <c r="AZ137">
+        <v>0</v>
+      </c>
+      <c r="BA137">
+        <v>0</v>
+      </c>
+      <c r="BB137">
+        <v>0</v>
+      </c>
+      <c r="BC137">
+        <v>0</v>
+      </c>
+      <c r="BD137">
+        <v>0</v>
+      </c>
+      <c r="BE137">
+        <v>0</v>
+      </c>
+      <c r="BF137">
+        <v>0</v>
+      </c>
+      <c r="BG137">
+        <v>0</v>
+      </c>
+      <c r="BH137">
+        <v>0</v>
+      </c>
+      <c r="BI137" s="3">
+        <v>46150.875</v>
+      </c>
+    </row>
+    <row r="138" spans="1:61">
+      <c r="A138" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B138" t="s">
+        <v>89</v>
+      </c>
+      <c r="C138" t="s">
+        <v>141</v>
+      </c>
+      <c r="D138" t="s">
+        <v>147</v>
+      </c>
+      <c r="E138" t="s">
+        <v>285</v>
+      </c>
+      <c r="F138" t="s">
+        <v>423</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>-1</v>
+      </c>
+      <c r="N138">
+        <v>-1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>425</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138">
+        <v>0</v>
+      </c>
+      <c r="AI138">
+        <v>0</v>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>0</v>
+      </c>
+      <c r="AN138">
+        <v>0</v>
+      </c>
+      <c r="AO138">
+        <v>0</v>
+      </c>
+      <c r="AP138">
+        <v>0</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138">
+        <v>0</v>
+      </c>
+      <c r="AV138">
+        <v>0</v>
+      </c>
+      <c r="AW138">
+        <v>0</v>
+      </c>
+      <c r="AX138">
+        <v>0</v>
+      </c>
+      <c r="AY138">
+        <v>0</v>
+      </c>
+      <c r="AZ138">
+        <v>0</v>
+      </c>
+      <c r="BA138">
+        <v>0</v>
+      </c>
+      <c r="BB138">
+        <v>0</v>
+      </c>
+      <c r="BC138">
+        <v>0</v>
+      </c>
+      <c r="BD138">
+        <v>0</v>
+      </c>
+      <c r="BE138">
+        <v>0</v>
+      </c>
+      <c r="BF138">
+        <v>0</v>
+      </c>
+      <c r="BG138">
+        <v>0</v>
+      </c>
+      <c r="BH138">
+        <v>0</v>
+      </c>
+      <c r="BI138" s="3">
+        <v>46150.875</v>
+      </c>
+    </row>
+    <row r="139" spans="1:61">
+      <c r="A139" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B139" t="s">
+        <v>90</v>
+      </c>
+      <c r="C139" t="s">
+        <v>140</v>
+      </c>
+      <c r="D139" t="s">
+        <v>148</v>
+      </c>
+      <c r="E139" t="s">
+        <v>286</v>
+      </c>
+      <c r="F139" t="s">
+        <v>424</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>-1</v>
+      </c>
+      <c r="N139">
+        <v>-1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>425</v>
+      </c>
+      <c r="P139">
         <v>1.62</v>
       </c>
-      <c r="Q135">
+      <c r="Q139">
         <v>3.6</v>
       </c>
-      <c r="R135">
+      <c r="R139">
         <v>4.75</v>
       </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135">
-        <v>0</v>
-      </c>
-      <c r="AI135">
-        <v>0</v>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>0</v>
-      </c>
-      <c r="AN135">
-        <v>0</v>
-      </c>
-      <c r="AO135">
-        <v>0</v>
-      </c>
-      <c r="AP135">
-        <v>0</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135">
-        <v>0</v>
-      </c>
-      <c r="AV135">
-        <v>0</v>
-      </c>
-      <c r="AW135">
-        <v>0</v>
-      </c>
-      <c r="AX135">
-        <v>0</v>
-      </c>
-      <c r="AY135">
-        <v>0</v>
-      </c>
-      <c r="AZ135">
-        <v>0</v>
-      </c>
-      <c r="BA135">
-        <v>0</v>
-      </c>
-      <c r="BB135">
-        <v>0</v>
-      </c>
-      <c r="BC135">
-        <v>0</v>
-      </c>
-      <c r="BD135">
-        <v>0</v>
-      </c>
-      <c r="BE135">
-        <v>0</v>
-      </c>
-      <c r="BF135">
-        <v>0</v>
-      </c>
-      <c r="BG135">
-        <v>0</v>
-      </c>
-      <c r="BH135">
-        <v>0</v>
-      </c>
-      <c r="BI135" s="3">
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139">
+        <v>0</v>
+      </c>
+      <c r="AI139">
+        <v>0</v>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>0</v>
+      </c>
+      <c r="AN139">
+        <v>0</v>
+      </c>
+      <c r="AO139">
+        <v>0</v>
+      </c>
+      <c r="AP139">
+        <v>0</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139">
+        <v>0</v>
+      </c>
+      <c r="AV139">
+        <v>0</v>
+      </c>
+      <c r="AW139">
+        <v>0</v>
+      </c>
+      <c r="AX139">
+        <v>0</v>
+      </c>
+      <c r="AY139">
+        <v>0</v>
+      </c>
+      <c r="AZ139">
+        <v>0</v>
+      </c>
+      <c r="BA139">
+        <v>0</v>
+      </c>
+      <c r="BB139">
+        <v>0</v>
+      </c>
+      <c r="BC139">
+        <v>0</v>
+      </c>
+      <c r="BD139">
+        <v>0</v>
+      </c>
+      <c r="BE139">
+        <v>0</v>
+      </c>
+      <c r="BF139">
+        <v>0</v>
+      </c>
+      <c r="BG139">
+        <v>0</v>
+      </c>
+      <c r="BH139">
+        <v>0</v>
+      </c>
+      <c r="BI139" s="3">
         <v>46150.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -319,75 +319,75 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>France National</t>
+  </si>
+  <si>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>Netherlands Eredivisie Women</t>
   </si>
   <si>
@@ -412,24 +412,24 @@
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>France Ligue 1</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -439,12 +439,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -481,223 +481,235 @@
     <t>Mil Mugan FK</t>
   </si>
   <si>
+    <t>PDRM</t>
+  </si>
+  <si>
     <t>Terengganu</t>
   </si>
   <si>
-    <t>PDRM</t>
-  </si>
-  <si>
     <t>Sur</t>
   </si>
   <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
     <t>BFC Daugavpils</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
     <t>Karlovac 1919</t>
   </si>
   <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Amstetten</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Brann W</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Lillestrøm W</t>
+  </si>
+  <si>
+    <t>Rīgas FS</t>
+  </si>
+  <si>
+    <t>Kapfenberger SV</t>
+  </si>
+  <si>
+    <t>Anorthosis</t>
+  </si>
+  <si>
+    <t>Molde W</t>
+  </si>
+  <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>WSPG Wels</t>
+  </si>
+  <si>
+    <t>Austria Salzburg</t>
+  </si>
+  <si>
+    <t>Fortuna Ålesund</t>
+  </si>
+  <si>
     <t>Liefering</t>
   </si>
   <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
-    <t>Amstetten</t>
-  </si>
-  <si>
-    <t>Anorthosis</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
-  </si>
-  <si>
-    <t>Kapfenberger SV</t>
-  </si>
-  <si>
-    <t>Rīgas FS</t>
-  </si>
-  <si>
-    <t>Brann W</t>
-  </si>
-  <si>
-    <t>WSPG Wels</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Austria Salzburg</t>
-  </si>
-  <si>
-    <t>Molde W</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Fortuna Ålesund</t>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
     <t>JS Kabylie</t>
   </si>
   <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
+    <t>Víkingur Reykjavík</t>
+  </si>
+  <si>
+    <t>Villefranche</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
   </si>
   <si>
     <t>Durban City</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Villefranche</t>
+    <t>PSV W</t>
   </si>
   <si>
     <t>NAC Breda W</t>
   </si>
   <si>
+    <t>PEC Zwolle W</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Utrecht W</t>
+  </si>
+  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
-    <t>PSV W</t>
+    <t>Excelsior Barendrecht W</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
   </si>
   <si>
     <t>Ajax W</t>
   </si>
   <si>
-    <t>Utrecht W</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>PEC Zwolle W</t>
-  </si>
-  <si>
-    <t>Excelsior Barendrecht W</t>
-  </si>
-  <si>
-    <t>CFR Cluj</t>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Wil</t>
   </si>
   <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
     <t>Cádiz</t>
   </si>
   <si>
+    <t>Pescara</t>
+  </si>
+  <si>
+    <t>Monza</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Avellino</t>
+  </si>
+  <si>
+    <t>Catanzaro</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
     <t>Virtus Entella</t>
   </si>
   <si>
-    <t>Avellino</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
     <t>Südtirol</t>
   </si>
   <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>Cesena</t>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Venezia</t>
@@ -706,78 +718,66 @@
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Pescara</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Catanzaro</t>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Torino</t>
   </si>
   <si>
     <t>Wexford</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>Standard Liège</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
     <t>Lens</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Torino</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
+    <t>Wisła Kraków</t>
   </si>
   <si>
     <t>Levante UD</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
     <t>MC Alger</t>
   </si>
   <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
@@ -793,87 +793,87 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Atlético Rafaela</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Voždovac</t>
+  </si>
+  <si>
+    <t>Inter de Limeira</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Orlando Pride</t>
+  </si>
+  <si>
+    <t>Loznica</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Orense SC</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
     <t>Maringá</t>
   </si>
   <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Brusque</t>
   </si>
   <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Inter de Limeira</t>
-  </si>
-  <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
-    <t>Voždovac</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Orense SC</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Loznica</t>
-  </si>
-  <si>
-    <t>Brusque</t>
-  </si>
-  <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Atlético Rafaela</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
@@ -895,223 +895,235 @@
     <t>Zira</t>
   </si>
   <si>
+    <t>Pulau Pinang</t>
+  </si>
+  <si>
     <t>Imigresen</t>
   </si>
   <si>
-    <t>Pulau Pinang</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
-    <t>El Gounah</t>
-  </si>
-  <si>
     <t>Riga</t>
   </si>
   <si>
     <t>Arda</t>
   </si>
   <si>
+    <t>SKA Khabarovsk</t>
+  </si>
+  <si>
+    <t>Trajal Krusevac</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
     <t>New York RB II</t>
   </si>
   <si>
-    <t>SKA Khabarovsk</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
     <t>Kapaz</t>
   </si>
   <si>
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Korona Kielce</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Austria Klagenfurt</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>First Vienna</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Haugesund W</t>
+  </si>
+  <si>
+    <t>Liepāja</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Digenis Ypsonas</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
+    <t>Bodø / Glimt W</t>
+  </si>
+  <si>
+    <t>Sturm Graz II</t>
+  </si>
+  <si>
+    <t>Austria Lustenau</t>
+  </si>
+  <si>
+    <t>Lyn W</t>
+  </si>
+  <si>
     <t>Admira</t>
   </si>
   <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Austria Klagenfurt</t>
-  </si>
-  <si>
-    <t>Digenis Ypsonas</t>
-  </si>
-  <si>
-    <t>First Vienna</t>
-  </si>
-  <si>
-    <t>Haugesund W</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Liepāja</t>
-  </si>
-  <si>
-    <t>Stabæk Women</t>
-  </si>
-  <si>
-    <t>Sturm Graz II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Austria Lustenau</t>
-  </si>
-  <si>
-    <t>Røa Women</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
-    <t>Bodø / Glimt W</t>
-  </si>
-  <si>
-    <t>Korona Kielce</t>
-  </si>
-  <si>
-    <t>Lyn W</t>
+    <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Arminia Bielefeld</t>
-  </si>
-  <si>
     <t>ES Sétif</t>
   </si>
   <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>MSV Duisburg</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>MSV Duisburg</t>
+    <t>Thór</t>
+  </si>
+  <si>
+    <t>Ajaccio</t>
+  </si>
+  <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
+    <t>HB</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>HB</t>
-  </si>
-  <si>
-    <t>Thór</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>Ajaccio</t>
+    <t>ADO Den Haag W</t>
   </si>
   <si>
     <t>Twente W</t>
   </si>
   <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>CS U Craiova</t>
+  </si>
+  <si>
+    <t>Heerenveen W</t>
+  </si>
+  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>ADO Den Haag W</t>
+    <t>Feyenoord W</t>
+  </si>
+  <si>
+    <t>HNK Vukovar 1991</t>
   </si>
   <si>
     <t>AZ W</t>
   </si>
   <si>
-    <t>Heerenveen W</t>
-  </si>
-  <si>
-    <t>HNK Vukovar 1991</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>Feyenoord W</t>
-  </si>
-  <si>
-    <t>CS U Craiova</t>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
     <t>Deportivo La Coruña</t>
   </si>
   <si>
+    <t>Spezia</t>
+  </si>
+  <si>
+    <t>Empoli</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>Sampdoria</t>
+  </si>
+  <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
+    <t>Calcio Padova</t>
+  </si>
+  <si>
     <t>Carrarese</t>
   </si>
   <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Eintracht Frankfurt</t>
-  </si>
-  <si>
     <t>Juve Stabia</t>
   </si>
   <si>
-    <t>Empoli</t>
-  </si>
-  <si>
-    <t>Calcio Padova</t>
+    <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Palermo</t>
@@ -1120,78 +1132,66 @@
     <t>Mantova</t>
   </si>
   <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
-    <t>Sampdoria</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
   </si>
   <si>
     <t>Longford Town</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>Nantes</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Sassuolo</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Derry City</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>CA Osasuna</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
     <t>MB Rouisset</t>
   </si>
   <si>
     <t>Waterford</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
     <t>Keflavík</t>
   </si>
   <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
@@ -1207,85 +1207,85 @@
     <t>Monterey Bay</t>
   </si>
   <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
     <t>Sarajevo</t>
   </si>
   <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Zemun</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
+    <t>Mačva Šabac</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Leones del Norte</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Confiança</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Leones del Norte</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Mačva Šabac</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Zemun</t>
-  </si>
-  <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Orange County SC</t>
@@ -4262,7 +4262,7 @@
         <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
         <v>162</v>
@@ -4298,13 +4298,13 @@
         <v>425</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4343,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -4483,13 +4483,13 @@
         <v>425</v>
       </c>
       <c r="P16">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -4528,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG16">
         <v>0</v>
@@ -4668,13 +4668,13 @@
         <v>425</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>147</v>
@@ -4853,13 +4853,13 @@
         <v>425</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -4999,7 +4999,7 @@
         <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>147</v>
@@ -5038,13 +5038,13 @@
         <v>425</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5184,10 +5184,10 @@
         <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
         <v>167</v>
@@ -5369,7 +5369,7 @@
         <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -5408,13 +5408,13 @@
         <v>425</v>
       </c>
       <c r="P21">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -5963,13 +5963,13 @@
         <v>425</v>
       </c>
       <c r="P24">
-        <v>3.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
         <v>3.78</v>
       </c>
       <c r="R24">
-        <v>1.97</v>
+        <v>4.18</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -6008,10 +6008,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6148,13 +6148,13 @@
         <v>425</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -6333,13 +6333,13 @@
         <v>425</v>
       </c>
       <c r="P26">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="Q26">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>4.19</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -6518,13 +6518,13 @@
         <v>425</v>
       </c>
       <c r="P27">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6664,10 +6664,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
         <v>175</v>
@@ -6703,13 +6703,13 @@
         <v>425</v>
       </c>
       <c r="P28">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6748,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -6849,7 +6849,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
         <v>147</v>
@@ -6888,13 +6888,13 @@
         <v>425</v>
       </c>
       <c r="P29">
-        <v>4.04</v>
+        <v>2.63</v>
       </c>
       <c r="Q29">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="R29">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7034,10 +7034,10 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" t="s">
         <v>177</v>
@@ -7073,13 +7073,13 @@
         <v>425</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7219,10 +7219,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E31" t="s">
         <v>178</v>
@@ -7258,13 +7258,13 @@
         <v>425</v>
       </c>
       <c r="P31">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7404,7 +7404,7 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -7443,13 +7443,13 @@
         <v>425</v>
       </c>
       <c r="P32">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7589,7 +7589,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
         <v>148</v>
@@ -7628,13 +7628,13 @@
         <v>425</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -7813,13 +7813,13 @@
         <v>425</v>
       </c>
       <c r="P34">
-        <v>2.4</v>
+        <v>4.78</v>
       </c>
       <c r="Q34">
-        <v>3.5</v>
+        <v>4.14</v>
       </c>
       <c r="R34">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7858,10 +7858,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -7959,7 +7959,7 @@
         <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
         <v>147</v>
@@ -7998,13 +7998,13 @@
         <v>425</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8144,10 +8144,10 @@
         <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
         <v>183</v>
@@ -8183,13 +8183,13 @@
         <v>425</v>
       </c>
       <c r="P36">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -8228,10 +8228,10 @@
         <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
         <v>148</v>
@@ -8514,10 +8514,10 @@
         <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
         <v>185</v>
@@ -8553,13 +8553,13 @@
         <v>425</v>
       </c>
       <c r="P38">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Q38">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8598,10 +8598,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -8699,10 +8699,10 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
         <v>186</v>
@@ -8738,13 +8738,13 @@
         <v>425</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8783,10 +8783,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -8884,10 +8884,10 @@
         <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E40" t="s">
         <v>187</v>
@@ -8923,13 +8923,13 @@
         <v>425</v>
       </c>
       <c r="P40">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -9069,10 +9069,10 @@
         <v>74</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" t="s">
         <v>188</v>
@@ -9108,13 +9108,13 @@
         <v>425</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -9293,13 +9293,13 @@
         <v>425</v>
       </c>
       <c r="P42">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R42">
-        <v>5.73</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         <v>425</v>
       </c>
       <c r="P43">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q43">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R43">
-        <v>2.4</v>
+        <v>5.73</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9624,7 +9624,7 @@
         <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
         <v>147</v>
@@ -9848,13 +9848,13 @@
         <v>425</v>
       </c>
       <c r="P45">
-        <v>2.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q45">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>2.32</v>
+        <v>3.75</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -10182,7 +10182,7 @@
         <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E47" t="s">
         <v>194</v>
@@ -10218,13 +10218,13 @@
         <v>425</v>
       </c>
       <c r="P47">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -10403,13 +10403,13 @@
         <v>425</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -10549,7 +10549,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
         <v>147</v>
@@ -10588,13 +10588,13 @@
         <v>425</v>
       </c>
       <c r="P49">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -10734,7 +10734,7 @@
         <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
         <v>147</v>
@@ -10773,13 +10773,13 @@
         <v>425</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -10919,7 +10919,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
         <v>147</v>
@@ -10958,13 +10958,13 @@
         <v>425</v>
       </c>
       <c r="P51">
-        <v>1.77</v>
+        <v>3.03</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R51">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11104,7 +11104,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
         <v>148</v>
@@ -11328,13 +11328,13 @@
         <v>425</v>
       </c>
       <c r="P53">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -11477,7 +11477,7 @@
         <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E54" t="s">
         <v>201</v>
@@ -11513,13 +11513,13 @@
         <v>425</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -11662,7 +11662,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E55" t="s">
         <v>202</v>
@@ -11698,13 +11698,13 @@
         <v>425</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -11847,7 +11847,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E56" t="s">
         <v>203</v>
@@ -11880,7 +11880,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -12029,10 +12029,10 @@
         <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D57" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E57" t="s">
         <v>204</v>
@@ -12068,13 +12068,13 @@
         <v>425</v>
       </c>
       <c r="P57">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="Q57">
-        <v>6.55</v>
+        <v>4</v>
       </c>
       <c r="R57">
-        <v>10.6</v>
+        <v>5.46</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12214,10 +12214,10 @@
         <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
         <v>205</v>
@@ -12253,13 +12253,13 @@
         <v>425</v>
       </c>
       <c r="P58">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12769,7 +12769,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
         <v>147</v>
@@ -13139,7 +13139,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -13178,13 +13178,13 @@
         <v>425</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -13509,7 +13509,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
         <v>147</v>
@@ -13879,7 +13879,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
         <v>147</v>
@@ -14064,7 +14064,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D68" t="s">
         <v>147</v>
@@ -14103,13 +14103,13 @@
         <v>425</v>
       </c>
       <c r="P68">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -14288,13 +14288,13 @@
         <v>425</v>
       </c>
       <c r="P69">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="Q69">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="R69">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -14473,13 +14473,13 @@
         <v>425</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="Q70">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14843,13 +14843,13 @@
         <v>425</v>
       </c>
       <c r="P72">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q72">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R72">
-        <v>6.5</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -14894,10 +14894,10 @@
         <v>0</v>
       </c>
       <c r="AG72">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH72">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI72">
         <v>0</v>
@@ -15028,13 +15028,13 @@
         <v>425</v>
       </c>
       <c r="P73">
-        <v>3.16</v>
+        <v>1.33</v>
       </c>
       <c r="Q73">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="R73">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15079,10 +15079,10 @@
         <v>0</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH73">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI73">
         <v>0</v>
@@ -15398,13 +15398,13 @@
         <v>425</v>
       </c>
       <c r="P75">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="Q75">
-        <v>3.18</v>
+        <v>3.56</v>
       </c>
       <c r="R75">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -15443,10 +15443,10 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AF75">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -15583,13 +15583,13 @@
         <v>425</v>
       </c>
       <c r="P76">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q76">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="R76">
-        <v>3.16</v>
+        <v>6.11</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -15628,10 +15628,10 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF76">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -15953,13 +15953,13 @@
         <v>425</v>
       </c>
       <c r="P78">
-        <v>2.03</v>
+        <v>3.41</v>
       </c>
       <c r="Q78">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="R78">
-        <v>3.58</v>
+        <v>2.16</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -15998,10 +15998,10 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF78">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -16138,13 +16138,13 @@
         <v>425</v>
       </c>
       <c r="P79">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="Q79">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="R79">
-        <v>6.11</v>
+        <v>3.16</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16183,10 +16183,10 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF79">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -16323,13 +16323,13 @@
         <v>425</v>
       </c>
       <c r="P80">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q80">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="R80">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -16368,10 +16368,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF80">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -16508,13 +16508,13 @@
         <v>425</v>
       </c>
       <c r="P81">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q81">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="R81">
-        <v>4.08</v>
+        <v>4.3</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF81">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16693,13 +16693,13 @@
         <v>425</v>
       </c>
       <c r="P82">
-        <v>1.55</v>
+        <v>1.99</v>
       </c>
       <c r="Q82">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="R82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16738,10 +16738,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16878,13 +16878,13 @@
         <v>425</v>
       </c>
       <c r="P83">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Q83">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="R83">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16923,10 +16923,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AF83">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17024,7 +17024,7 @@
         <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D84" t="s">
         <v>147</v>
@@ -17248,13 +17248,13 @@
         <v>425</v>
       </c>
       <c r="P85">
-        <v>3.41</v>
+        <v>1.78</v>
       </c>
       <c r="Q85">
-        <v>3.22</v>
+        <v>3.84</v>
       </c>
       <c r="R85">
-        <v>2.16</v>
+        <v>4.08</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -17293,10 +17293,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AF85">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -17433,13 +17433,13 @@
         <v>425</v>
       </c>
       <c r="P86">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="Q86">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="R86">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -17618,13 +17618,13 @@
         <v>425</v>
       </c>
       <c r="P87">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="Q87">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R87">
-        <v>3.79</v>
+        <v>6.78</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -17767,7 +17767,7 @@
         <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E88" t="s">
         <v>235</v>
@@ -17803,13 +17803,13 @@
         <v>425</v>
       </c>
       <c r="P88">
-        <v>2.25</v>
+        <v>3.88</v>
       </c>
       <c r="Q88">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="R88">
-        <v>3.15</v>
+        <v>1.96</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -17988,13 +17988,13 @@
         <v>425</v>
       </c>
       <c r="P89">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="Q89">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R89">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18134,7 +18134,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
         <v>148</v>
@@ -18173,13 +18173,13 @@
         <v>425</v>
       </c>
       <c r="P90">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="Q90">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18319,10 +18319,10 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E91" t="s">
         <v>238</v>
@@ -18358,13 +18358,13 @@
         <v>425</v>
       </c>
       <c r="P91">
-        <v>1.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q91">
-        <v>6.09</v>
+        <v>3.3</v>
       </c>
       <c r="R91">
-        <v>10.6</v>
+        <v>2.7</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -18504,7 +18504,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
         <v>148</v>
@@ -18543,13 +18543,13 @@
         <v>425</v>
       </c>
       <c r="P92">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="Q92">
         <v>3.34</v>
       </c>
       <c r="R92">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -18689,7 +18689,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
         <v>148</v>
@@ -18728,13 +18728,13 @@
         <v>425</v>
       </c>
       <c r="P93">
-        <v>1.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q93">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="R93">
-        <v>6.26</v>
+        <v>2.7</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -18874,10 +18874,10 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E94" t="s">
         <v>241</v>
@@ -18913,13 +18913,13 @@
         <v>425</v>
       </c>
       <c r="P94">
-        <v>3.11</v>
+        <v>2.37</v>
       </c>
       <c r="Q94">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R94">
-        <v>2.24</v>
+        <v>3.56</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -18958,10 +18958,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19059,10 +19059,10 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E95" t="s">
         <v>242</v>
@@ -19098,13 +19098,13 @@
         <v>425</v>
       </c>
       <c r="P95">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="Q95">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R95">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19143,10 +19143,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -19244,7 +19244,7 @@
         <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
         <v>148</v>
@@ -19283,13 +19283,13 @@
         <v>425</v>
       </c>
       <c r="P96">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="Q96">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="R96">
-        <v>2.99</v>
+        <v>6.26</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -19328,10 +19328,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -19429,10 +19429,10 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E97" t="s">
         <v>244</v>
@@ -19468,13 +19468,13 @@
         <v>425</v>
       </c>
       <c r="P97">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="Q97">
-        <v>4.1</v>
+        <v>3.51</v>
       </c>
       <c r="R97">
-        <v>6.78</v>
+        <v>3.15</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -19614,10 +19614,10 @@
         <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E98" t="s">
         <v>245</v>
@@ -19653,13 +19653,13 @@
         <v>425</v>
       </c>
       <c r="P98">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="Q98">
-        <v>3.18</v>
+        <v>6.09</v>
       </c>
       <c r="R98">
-        <v>2.35</v>
+        <v>10.6</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -19838,13 +19838,13 @@
         <v>425</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20023,13 +20023,13 @@
         <v>425</v>
       </c>
       <c r="P100">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20169,7 +20169,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D101" t="s">
         <v>147</v>
@@ -20354,7 +20354,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D102" t="s">
         <v>148</v>
@@ -20539,7 +20539,7 @@
         <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D103" t="s">
         <v>148</v>
@@ -20578,13 +20578,13 @@
         <v>425</v>
       </c>
       <c r="P103">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="Q103">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R103">
-        <v>4.23</v>
+        <v>3.11</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -20629,10 +20629,10 @@
         <v>0</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH103">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI103">
         <v>0</v>
@@ -20724,7 +20724,7 @@
         <v>84</v>
       </c>
       <c r="C104" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D104" t="s">
         <v>148</v>
@@ -20763,13 +20763,13 @@
         <v>425</v>
       </c>
       <c r="P104">
-        <v>1.57</v>
+        <v>3.13</v>
       </c>
       <c r="Q104">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R104">
-        <v>4.59</v>
+        <v>1.94</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -20814,10 +20814,10 @@
         <v>0</v>
       </c>
       <c r="AG104">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH104">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI104">
         <v>0</v>
@@ -20909,7 +20909,7 @@
         <v>84</v>
       </c>
       <c r="C105" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D105" t="s">
         <v>148</v>
@@ -20948,13 +20948,13 @@
         <v>425</v>
       </c>
       <c r="P105">
-        <v>3.13</v>
+        <v>1.57</v>
       </c>
       <c r="Q105">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R105">
-        <v>1.94</v>
+        <v>4.59</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -20999,10 +20999,10 @@
         <v>0</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH105">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI105">
         <v>0</v>
@@ -21094,7 +21094,7 @@
         <v>84</v>
       </c>
       <c r="C106" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
         <v>148</v>
@@ -21133,13 +21133,13 @@
         <v>425</v>
       </c>
       <c r="P106">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="Q106">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R106">
-        <v>3.11</v>
+        <v>4.23</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -21184,10 +21184,10 @@
         <v>0</v>
       </c>
       <c r="AG106">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH106">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI106">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>87</v>
       </c>
       <c r="C110" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D110" t="s">
         <v>148</v>
@@ -22207,7 +22207,7 @@
         <v>141</v>
       </c>
       <c r="D112" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E112" t="s">
         <v>259</v>
@@ -22392,7 +22392,7 @@
         <v>142</v>
       </c>
       <c r="D113" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E113" t="s">
         <v>260</v>
@@ -22574,7 +22574,7 @@
         <v>89</v>
       </c>
       <c r="C114" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D114" t="s">
         <v>148</v>
@@ -22759,7 +22759,7 @@
         <v>89</v>
       </c>
       <c r="C115" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D115" t="s">
         <v>148</v>
@@ -22944,7 +22944,7 @@
         <v>89</v>
       </c>
       <c r="C116" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D116" t="s">
         <v>148</v>
@@ -23129,7 +23129,7 @@
         <v>89</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D117" t="s">
         <v>147</v>
@@ -23314,7 +23314,7 @@
         <v>89</v>
       </c>
       <c r="C118" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D118" t="s">
         <v>148</v>
@@ -23499,10 +23499,10 @@
         <v>89</v>
       </c>
       <c r="C119" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D119" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E119" t="s">
         <v>266</v>
@@ -23684,10 +23684,10 @@
         <v>89</v>
       </c>
       <c r="C120" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E120" t="s">
         <v>267</v>
@@ -23869,10 +23869,10 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D121" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E121" t="s">
         <v>268</v>
@@ -24054,7 +24054,7 @@
         <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D122" t="s">
         <v>148</v>
@@ -24239,7 +24239,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
         <v>147</v>
@@ -24424,7 +24424,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
         <v>148</v>
@@ -24609,7 +24609,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
         <v>148</v>
@@ -24648,13 +24648,13 @@
         <v>425</v>
       </c>
       <c r="P125">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D126" t="s">
         <v>148</v>
@@ -24979,10 +24979,10 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D127" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E127" t="s">
         <v>274</v>
@@ -25018,13 +25018,13 @@
         <v>425</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25164,10 +25164,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D128" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E128" t="s">
         <v>275</v>
@@ -25349,7 +25349,7 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D129" t="s">
         <v>148</v>
@@ -25388,13 +25388,13 @@
         <v>425</v>
       </c>
       <c r="P129">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -25534,10 +25534,10 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D130" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E130" t="s">
         <v>277</v>
@@ -25573,13 +25573,13 @@
         <v>425</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -25722,7 +25722,7 @@
         <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E131" t="s">
         <v>278</v>
@@ -25904,10 +25904,10 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E132" t="s">
         <v>279</v>
@@ -26089,10 +26089,10 @@
         <v>89</v>
       </c>
       <c r="C133" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="D133" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E133" t="s">
         <v>280</v>
@@ -26274,10 +26274,10 @@
         <v>89</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D134" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E134" t="s">
         <v>281</v>
@@ -26310,7 +26310,7 @@
         <v>-1</v>
       </c>
       <c r="O134" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -26459,10 +26459,10 @@
         <v>89</v>
       </c>
       <c r="C135" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D135" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E135" t="s">
         <v>282</v>
@@ -26495,7 +26495,7 @@
         <v>-1</v>
       </c>
       <c r="O135" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -26644,7 +26644,7 @@
         <v>89</v>
       </c>
       <c r="C136" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D136" t="s">
         <v>148</v>
@@ -26829,7 +26829,7 @@
         <v>89</v>
       </c>
       <c r="C137" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D137" t="s">
         <v>148</v>
@@ -27017,7 +27017,7 @@
         <v>141</v>
       </c>
       <c r="D138" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E138" t="s">
         <v>285</v>

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -840,7 +840,7 @@
         <v>1.04</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AD2" t="n">
         <v>3.75</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>1.07</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK12" t="n">
         <v>2.32</v>
@@ -2855,7 +2855,7 @@
         <v>1.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>1.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>8.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>3.11</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>2.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AD14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG14" t="n">
         <v>4.5</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
         <v>2.28</v>
       </c>
-      <c r="AG14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>4.86</v>
       </c>
       <c r="R17" t="n">
-        <v>3.75</v>
+        <v>9.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
         <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.79</v>
+        <v>4.19</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R26" t="n">
-        <v>4.19</v>
+        <v>6.17</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>3.33</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>3.78</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.33</v>
+        <v>3.58</v>
       </c>
       <c r="R28" t="n">
-        <v>3.78</v>
+        <v>2.38</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="Q29" t="n">
         <v>3.78</v>
       </c>
       <c r="R29" t="n">
-        <v>4.18</v>
+        <v>1.97</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,28 +6317,28 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>3.57</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R41" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.44</v>
+        <v>3.61</v>
       </c>
       <c r="R45" t="n">
-        <v>2.79</v>
+        <v>2.32</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R50" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="R51" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.77</v>
+        <v>3.03</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="R69" t="n">
-        <v>2.25</v>
+        <v>6.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.96</v>
+        <v>1.49</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
       <c r="R70" t="n">
-        <v>2.19</v>
+        <v>5.11</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.33</v>
+        <v>3.16</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="R71" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14445,10 +14445,10 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.49</v>
+        <v>2.96</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R72" t="n">
-        <v>5.11</v>
+        <v>2.19</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.16</v>
+        <v>2.6</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.49</v>
+        <v>3.41</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="R74" t="n">
-        <v>6.11</v>
+        <v>2.16</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.57</v>
+        <v>1.49</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="R75" t="n">
-        <v>2.13</v>
+        <v>6.11</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="R78" t="n">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.35</v>
+        <v>3.56</v>
       </c>
       <c r="R79" t="n">
-        <v>6.14</v>
+        <v>3.05</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.41</v>
+        <v>3.57</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R82" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB82" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC82" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.16</v>
+        <v>4.35</v>
       </c>
       <c r="R84" t="n">
-        <v>3.16</v>
+        <v>6.14</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.03</v>
+        <v>3.16</v>
       </c>
       <c r="R85" t="n">
-        <v>5.63</v>
+        <v>3.16</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,16 +17197,16 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.38</v>
+        <v>5.03</v>
       </c>
       <c r="R86" t="n">
-        <v>3.58</v>
+        <v>5.63</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.18</v>
+        <v>3.51</v>
       </c>
       <c r="R87" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,133 +17743,133 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R88" t="n">
-        <v>1.96</v>
+        <v>3.56</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R89" t="n">
-        <v>3.56</v>
+        <v>2.24</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.3</v>
+        <v>6.09</v>
       </c>
       <c r="R90" t="n">
-        <v>2.7</v>
+        <v>10.6</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.51</v>
+        <v>3.18</v>
       </c>
       <c r="R91" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.42</v>
+        <v>1.5</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="R92" t="n">
-        <v>2.7</v>
+        <v>6.26</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="R93" t="n">
-        <v>6.26</v>
+        <v>2.7</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R94" t="n">
-        <v>3.79</v>
+        <v>6.78</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R95" t="n">
-        <v>6.78</v>
+        <v>3.79</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q96" t="n">
-        <v>6.09</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>10.6</v>
+        <v>2.7</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.11</v>
+        <v>2.29</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="R97" t="n">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.29</v>
+        <v>3.88</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="R98" t="n">
-        <v>2.99</v>
+        <v>1.96</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.68</v>
+        <v>3.13</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R104" t="n">
-        <v>4.23</v>
+        <v>1.94</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.13</v>
+        <v>1.57</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R105" t="n">
-        <v>1.94</v>
+        <v>4.59</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R106" t="n">
-        <v>3.11</v>
+        <v>4.23</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21340,10 +21340,10 @@
         <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="R107" t="n">
-        <v>4.59</v>
+        <v>3.11</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21537,10 +21537,10 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26013,7 +26013,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-05-08.xlsx
+++ b/jogos_2026-05-08.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -2867,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="R20" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>4.19</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>1.97</v>
+        <v>3.14</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,19 +6326,19 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,28 +7696,28 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -7735,40 +7735,40 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="R38" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF38" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S39" t="n">
         <v>3.65</v>
       </c>
-      <c r="R39" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,19 +8401,19 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.44</v>
+        <v>3.78</v>
       </c>
       <c r="R41" t="n">
-        <v>1.99</v>
+        <v>4.18</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8690,70 +8690,70 @@
         <v>5.73</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8762,52 +8762,52 @@
         <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU42" t="n">
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="R43" t="n">
         <v>2.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.61</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S47" t="n">
         <v>4</v>
       </c>
-      <c r="R47" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="R49" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="R50" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
       <c r="R51" t="n">
-        <v>2.79</v>
+        <v>2.04</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.03</v>
+        <v>2.31</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="R52" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,83 +11632,83 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11750,19 +11750,19 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,133 +13212,133 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,79 +13606,79 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>7.43</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
@@ -13720,19 +13720,19 @@
         <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF67" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,79 +14000,79 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.33</v>
+        <v>3.16</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="R69" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM69" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO69" t="n">
         <v>0</v>
@@ -14114,19 +14114,19 @@
         <v>0</v>
       </c>
       <c r="BB69" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC69" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD69" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF69" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG69" t="n">
         <v>0</v>
@@ -14206,70 +14206,70 @@
         <v>5.11</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM70" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN70" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO70" t="n">
         <v>0</v>
@@ -14311,19 +14311,19 @@
         <v>0</v>
       </c>
       <c r="BB70" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD70" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF70" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,79 +14394,79 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.16</v>
+        <v>1.33</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
@@ -14508,19 +14508,19 @@
         <v>0</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
@@ -14600,70 +14600,70 @@
         <v>2.19</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO72" t="n">
         <v>0</v>
@@ -14705,19 +14705,19 @@
         <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD72" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG72" t="n">
         <v>0</v>
@@ -14797,70 +14797,70 @@
         <v>2.25</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM73" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AN73" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO73" t="n">
         <v>0</v>
@@ -14902,19 +14902,19 @@
         <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC73" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD73" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE73" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF73" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.41</v>
+        <v>1.49</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="R74" t="n">
-        <v>2.16</v>
+        <v>6.11</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.49</v>
+        <v>3.41</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="R75" t="n">
-        <v>6.11</v>
+        <v>2.16</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="R76" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,55 +15576,55 @@
         </is>
       </c>
       <c r="P77" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R77" t="n">
+        <v>4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF77" t="n">
         <v>1.78</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R77" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>2.1</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="R78" t="n">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,133 +15970,133 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR79" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB79" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF79" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="R80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>3.16</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.57</v>
+        <v>2.03</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R82" t="n">
-        <v>2.13</v>
+        <v>3.58</v>
       </c>
       <c r="S82" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC82" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE82" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.78</v>
+        <v>4.35</v>
       </c>
       <c r="R83" t="n">
-        <v>4.22</v>
+        <v>6.14</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF83" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.35</v>
+        <v>3.84</v>
       </c>
       <c r="R84" t="n">
-        <v>6.14</v>
+        <v>4.08</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="R85" t="n">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17349,133 +17349,133 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.03</v>
+        <v>4.84</v>
       </c>
       <c r="R86" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH86" t="n">
         <v>1.8</v>
       </c>
       <c r="AI86" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK86" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL86" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM86" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN86" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR86" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS86" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU86" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AW86" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY86" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ86" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB86" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC86" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD86" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG86" t="n">
         <v>0</v>
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="R87" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,133 +17743,133 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R88" t="n">
-        <v>3.56</v>
+        <v>2.7</v>
       </c>
       <c r="S88" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="R89" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18137,133 +18137,133 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Q90" t="n">
-        <v>6.09</v>
+        <v>5.1</v>
       </c>
       <c r="R90" t="n">
-        <v>10.6</v>
+        <v>8</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM90" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO90" t="n">
         <v>0</v>
       </c>
       <c r="AP90" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV90" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ90" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB90" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD90" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="BE90" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF90" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG90" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="R92" t="n">
-        <v>6.26</v>
+        <v>2.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.42</v>
+        <v>3.88</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="R93" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="R94" t="n">
-        <v>6.78</v>
+        <v>6.26</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="R95" t="n">
-        <v>3.79</v>
+        <v>2.24</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,133 +19319,133 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q96" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R96" t="n">
+        <v>3</v>
+      </c>
+      <c r="S96" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2</v>
+      </c>
+      <c r="U96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W96" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X96" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT96" t="n">
         <v>3.3</v>
       </c>
-      <c r="R96" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>0</v>
-      </c>
       <c r="AU96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV96" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX96" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY96" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF96" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.29</v>
+        <v>1.43</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R97" t="n">
-        <v>2.99</v>
+        <v>6.78</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R98" t="n">
-        <v>1.96</v>
+        <v>3.79</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,133 +19910,133 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL99" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM99" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN99" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR99" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB99" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC99" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD99" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF99" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,133 +20107,133 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.23</v>
+        <v>2.62</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.95</v>
+        <v>3.15</v>
       </c>
       <c r="R100" t="n">
-        <v>11.5</v>
+        <v>2.75</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI100" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK100" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM100" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN100" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO100" t="n">
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR100" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW100" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY100" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA100" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB100" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC100" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD100" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE100" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF100" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20501,79 +20501,79 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Q102" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T102" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U102" t="n">
+        <v>7</v>
+      </c>
+      <c r="V102" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W102" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X102" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI102" t="n">
         <v>4.5</v>
       </c>
-      <c r="R102" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ102" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL102" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM102" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO102" t="n">
         <v>0</v>
@@ -20615,19 +20615,19 @@
         <v>0</v>
       </c>
       <c r="BB102" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD102" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF102" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.13</v>
+        <v>1.68</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R104" t="n">
-        <v>1.94</v>
+        <v>4.23</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.57</v>
+        <v>3.13</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R105" t="n">
-        <v>4.59</v>
+        <v>1.94</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="R106" t="n">
-        <v>4.23</v>
+        <v>4.59</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21340,10 +21340,10 @@
         <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
  